--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE184"/>
+  <dimension ref="A1:AE186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 944-2025</t>
+          <t>A 26044-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45666</v>
+        <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams
+Humleblomster</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 944-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45666</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Fällmossa
 Rävticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 26044-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams
-Humleblomster</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44760</v>
+        <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3085,8 +3085,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>14.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3129,7 +3134,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3143,10 +3148,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45341</v>
+        <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3164,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3202,7 +3207,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3216,10 +3221,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45230</v>
+        <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3237,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3275,7 +3280,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45397</v>
+        <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3310,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3348,7 +3353,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3362,10 +3367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45385</v>
+        <v>44844</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3378,7 +3383,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3421,7 +3426,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3435,10 +3440,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45379</v>
+        <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3451,7 +3456,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3494,7 +3499,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3508,10 +3513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44886</v>
+        <v>45184</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3523,13 +3528,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44512</v>
+        <v>45358</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44582</v>
+        <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44582</v>
+        <v>44966</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45699</v>
+        <v>45660</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.4</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44526</v>
+        <v>45290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44974</v>
+        <v>45588</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3966,13 +3966,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>14.1</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4015,7 +4010,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44671</v>
+        <v>45547</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4044,8 +4039,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44886</v>
+        <v>46010</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4117,13 +4117,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>19.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4166,7 +4161,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4180,10 +4175,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45560</v>
+        <v>44917</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4196,7 +4191,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>10.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4239,7 +4234,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4253,10 +4248,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45358</v>
+        <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4269,7 +4264,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4312,7 +4307,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4326,10 +4321,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44887</v>
+        <v>46030</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4342,7 +4337,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4385,7 +4380,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4399,10 +4394,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45883</v>
+        <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4414,8 +4409,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>0.4</v>
+        <v>19.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45883</v>
+        <v>46030</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4531,7 +4531,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50007-2021</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44456</v>
+        <v>46037</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4560,13 +4560,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6.5</v>
+        <v>9.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4609,7 +4604,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4623,10 +4618,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45006</v>
+        <v>45264</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4639,7 +4634,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4682,7 +4677,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4692,14 +4687,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45187</v>
+        <v>45919</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4711,13 +4706,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4760,7 +4750,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4774,10 +4764,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45264</v>
+        <v>45232</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4790,7 +4780,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4833,7 +4823,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4850,7 +4840,7 @@
         <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4863,7 +4853,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4906,7 +4896,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4920,10 +4910,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44909</v>
+        <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4936,7 +4926,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4979,7 +4969,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4996,7 +4986,7 @@
         <v>45919</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5009,7 +4999,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5052,7 +5042,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5066,10 +5056,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5082,7 +5072,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5125,7 +5115,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5139,10 +5129,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45919</v>
+        <v>46078</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5155,7 +5145,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5215,7 +5205,7 @@
         <v>46078</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5271,7 +5261,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5288,7 +5278,7 @@
         <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5301,7 +5291,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5344,7 +5334,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5358,10 +5348,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45000</v>
+        <v>45883</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5374,7 +5364,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5417,7 +5407,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5431,10 +5421,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46078</v>
+        <v>45883</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5447,7 +5437,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5490,7 +5480,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5504,10 +5494,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45933</v>
+        <v>44671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5520,7 +5510,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5563,7 +5553,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5573,14 +5563,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45512</v>
+        <v>45694</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5593,7 +5583,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5636,7 +5626,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5650,10 +5640,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46078</v>
+        <v>44582</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5666,7 +5656,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5709,7 +5699,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5723,10 +5713,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45952</v>
+        <v>44582</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5739,7 +5729,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5782,7 +5772,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5796,10 +5786,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45243</v>
+        <v>45000</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5811,13 +5801,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5860,7 +5845,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5874,10 +5859,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46106</v>
+        <v>44663</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5889,13 +5874,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5938,7 +5918,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5952,10 +5932,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45962</v>
+        <v>44516</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5968,7 +5948,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6011,7 +5991,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6025,10 +6005,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45665</v>
+        <v>45167</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6041,7 +6021,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6084,7 +6064,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6094,14 +6074,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45965</v>
+        <v>45512</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6113,13 +6093,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>11.6</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6162,7 +6137,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6176,10 +6151,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44844</v>
+        <v>44830</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6192,7 +6167,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6235,7 +6210,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6249,10 +6224,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45111</v>
+        <v>46078</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6265,7 +6240,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6308,7 +6283,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6322,10 +6297,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46122</v>
+        <v>45952</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6338,7 +6313,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6381,7 +6356,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6395,10 +6370,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45986</v>
+        <v>46106</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6412,11 +6387,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6459,7 +6434,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6473,10 +6448,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45983</v>
+        <v>45965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6488,8 +6463,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6532,7 +6512,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6546,10 +6526,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45983</v>
+        <v>46122</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6562,7 +6542,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6605,7 +6585,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6619,10 +6599,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46128</v>
+        <v>45962</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6635,7 +6615,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6678,7 +6658,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6692,10 +6672,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6708,7 +6688,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6751,7 +6731,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6765,10 +6745,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45999</v>
+        <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6780,13 +6760,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8.6</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6829,7 +6804,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6843,10 +6818,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45740</v>
+        <v>45614</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6858,8 +6833,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6902,7 +6882,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6916,10 +6896,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44917</v>
+        <v>46132</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6932,7 +6912,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10.9</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6975,7 +6955,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6989,10 +6969,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46010</v>
+        <v>45397</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7005,7 +6985,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7048,7 +7028,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7062,10 +7042,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45092</v>
+        <v>44909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7078,7 +7058,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7121,7 +7101,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7135,10 +7115,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45264</v>
+        <v>45983</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7151,7 +7131,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.7</v>
+        <v>13.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7194,7 +7174,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7208,10 +7188,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45758</v>
+        <v>45264</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7224,7 +7204,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7267,7 +7247,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7281,10 +7261,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45741</v>
+        <v>45983</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7297,7 +7277,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7340,7 +7320,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7354,10 +7334,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46030</v>
+        <v>44909</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7370,7 +7350,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7413,7 +7393,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7427,10 +7407,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45747</v>
+        <v>45986</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7442,8 +7422,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>7.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7486,7 +7471,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7500,10 +7485,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46030</v>
+        <v>45758</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7516,7 +7501,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7559,7 +7544,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7573,10 +7558,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45789</v>
+        <v>45740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7589,7 +7574,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7632,7 +7617,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7646,10 +7631,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44909</v>
+        <v>45999</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7661,8 +7646,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7705,7 +7695,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7719,10 +7709,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44909</v>
+        <v>45741</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7778,7 +7768,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7792,10 +7782,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46037</v>
+        <v>45789</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7808,7 +7798,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>9.1</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7851,7 +7841,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7865,10 +7855,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45109</v>
+        <v>44526</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7881,7 +7871,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7924,7 +7914,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7938,10 +7928,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44994</v>
+        <v>45111</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7954,7 +7944,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7997,7 +7987,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8011,10 +8001,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45408</v>
+        <v>44760</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8027,7 +8017,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8070,7 +8060,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8084,10 +8074,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45012</v>
+        <v>45679</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8100,7 +8090,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>3.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8143,7 +8133,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8157,10 +8147,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44909</v>
+        <v>44754</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8172,8 +8162,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>2.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8216,7 +8211,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8230,10 +8225,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45264</v>
+        <v>45817</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8246,7 +8241,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.7</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8289,7 +8284,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8303,10 +8298,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44516</v>
+        <v>46154</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8319,7 +8314,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8362,7 +8357,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8376,10 +8371,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45429</v>
+        <v>45368</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8392,7 +8387,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8435,7 +8430,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8452,7 +8447,7 @@
         <v>46154</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8465,7 +8460,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.3</v>
+        <v>13.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8508,7 +8503,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8522,10 +8517,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44602</v>
+        <v>46154</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8538,7 +8533,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8581,7 +8576,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8595,10 +8590,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8611,7 +8606,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8654,7 +8649,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8668,10 +8663,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8684,7 +8679,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>13.6</v>
+        <v>6.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8727,7 +8722,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8741,10 +8736,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45817</v>
+        <v>46157</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8757,7 +8752,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8800,7 +8795,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8814,10 +8809,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8830,7 +8825,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8873,7 +8868,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8887,10 +8882,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8903,7 +8898,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8946,7 +8941,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8960,10 +8955,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8976,7 +8971,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9019,7 +9014,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9033,10 +9028,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9049,7 +9044,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9092,7 +9087,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9106,10 +9101,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9122,7 +9117,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9165,7 +9160,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9179,10 +9174,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44830</v>
+        <v>46177</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9195,7 +9190,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9238,7 +9233,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9252,10 +9247,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45608</v>
+        <v>46177</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9311,7 +9306,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9325,10 +9320,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45706</v>
+        <v>46181</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9341,7 +9336,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9384,7 +9379,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9398,10 +9393,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46169</v>
+        <v>46195</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9413,8 +9408,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9457,7 +9457,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9471,10 +9471,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44668</v>
+        <v>46204</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9530,7 +9530,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9544,10 +9544,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45167</v>
+        <v>46206</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>7.1</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9603,7 +9603,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9617,10 +9617,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44662</v>
+        <v>46206</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9690,10 +9690,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9749,7 +9749,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9822,7 +9822,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9895,7 +9895,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9909,10 +9909,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46177</v>
+        <v>46251</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9924,8 +9924,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9968,7 +9973,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9982,10 +9987,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46181</v>
+        <v>46206</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9998,7 +10003,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10041,7 +10046,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10055,10 +10060,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44754</v>
+        <v>45092</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10070,13 +10075,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10119,7 +10119,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10133,10 +10133,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45230</v>
+        <v>46169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44663</v>
+        <v>45560</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10265,7 +10265,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45264</v>
+        <v>46169</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10295,7 +10295,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10338,7 +10338,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10352,10 +10352,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45264</v>
+        <v>46265</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10368,7 +10368,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.3</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10411,7 +10411,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10425,10 +10425,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44781</v>
+        <v>44662</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10498,10 +10498,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46195</v>
+        <v>46169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10513,13 +10513,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10562,7 +10557,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10576,10 +10571,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45448</v>
+        <v>45456</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10592,7 +10587,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2.6</v>
+        <v>7.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10635,7 +10630,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10649,10 +10644,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44978</v>
+        <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10665,7 +10660,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10708,7 +10703,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10722,10 +10717,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44790</v>
+        <v>45385</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10738,7 +10733,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10781,7 +10776,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10795,10 +10790,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46204</v>
+        <v>45012</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10811,7 +10806,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10854,7 +10849,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10868,10 +10863,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45614</v>
+        <v>44668</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10883,13 +10878,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10932,7 +10922,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10946,10 +10936,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45593</v>
+        <v>45230</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10962,7 +10952,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11005,7 +10995,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11019,10 +11009,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44634</v>
+        <v>45429</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11035,7 +11025,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11078,7 +11068,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11092,10 +11082,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11108,7 +11098,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11151,7 +11141,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11165,10 +11155,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45232</v>
+        <v>46275</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11181,7 +11171,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11224,7 +11214,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11238,10 +11228,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11253,13 +11243,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>6.7</v>
+        <v>2.8</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11302,7 +11287,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11316,10 +11301,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11332,7 +11317,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11375,7 +11360,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11389,10 +11374,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44960</v>
+        <v>46275</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11404,13 +11389,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I143" t="n">
-        <v>14.8</v>
+        <v>2.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11453,7 +11433,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11463,14 +11443,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11483,7 +11463,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11526,7 +11506,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11540,10 +11520,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46206</v>
+        <v>45714</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11556,7 +11536,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11599,7 +11579,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11613,10 +11593,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46206</v>
+        <v>45608</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11629,7 +11609,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11672,7 +11652,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11686,10 +11666,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46206</v>
+        <v>46277</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11702,7 +11682,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11745,7 +11725,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11759,10 +11739,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46169</v>
+        <v>46277</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11775,7 +11755,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11818,7 +11798,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11832,10 +11812,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44494</v>
+        <v>45434</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11848,7 +11828,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11891,7 +11871,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11905,10 +11885,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45145</v>
+        <v>44602</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11921,7 +11901,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11964,7 +11944,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11978,10 +11958,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45679</v>
+        <v>45706</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11994,7 +11974,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12037,7 +12017,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12051,10 +12031,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44622</v>
+        <v>44781</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12067,7 +12047,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12110,7 +12090,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12124,10 +12104,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45456</v>
+        <v>44512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12140,7 +12120,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12183,7 +12163,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12197,10 +12177,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46265</v>
+        <v>45006</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12256,7 +12236,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12270,10 +12250,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46169</v>
+        <v>44978</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12286,7 +12266,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12329,7 +12309,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12343,10 +12323,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46169</v>
+        <v>44960</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12358,8 +12338,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12402,7 +12387,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12416,10 +12401,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45434</v>
+        <v>45699</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12432,7 +12417,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>3.1</v>
+        <v>5.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12475,7 +12460,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12489,10 +12474,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45209</v>
+        <v>45379</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12505,7 +12490,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12565,7 +12550,7 @@
         <v>44988</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12621,7 +12606,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12635,10 +12620,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45194</v>
+        <v>45243</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12650,8 +12635,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12694,7 +12684,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12708,10 +12698,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45368</v>
+        <v>45109</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12724,7 +12714,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12767,7 +12757,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12781,10 +12771,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44530</v>
+        <v>45408</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12840,7 +12830,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12854,10 +12844,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45714</v>
+        <v>44622</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12870,7 +12860,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12913,7 +12903,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12923,14 +12913,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46275</v>
+        <v>45159</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12943,7 +12933,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10.2</v>
+        <v>7.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12986,7 +12976,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13000,10 +12990,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46275</v>
+        <v>44790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13016,7 +13006,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13059,7 +13049,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13073,10 +13063,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46275</v>
+        <v>44887</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13089,7 +13079,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13132,7 +13122,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13146,10 +13136,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46275</v>
+        <v>44886</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13161,8 +13151,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13205,7 +13200,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13219,10 +13214,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45159</v>
+        <v>45230</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13235,7 +13230,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>7.3</v>
+        <v>4.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13278,7 +13273,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13292,10 +13287,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46275</v>
+        <v>44634</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13308,7 +13303,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13351,7 +13346,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13365,10 +13360,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45699</v>
+        <v>45194</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13381,7 +13376,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13424,7 +13419,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13438,10 +13433,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45694</v>
+        <v>45145</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13454,7 +13449,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13497,7 +13492,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13511,10 +13506,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46275</v>
+        <v>44909</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13527,7 +13522,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13570,7 +13565,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13584,10 +13579,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45253</v>
+        <v>44909</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13600,7 +13595,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13643,7 +13638,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13653,14 +13648,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45615</v>
+        <v>45187</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13672,8 +13667,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13730,10 +13730,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45012</v>
+        <v>45699</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13789,7 +13789,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13803,10 +13803,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45629</v>
+        <v>44994</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13862,7 +13862,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13876,10 +13876,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45632</v>
+        <v>45253</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13935,7 +13935,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13949,10 +13949,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45290</v>
+        <v>45341</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14008,7 +14008,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 50007-2021</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14022,10 +14022,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44966</v>
+        <v>44456</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14037,8 +14037,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14081,7 +14086,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14095,10 +14100,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45588</v>
+        <v>44530</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14111,7 +14116,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14154,7 +14159,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14168,10 +14173,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45660</v>
+        <v>45448</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14184,7 +14189,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14227,7 +14232,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14241,10 +14246,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45628</v>
+        <v>45747</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14257,7 +14262,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14300,7 +14305,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14314,10 +14319,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45184</v>
+        <v>45632</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14330,86 +14335,81 @@
         </is>
       </c>
       <c r="I183" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0</v>
+      </c>
+      <c r="S183" t="n">
+        <v>0</v>
+      </c>
+      <c r="T183" t="n">
+        <v>0</v>
+      </c>
+      <c r="U183" t="n">
+        <v>0</v>
+      </c>
+      <c r="V183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>A 54054-2024</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="n">
+        <v>45615</v>
+      </c>
+      <c r="E184" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
         <v>3.2</v>
       </c>
-      <c r="J183" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" t="n">
-        <v>0</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>0</v>
-      </c>
-      <c r="P183" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
-      <c r="R183" t="n">
-        <v>0</v>
-      </c>
-      <c r="S183" t="n">
-        <v>0</v>
-      </c>
-      <c r="T183" t="n">
-        <v>0</v>
-      </c>
-      <c r="U183" t="n">
-        <v>0</v>
-      </c>
-      <c r="V183" s="2" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>A 38788-2024</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D184" s="1" t="n">
-        <v>45547</v>
-      </c>
-      <c r="E184" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I184" t="n">
-        <v>1.6</v>
-      </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
@@ -14447,6 +14447,152 @@
         <v>0</v>
       </c>
       <c r="V184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>A 14413-2023</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="n">
+        <v>45012</v>
+      </c>
+      <c r="E185" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0</v>
+      </c>
+      <c r="S185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
+        <v>0</v>
+      </c>
+      <c r="U185" t="n">
+        <v>0</v>
+      </c>
+      <c r="V185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>A 57256-2024</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>45629</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0</v>
+      </c>
+      <c r="V186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26044-2025</t>
+          <t>A 944-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45804</v>
+        <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,17 +1088,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>31.3</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Fällmossa
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 26044-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams
 Humleblomster</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 944-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45666</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Fällmossa
-Rävticka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46674-2023</t>
+          <t>A 20064-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45198</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46674-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45198</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20064-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16173-2022</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44668</v>
+        <v>45167</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 16173-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44974</v>
+        <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3085,13 +3085,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>14.1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3134,7 +3129,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3148,10 +3143,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45209</v>
+        <v>45230</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3164,7 +3159,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3207,7 +3202,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3221,10 +3216,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45264</v>
+        <v>45397</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3232,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3280,7 +3275,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45264</v>
+        <v>44662</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3310,7 +3305,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3353,7 +3348,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,10 +3362,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44844</v>
+        <v>45341</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3378,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3426,7 +3421,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3440,10 +3435,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45665</v>
+        <v>44760</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3451,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3499,7 +3494,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3513,10 +3508,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45184</v>
+        <v>45385</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3524,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3567,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3581,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45358</v>
+        <v>44754</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3601,8 +3596,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45628</v>
+        <v>45379</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.2</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44966</v>
+        <v>45230</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45660</v>
+        <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45290</v>
+        <v>45264</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45588</v>
+        <v>45264</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45547</v>
+        <v>46078</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4039,13 +4039,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4088,7 +4083,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4102,10 +4097,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46010</v>
+        <v>46078</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4118,7 +4113,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4161,7 +4156,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4175,10 +4170,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44917</v>
+        <v>46078</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4191,7 +4186,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10.9</v>
+        <v>0.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4234,7 +4229,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4248,10 +4243,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44494</v>
+        <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4264,7 +4259,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4307,7 +4302,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4321,10 +4316,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46030</v>
+        <v>44582</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4337,7 +4332,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4380,7 +4375,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4394,10 +4389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44886</v>
+        <v>44582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4409,13 +4404,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>19.4</v>
+        <v>5.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4458,7 +4448,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4472,10 +4462,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46030</v>
+        <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4488,7 +4478,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4531,7 +4521,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4545,10 +4535,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46037</v>
+        <v>44886</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4560,8 +4550,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4604,7 +4599,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4618,10 +4613,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45264</v>
+        <v>44781</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4634,7 +4629,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4677,7 +4672,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4691,10 +4686,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45919</v>
+        <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4707,7 +4702,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4750,7 +4745,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4764,10 +4759,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45232</v>
+        <v>46078</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4780,7 +4775,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4823,7 +4818,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4837,10 +4832,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45919</v>
+        <v>46106</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4852,8 +4847,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45919</v>
+        <v>45699</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45919</v>
+        <v>44526</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5042,7 +5042,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45933</v>
+        <v>44671</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5115,7 +5115,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46078</v>
+        <v>45919</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46078</v>
+        <v>45919</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5275,10 +5275,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46078</v>
+        <v>45919</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5334,7 +5334,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45883</v>
+        <v>44974</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5363,8 +5363,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>14.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5407,7 +5412,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5421,10 +5426,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45883</v>
+        <v>45919</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5437,7 +5442,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>9.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5480,7 +5485,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5494,10 +5499,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44671</v>
+        <v>45560</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5510,7 +5515,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5553,7 +5558,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5567,10 +5572,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45694</v>
+        <v>45448</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5583,7 +5588,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5626,7 +5631,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5640,10 +5645,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44582</v>
+        <v>45358</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5656,7 +5661,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5699,7 +5704,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5713,10 +5718,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44582</v>
+        <v>46122</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5729,7 +5734,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5772,7 +5777,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5786,10 +5791,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45000</v>
+        <v>44887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5802,7 +5807,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5845,7 +5850,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5859,10 +5864,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44663</v>
+        <v>46128</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5875,7 +5880,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5918,7 +5923,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5932,10 +5937,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44516</v>
+        <v>45933</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,7 +5953,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5991,7 +5996,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6005,10 +6010,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45167</v>
+        <v>46132</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,7 +6026,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>7.1</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6064,7 +6069,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6074,14 +6079,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45512</v>
+        <v>45740</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,7 +6099,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6137,7 +6142,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6151,10 +6156,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44830</v>
+        <v>45952</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6167,7 +6172,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6210,7 +6215,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 50007-2021</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6224,10 +6229,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46078</v>
+        <v>44456</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6239,8 +6244,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6283,7 +6293,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6297,10 +6307,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45952</v>
+        <v>45758</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6313,7 +6323,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6356,7 +6366,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6370,10 +6380,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46106</v>
+        <v>45006</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6385,13 +6395,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6434,7 +6439,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6448,10 +6453,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45965</v>
+        <v>45741</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6463,13 +6468,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>11.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6522,14 +6522,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46122</v>
+        <v>45187</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6541,8 +6541,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6585,7 +6590,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6599,10 +6604,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45962</v>
+        <v>45789</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6615,7 +6620,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6658,7 +6663,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6672,10 +6677,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46128</v>
+        <v>45962</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6688,7 +6693,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6731,7 +6736,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6745,10 +6750,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45593</v>
+        <v>45965</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6760,8 +6765,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6804,7 +6814,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6818,10 +6828,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45614</v>
+        <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6833,13 +6843,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6882,7 +6887,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6896,10 +6901,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46132</v>
+        <v>44909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6912,7 +6917,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6955,7 +6960,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6969,10 +6974,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45397</v>
+        <v>45000</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6985,7 +6990,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7028,7 +7033,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7045,7 +7050,7 @@
         <v>44909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7101,7 +7106,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7115,10 +7120,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45983</v>
+        <v>44978</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7131,7 +7136,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.2</v>
+        <v>3.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7174,7 +7179,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7184,14 +7189,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45264</v>
+        <v>45512</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7204,7 +7209,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7247,7 +7252,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7261,10 +7266,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45983</v>
+        <v>45986</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7276,8 +7281,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7320,7 +7330,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7334,10 +7344,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44909</v>
+        <v>45983</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7350,7 +7360,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7393,7 +7403,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7407,10 +7417,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45986</v>
+        <v>45983</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7422,13 +7432,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>7.7</v>
+        <v>13.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7471,7 +7476,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7485,10 +7490,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45758</v>
+        <v>44790</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7501,7 +7506,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7544,7 +7549,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7558,10 +7563,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45740</v>
+        <v>45999</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7573,8 +7578,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7617,7 +7627,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7631,10 +7641,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45999</v>
+        <v>45243</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7648,11 +7658,11 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>8.6</v>
+        <v>3.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7695,7 +7705,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7709,10 +7719,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45741</v>
+        <v>46154</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7725,7 +7735,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7768,7 +7778,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7782,10 +7792,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45789</v>
+        <v>46154</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7798,7 +7808,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7841,7 +7851,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7855,10 +7865,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44526</v>
+        <v>46154</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7871,7 +7881,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.2</v>
+        <v>13.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7914,7 +7924,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7928,10 +7938,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45111</v>
+        <v>45665</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7944,7 +7954,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7987,7 +7997,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8001,10 +8011,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44760</v>
+        <v>44844</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8017,7 +8027,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8060,7 +8070,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8074,10 +8084,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45679</v>
+        <v>45817</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8090,7 +8100,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8133,7 +8143,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8147,10 +8157,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44754</v>
+        <v>46010</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8162,13 +8172,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>8.800000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8211,7 +8216,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8225,10 +8230,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45817</v>
+        <v>46157</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8241,7 +8246,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8284,7 +8289,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8298,10 +8303,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46154</v>
+        <v>45111</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8314,7 +8319,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8357,7 +8362,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8371,10 +8376,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45368</v>
+        <v>46157</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8387,7 +8392,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8430,7 +8435,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8444,10 +8449,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8460,7 +8465,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>13.6</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8503,7 +8508,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8517,10 +8522,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46154</v>
+        <v>45614</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8532,8 +8537,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8576,7 +8586,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8590,10 +8600,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8606,7 +8616,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8649,7 +8659,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8663,10 +8673,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8679,7 +8689,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8722,7 +8732,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8736,10 +8746,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46157</v>
+        <v>45593</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8752,7 +8762,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8795,7 +8805,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8809,10 +8819,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46161</v>
+        <v>44634</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8825,7 +8835,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8868,7 +8878,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8882,10 +8892,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46161</v>
+        <v>46030</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8898,7 +8908,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8941,7 +8951,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8955,10 +8965,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46169</v>
+        <v>46030</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8971,7 +8981,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9014,7 +9024,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9028,10 +9038,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46177</v>
+        <v>45232</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9044,7 +9054,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9087,7 +9097,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9101,10 +9111,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46177</v>
+        <v>46037</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9117,7 +9127,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>9.1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9160,7 +9170,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9174,10 +9184,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46177</v>
+        <v>46169</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9190,7 +9200,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9233,7 +9243,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9247,10 +9257,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46177</v>
+        <v>44960</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9262,8 +9272,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>14.8</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9306,7 +9321,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9320,10 +9335,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9336,7 +9351,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9379,7 +9394,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9393,10 +9408,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46195</v>
+        <v>46177</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9408,13 +9423,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9457,7 +9467,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9471,10 +9481,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46204</v>
+        <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9487,7 +9497,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9530,7 +9540,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9544,10 +9554,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46206</v>
+        <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9560,7 +9570,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9603,7 +9613,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9617,10 +9627,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46206</v>
+        <v>44917</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9633,7 +9643,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>10.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9676,7 +9686,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9690,10 +9700,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46206</v>
+        <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9706,7 +9716,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9749,7 +9759,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9763,10 +9773,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46206</v>
+        <v>45092</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9779,7 +9789,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9822,7 +9832,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9836,10 +9846,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46206</v>
+        <v>45264</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9852,7 +9862,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9895,7 +9905,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9909,10 +9919,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46251</v>
+        <v>45747</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9924,13 +9934,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>6.7</v>
+        <v>1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9973,7 +9978,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9987,10 +9992,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46206</v>
+        <v>44909</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10003,7 +10008,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10046,7 +10051,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10060,10 +10065,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45092</v>
+        <v>44909</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10076,7 +10081,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10119,7 +10124,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10133,10 +10138,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46169</v>
+        <v>45109</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10149,7 +10154,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.6</v>
+        <v>5.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10192,7 +10197,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10206,10 +10211,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45560</v>
+        <v>46195</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10221,8 +10226,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10265,7 +10275,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10279,10 +10289,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46169</v>
+        <v>44994</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10295,7 +10305,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10338,7 +10348,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10352,10 +10362,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46265</v>
+        <v>44494</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10368,7 +10378,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10411,7 +10421,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10425,10 +10435,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44662</v>
+        <v>45408</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10441,7 +10451,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10484,7 +10494,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10498,10 +10508,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46169</v>
+        <v>45012</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10514,7 +10524,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10557,7 +10567,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10571,10 +10581,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45456</v>
+        <v>45264</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10587,7 +10597,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10630,7 +10640,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10644,10 +10654,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45264</v>
+        <v>45145</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10660,7 +10670,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10703,7 +10713,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10717,10 +10727,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45385</v>
+        <v>44516</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10733,7 +10743,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10776,7 +10786,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10790,10 +10800,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45012</v>
+        <v>46204</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10806,7 +10816,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10849,7 +10859,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10863,10 +10873,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44668</v>
+        <v>45429</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10879,7 +10889,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10922,7 +10932,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10936,10 +10946,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45230</v>
+        <v>45679</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10952,7 +10962,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10995,7 +11005,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11009,10 +11019,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45429</v>
+        <v>46206</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11068,7 +11078,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11082,10 +11092,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46275</v>
+        <v>46251</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11097,8 +11107,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11141,7 +11156,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11155,10 +11170,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11171,7 +11186,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11214,7 +11229,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11228,10 +11243,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46275</v>
+        <v>44622</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11244,7 +11259,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11287,7 +11302,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11301,10 +11316,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46275</v>
+        <v>44602</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11317,7 +11332,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11360,7 +11375,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11374,10 +11389,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11390,7 +11405,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11433,7 +11448,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11443,14 +11458,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11463,7 +11478,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11506,7 +11521,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11520,10 +11535,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45714</v>
+        <v>46206</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11536,7 +11551,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11579,7 +11594,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11593,10 +11608,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45608</v>
+        <v>45456</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11609,7 +11624,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11652,7 +11667,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11666,10 +11681,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46277</v>
+        <v>46206</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11682,7 +11697,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11725,7 +11740,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11739,10 +11754,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46277</v>
+        <v>46169</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11755,7 +11770,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11798,7 +11813,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11812,10 +11827,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45434</v>
+        <v>44830</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11828,7 +11843,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11871,7 +11886,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11885,10 +11900,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44602</v>
+        <v>45608</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11901,7 +11916,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11944,7 +11959,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11958,10 +11973,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45706</v>
+        <v>45434</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11974,7 +11989,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12017,7 +12032,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12031,10 +12046,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44781</v>
+        <v>45706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12047,7 +12062,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12090,7 +12105,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12104,10 +12119,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44512</v>
+        <v>45209</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12120,7 +12135,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12163,7 +12178,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12177,10 +12192,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45006</v>
+        <v>44988</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12193,7 +12208,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12236,7 +12251,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12250,10 +12265,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44978</v>
+        <v>45194</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12266,7 +12281,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12309,7 +12324,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12323,10 +12338,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44960</v>
+        <v>44668</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12338,13 +12353,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>14.8</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12387,7 +12397,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12401,10 +12411,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45699</v>
+        <v>46265</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12417,7 +12427,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12460,7 +12470,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12474,10 +12484,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45379</v>
+        <v>45368</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12490,7 +12500,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12533,7 +12543,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12547,10 +12557,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44988</v>
+        <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12563,7 +12573,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12606,7 +12616,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12620,10 +12630,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45243</v>
+        <v>46169</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12635,13 +12645,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12684,7 +12689,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12698,10 +12703,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45109</v>
+        <v>44530</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12714,7 +12719,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12757,7 +12762,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12771,10 +12776,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45408</v>
+        <v>45714</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12787,7 +12792,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.2</v>
+        <v>0.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12830,7 +12835,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12840,14 +12845,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44622</v>
+        <v>46275</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12860,7 +12865,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.5</v>
+        <v>10.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12920,7 +12925,7 @@
         <v>45159</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12976,7 +12981,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12990,10 +12995,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44790</v>
+        <v>45699</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13006,7 +13011,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13049,7 +13054,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13063,10 +13068,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44887</v>
+        <v>45694</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13079,7 +13084,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13122,7 +13127,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13136,10 +13141,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44886</v>
+        <v>46275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13151,13 +13156,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13200,7 +13200,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13214,10 +13214,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45230</v>
+        <v>46275</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13273,7 +13273,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13287,10 +13287,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44634</v>
+        <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13346,7 +13346,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13360,10 +13360,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45194</v>
+        <v>46275</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13433,10 +13433,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45145</v>
+        <v>46275</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13506,10 +13506,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44909</v>
+        <v>45253</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13565,7 +13565,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13579,10 +13579,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44909</v>
+        <v>46277</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13595,7 +13595,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13638,7 +13638,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13648,14 +13648,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45187</v>
+        <v>45615</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13667,13 +13667,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13716,7 +13711,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13730,10 +13725,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45699</v>
+        <v>46277</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13746,7 +13741,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13789,7 +13784,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13803,10 +13798,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44994</v>
+        <v>45012</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13819,7 +13814,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13862,7 +13857,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13876,10 +13871,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45253</v>
+        <v>45629</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13892,7 +13887,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13935,7 +13930,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13949,10 +13944,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45341</v>
+        <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13965,7 +13960,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14008,7 +14003,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 50007-2021</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14022,10 +14017,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44456</v>
+        <v>45290</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14037,13 +14032,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14086,7 +14076,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14100,10 +14090,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44530</v>
+        <v>44966</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14116,7 +14106,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14159,7 +14149,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14173,10 +14163,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45448</v>
+        <v>45588</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14189,7 +14179,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14232,7 +14222,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14246,10 +14236,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45747</v>
+        <v>45660</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14262,7 +14252,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14305,7 +14295,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14319,10 +14309,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14335,7 +14325,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14378,7 +14368,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14392,10 +14382,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45615</v>
+        <v>45184</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14451,7 +14441,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14465,10 +14455,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45012</v>
+        <v>45547</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14480,8 +14470,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14524,7 +14519,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14538,10 +14533,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45629</v>
+        <v>44886</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14553,8 +14548,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.8</v>
+        <v>19.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 944-2025</t>
+          <t>A 26044-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45666</v>
+        <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams
+Humleblomster</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 944-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45666</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Fällmossa
 Rävticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 26044-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams
-Humleblomster</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 69169-2021</t>
+          <t>A 16116-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44530</v>
+        <v>44665</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16116-2022</t>
+          <t>A 69169-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44665</v>
+        <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 16173-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45167</v>
+        <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16173-2022</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44668</v>
+        <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3085,8 +3085,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>14.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3129,7 +3134,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3143,10 +3148,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45230</v>
+        <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3164,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3202,7 +3207,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3216,10 +3221,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45397</v>
+        <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3237,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3275,7 +3280,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44662</v>
+        <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3310,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3348,7 +3353,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3362,10 +3367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45341</v>
+        <v>44844</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3378,7 +3383,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3421,7 +3426,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3435,10 +3440,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44760</v>
+        <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3451,7 +3456,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3494,7 +3499,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3508,10 +3513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45385</v>
+        <v>45358</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3524,7 +3529,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3567,7 +3572,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3581,10 +3586,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44754</v>
+        <v>44917</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3596,13 +3601,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>8.800000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45379</v>
+        <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45230</v>
+        <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3747,8 +3747,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3796,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44663</v>
+        <v>46030</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3826,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3881,7 +3886,7 @@
         <v>45264</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3937,7 +3942,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3956,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45264</v>
+        <v>46030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3972,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4010,7 +4015,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4024,10 +4029,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46078</v>
+        <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4039,8 +4044,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>19.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4083,7 +4093,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,10 +4107,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46078</v>
+        <v>45232</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4123,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4156,7 +4166,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4170,10 +4180,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46078</v>
+        <v>45919</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4186,7 +4196,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4229,7 +4239,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4243,10 +4253,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45883</v>
+        <v>45919</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4269,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4302,7 +4312,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4316,10 +4326,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44582</v>
+        <v>45919</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4342,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4375,7 +4385,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4389,10 +4399,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44582</v>
+        <v>45919</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4405,7 +4415,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4448,7 +4458,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4462,10 +4472,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45883</v>
+        <v>46037</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4488,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4521,7 +4531,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4535,10 +4545,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44886</v>
+        <v>44671</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4550,13 +4560,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4599,7 +4604,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4613,10 +4618,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44781</v>
+        <v>45694</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4629,7 +4634,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4672,7 +4677,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4686,10 +4691,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44512</v>
+        <v>45933</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4702,7 +4707,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4745,7 +4750,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4759,10 +4764,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46078</v>
+        <v>44582</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4775,7 +4780,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4818,7 +4823,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4832,10 +4837,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46106</v>
+        <v>44582</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4847,13 +4852,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45699</v>
+        <v>45000</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44526</v>
+        <v>44663</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5042,7 +5042,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44671</v>
+        <v>44516</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5115,7 +5115,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45919</v>
+        <v>45883</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45919</v>
+        <v>45167</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5271,14 +5271,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45919</v>
+        <v>45512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5334,7 +5334,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5348,10 +5348,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44974</v>
+        <v>45883</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5363,13 +5363,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>14.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5412,7 +5407,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5426,10 +5421,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45919</v>
+        <v>44830</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5442,7 +5437,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5485,7 +5480,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5499,10 +5494,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45560</v>
+        <v>45952</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5515,7 +5510,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>6.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5558,7 +5553,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5572,10 +5567,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45448</v>
+        <v>45965</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5587,8 +5582,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.6</v>
+        <v>11.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5631,7 +5631,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45358</v>
+        <v>45962</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5704,7 +5704,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46122</v>
+        <v>45593</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5777,7 +5777,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5791,10 +5791,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44887</v>
+        <v>45614</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5806,8 +5806,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5850,7 +5855,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5864,10 +5869,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46128</v>
+        <v>45397</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5880,7 +5885,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5923,7 +5928,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5937,10 +5942,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45933</v>
+        <v>44909</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5996,7 +6001,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6010,10 +6015,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46132</v>
+        <v>45264</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6026,7 +6031,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6069,7 +6074,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6083,10 +6088,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45740</v>
+        <v>45983</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6099,7 +6104,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.8</v>
+        <v>13.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6142,7 +6147,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6156,10 +6161,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45952</v>
+        <v>46078</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6172,7 +6177,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6215,7 +6220,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50007-2021</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6229,10 +6234,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44456</v>
+        <v>46078</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6244,13 +6249,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>6.5</v>
+        <v>0.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45758</v>
+        <v>45983</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6380,10 +6380,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45006</v>
+        <v>45986</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6395,8 +6395,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6439,7 +6444,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6453,10 +6458,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45741</v>
+        <v>46078</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6469,7 +6474,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6512,7 +6517,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6522,14 +6527,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45187</v>
+        <v>45999</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6543,11 +6548,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>8.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6590,7 +6595,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6604,10 +6609,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45789</v>
+        <v>46010</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6620,7 +6625,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6663,7 +6668,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6677,10 +6682,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45962</v>
+        <v>44526</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6693,7 +6698,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6736,7 +6741,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6750,10 +6755,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45965</v>
+        <v>45111</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6765,13 +6770,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>11.6</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6814,7 +6814,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6828,10 +6828,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45264</v>
+        <v>44760</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6887,7 +6887,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6901,10 +6901,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44909</v>
+        <v>45679</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6974,10 +6974,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45000</v>
+        <v>46078</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7033,7 +7033,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44909</v>
+        <v>46106</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7062,8 +7062,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7106,7 +7111,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7120,10 +7125,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44978</v>
+        <v>44754</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7135,8 +7140,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7179,7 +7189,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7189,14 +7199,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45512</v>
+        <v>45368</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7209,7 +7219,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7252,7 +7262,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7266,10 +7276,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45986</v>
+        <v>46122</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7281,13 +7291,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7330,7 +7335,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7344,10 +7349,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45983</v>
+        <v>46128</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7360,7 +7365,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7403,7 +7408,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7417,10 +7422,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45983</v>
+        <v>46132</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7433,7 +7438,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>13.2</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7476,7 +7481,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7490,10 +7495,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44790</v>
+        <v>45092</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7506,7 +7511,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7549,7 +7554,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7563,10 +7568,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45999</v>
+        <v>45560</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7578,13 +7583,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>8.6</v>
+        <v>2.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7627,7 +7627,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7641,10 +7641,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45243</v>
+        <v>44909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7656,13 +7656,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7705,7 +7700,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7719,10 +7714,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46154</v>
+        <v>44662</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7735,7 +7730,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7778,7 +7773,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7792,10 +7787,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46154</v>
+        <v>45758</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7808,7 +7803,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7851,7 +7846,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7865,10 +7860,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46154</v>
+        <v>45740</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7881,7 +7876,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>13.6</v>
+        <v>4.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7924,7 +7919,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7938,10 +7933,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45665</v>
+        <v>45456</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7954,7 +7949,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7997,7 +7992,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8011,10 +8006,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44844</v>
+        <v>45741</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8027,7 +8022,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8070,7 +8065,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8084,10 +8079,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45817</v>
+        <v>45264</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8100,7 +8095,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8143,7 +8138,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8157,10 +8152,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46010</v>
+        <v>45385</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8173,7 +8168,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8216,7 +8211,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8230,10 +8225,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46157</v>
+        <v>45012</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8246,7 +8241,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8289,7 +8284,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8303,10 +8298,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45111</v>
+        <v>44668</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8319,7 +8314,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8362,7 +8357,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8376,10 +8371,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46157</v>
+        <v>45789</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8392,7 +8387,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8435,7 +8430,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8449,10 +8444,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46157</v>
+        <v>45230</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8465,7 +8460,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8508,7 +8503,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8522,10 +8517,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45614</v>
+        <v>45429</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8537,13 +8532,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8586,7 +8576,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8600,10 +8590,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46161</v>
+        <v>45714</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8616,7 +8606,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8659,7 +8649,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8673,10 +8663,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46161</v>
+        <v>45608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8689,7 +8679,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8732,7 +8722,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8746,10 +8736,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45593</v>
+        <v>45434</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8762,7 +8752,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8805,7 +8795,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8819,10 +8809,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44634</v>
+        <v>44602</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8835,7 +8825,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8878,7 +8868,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8892,10 +8882,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46030</v>
+        <v>45706</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8908,7 +8898,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8951,7 +8941,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8965,10 +8955,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46030</v>
+        <v>45817</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8981,7 +8971,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9024,7 +9014,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9038,10 +9028,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45232</v>
+        <v>46154</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9054,7 +9044,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9097,7 +9087,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9111,10 +9101,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46037</v>
+        <v>46154</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9127,7 +9117,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>9.1</v>
+        <v>13.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9170,7 +9160,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9184,10 +9174,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46169</v>
+        <v>46154</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9200,7 +9190,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9243,7 +9233,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9257,10 +9247,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44960</v>
+        <v>46157</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9272,13 +9262,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>14.8</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9321,7 +9306,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9335,10 +9320,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46177</v>
+        <v>46157</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9351,7 +9336,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9394,7 +9379,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9408,10 +9393,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46177</v>
+        <v>46157</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9467,7 +9452,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9481,10 +9466,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46177</v>
+        <v>46161</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9497,7 +9482,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9540,7 +9525,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9554,10 +9539,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46177</v>
+        <v>46161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9570,7 +9555,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9613,7 +9598,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9627,10 +9612,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44917</v>
+        <v>44781</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9643,7 +9628,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>10.9</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9686,7 +9671,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9700,10 +9685,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46181</v>
+        <v>44512</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9716,7 +9701,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9759,7 +9744,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9773,10 +9758,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45092</v>
+        <v>46169</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9789,7 +9774,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9832,7 +9817,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9846,10 +9831,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45264</v>
+        <v>46177</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9862,7 +9847,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9905,7 +9890,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9919,10 +9904,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45747</v>
+        <v>46177</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9935,7 +9920,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9978,7 +9963,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9992,10 +9977,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44909</v>
+        <v>45006</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10008,7 +9993,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10051,7 +10036,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10065,10 +10050,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44909</v>
+        <v>46177</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10081,7 +10066,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10124,7 +10109,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10138,10 +10123,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45109</v>
+        <v>46177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10154,7 +10139,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.9</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10197,7 +10182,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10211,10 +10196,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46195</v>
+        <v>44978</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10226,13 +10211,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10275,7 +10255,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10289,10 +10269,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>44994</v>
+        <v>46181</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10305,7 +10285,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10348,7 +10328,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10362,10 +10342,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44494</v>
+        <v>44960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10377,8 +10357,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>14.8</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10421,7 +10406,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10435,10 +10420,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45408</v>
+        <v>45699</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10451,7 +10436,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10494,7 +10479,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10508,10 +10493,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45012</v>
+        <v>45379</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10524,7 +10509,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10567,7 +10552,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10581,10 +10566,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45264</v>
+        <v>44988</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10597,7 +10582,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10640,7 +10625,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10654,10 +10639,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45145</v>
+        <v>46195</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10669,8 +10654,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10713,7 +10703,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10727,10 +10717,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44516</v>
+        <v>45243</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10742,8 +10732,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10786,7 +10781,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10800,10 +10795,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46204</v>
+        <v>45109</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10816,7 +10811,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10859,7 +10854,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10873,10 +10868,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45429</v>
+        <v>45408</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10889,7 +10884,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10932,7 +10927,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10946,10 +10941,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45679</v>
+        <v>46204</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10962,7 +10957,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11005,7 +11000,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11019,10 +11014,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46206</v>
+        <v>44622</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11035,7 +11030,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11078,7 +11073,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11092,10 +11087,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46251</v>
+        <v>46206</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11107,13 +11102,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.7</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11156,7 +11146,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11173,7 +11163,7 @@
         <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11186,7 +11176,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11229,7 +11219,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11243,10 +11233,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44622</v>
+        <v>46206</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11259,7 +11249,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11302,7 +11292,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11316,10 +11306,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44602</v>
+        <v>46206</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11375,7 +11365,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11389,10 +11379,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46206</v>
+        <v>45159</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11405,7 +11395,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>7.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11448,7 +11438,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11465,7 +11455,7 @@
         <v>46206</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11521,7 +11511,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11535,10 +11525,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46206</v>
+        <v>46251</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11550,8 +11540,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>6.7</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11594,7 +11589,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11608,10 +11603,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45456</v>
+        <v>46206</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11624,7 +11619,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>7.5</v>
+        <v>1.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11667,7 +11662,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11681,10 +11676,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46206</v>
+        <v>44790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11697,7 +11692,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11740,7 +11735,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11754,10 +11749,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46169</v>
+        <v>44887</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11770,7 +11765,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11813,7 +11808,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11827,10 +11822,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44830</v>
+        <v>44886</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11840,6 +11835,11 @@
       <c r="G149" t="inlineStr">
         <is>
           <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -11886,7 +11886,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11900,10 +11900,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45608</v>
+        <v>45230</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11959,7 +11959,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11973,10 +11973,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45434</v>
+        <v>46169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12032,7 +12032,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12046,10 +12046,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45706</v>
+        <v>44634</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12105,7 +12105,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12119,10 +12119,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45209</v>
+        <v>45194</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12178,7 +12178,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12192,10 +12192,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44988</v>
+        <v>45145</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12251,7 +12251,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12265,10 +12265,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45194</v>
+        <v>44909</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12324,7 +12324,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12338,10 +12338,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44668</v>
+        <v>44909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12397,7 +12397,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12411,10 +12411,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46265</v>
+        <v>46169</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12484,10 +12484,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45368</v>
+        <v>46265</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12543,7 +12543,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12553,14 +12553,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46169</v>
+        <v>45187</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12570,6 +12570,11 @@
       <c r="G159" t="inlineStr">
         <is>
           <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -12633,7 +12638,7 @@
         <v>46169</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12689,7 +12694,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12703,10 +12708,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44530</v>
+        <v>45699</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12719,7 +12724,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12762,7 +12767,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12776,10 +12781,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45714</v>
+        <v>44994</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12792,7 +12797,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>3.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12835,7 +12840,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12845,14 +12850,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46275</v>
+        <v>45253</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12865,7 +12870,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>10.2</v>
+        <v>4.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12908,7 +12913,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12922,10 +12927,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45159</v>
+        <v>45341</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12938,7 +12943,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>7.3</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12981,7 +12986,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12995,10 +13000,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45699</v>
+        <v>46275</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13011,7 +13016,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13054,7 +13059,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 50007-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13068,10 +13073,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45694</v>
+        <v>44456</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13083,8 +13088,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13127,7 +13137,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13141,10 +13151,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46275</v>
+        <v>44530</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13157,7 +13167,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13200,7 +13210,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13217,7 +13227,7 @@
         <v>46275</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13273,7 +13283,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13287,10 +13297,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46275</v>
+        <v>45448</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13303,7 +13313,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13346,7 +13356,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13363,7 +13373,7 @@
         <v>46275</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13376,7 +13386,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13419,7 +13429,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13436,7 +13446,7 @@
         <v>46275</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13449,7 +13459,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13492,7 +13502,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13506,10 +13516,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45253</v>
+        <v>46275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13522,7 +13532,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13565,7 +13575,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13575,14 +13585,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46277</v>
+        <v>46275</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13595,7 +13605,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>10.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13638,7 +13648,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13652,10 +13662,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45615</v>
+        <v>45747</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13668,7 +13678,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13711,7 +13721,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13728,7 +13738,7 @@
         <v>46277</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13741,7 +13751,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13784,7 +13794,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13798,10 +13808,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45012</v>
+        <v>46277</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13814,7 +13824,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13857,7 +13867,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13871,10 +13881,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45629</v>
+        <v>45632</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13887,7 +13897,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13930,7 +13940,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13944,10 +13954,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45632</v>
+        <v>45615</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13960,7 +13970,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14003,7 +14013,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14017,10 +14027,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45290</v>
+        <v>45012</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14033,7 +14043,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14076,7 +14086,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14090,10 +14100,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44966</v>
+        <v>45629</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14106,7 +14116,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14149,7 +14159,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14163,10 +14173,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45588</v>
+        <v>45184</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14179,7 +14189,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14222,7 +14232,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14236,10 +14246,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45660</v>
+        <v>45628</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14252,7 +14262,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14295,7 +14305,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14309,10 +14319,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45628</v>
+        <v>44966</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14325,7 +14335,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14368,7 +14378,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14382,10 +14392,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45184</v>
+        <v>45660</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14398,7 +14408,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14441,7 +14451,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14455,10 +14465,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45547</v>
+        <v>45290</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14470,13 +14480,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14519,7 +14524,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14533,10 +14538,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44886</v>
+        <v>45588</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,13 +14553,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>19.4</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE186"/>
+  <dimension ref="A1:AE185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26044-2025</t>
+          <t>A 944-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45804</v>
+        <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,17 +1088,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>31.3</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Fällmossa
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 26044-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams
 Humleblomster</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 944-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45666</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Fällmossa
-Rävticka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46674-2023</t>
+          <t>A 20064-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45198</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46674-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45198</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20064-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44665</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44974</v>
+        <v>44760</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3085,13 +3085,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>14.1</v>
+        <v>0.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3134,7 +3129,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3148,10 +3143,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45209</v>
+        <v>45341</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3164,7 +3159,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3207,7 +3202,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3221,10 +3216,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45264</v>
+        <v>45397</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3232,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3280,7 +3275,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3294,10 +3289,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45264</v>
+        <v>45385</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3310,7 +3305,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3353,7 +3348,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,10 +3362,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44844</v>
+        <v>45379</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3378,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3426,7 +3421,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3440,10 +3435,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45665</v>
+        <v>44886</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3455,8 +3450,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45358</v>
+        <v>44582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44917</v>
+        <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.9</v>
+        <v>5.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44494</v>
+        <v>45230</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45547</v>
+        <v>44512</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3747,13 +3747,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3796,7 +3791,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3810,10 +3805,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46030</v>
+        <v>44526</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3826,7 +3821,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3869,7 +3864,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3883,10 +3878,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45264</v>
+        <v>44974</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3898,8 +3893,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>14.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3942,7 +3942,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46030</v>
+        <v>44671</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44886</v>
+        <v>45699</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4044,13 +4044,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>19.4</v>
+        <v>5.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4093,7 +4088,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4107,10 +4102,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45232</v>
+        <v>45560</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4123,7 +4118,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4166,7 +4161,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4180,10 +4175,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45919</v>
+        <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4195,8 +4190,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.2</v>
+        <v>19.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4253,10 +4253,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45919</v>
+        <v>45358</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45919</v>
+        <v>45883</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4385,7 +4385,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45919</v>
+        <v>45883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4472,10 +4472,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46037</v>
+        <v>44887</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4531,7 +4531,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44671</v>
+        <v>46078</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4604,7 +4604,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45694</v>
+        <v>46078</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4677,7 +4677,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45933</v>
+        <v>46078</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4750,7 +4750,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44582</v>
+        <v>45006</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4823,7 +4823,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4833,14 +4833,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44582</v>
+        <v>45187</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4852,8 +4852,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4896,7 +4901,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4910,10 +4915,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45000</v>
+        <v>46078</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4926,7 +4931,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4969,7 +4974,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4983,10 +4988,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44663</v>
+        <v>45264</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4999,7 +5004,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5042,7 +5047,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5056,10 +5061,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44516</v>
+        <v>44909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5072,7 +5077,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5115,7 +5120,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5129,10 +5134,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45883</v>
+        <v>46106</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5144,8 +5149,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5188,7 +5198,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5202,10 +5212,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45167</v>
+        <v>45000</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5218,7 +5228,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5261,7 +5271,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5271,14 +5281,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45512</v>
+        <v>46122</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5291,7 +5301,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>6.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5334,7 +5344,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5344,14 +5354,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45883</v>
+        <v>45512</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5364,7 +5374,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5407,7 +5417,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5421,10 +5431,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44830</v>
+        <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5437,7 +5447,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5480,7 +5490,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5494,10 +5504,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45952</v>
+        <v>46132</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5510,7 +5520,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5553,7 +5563,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5567,10 +5577,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45965</v>
+        <v>45740</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5582,13 +5592,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>11.6</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5631,7 +5636,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5645,10 +5650,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45962</v>
+        <v>45758</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5661,7 +5666,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5704,7 +5709,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5718,10 +5723,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45593</v>
+        <v>45243</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5733,8 +5738,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5777,7 +5787,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5791,10 +5801,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45614</v>
+        <v>45919</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5806,13 +5816,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5855,7 +5860,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5869,10 +5874,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45397</v>
+        <v>45741</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5885,7 +5890,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5928,7 +5933,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5942,10 +5947,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44909</v>
+        <v>45919</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5958,7 +5963,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6001,7 +6006,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6015,10 +6020,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45264</v>
+        <v>45919</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6031,7 +6036,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.3</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6074,7 +6079,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6088,10 +6093,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45983</v>
+        <v>45919</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6104,7 +6109,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>13.2</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6147,7 +6152,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6161,10 +6166,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46078</v>
+        <v>45665</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6177,7 +6182,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6220,7 +6225,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6234,10 +6239,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46078</v>
+        <v>44844</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6250,7 +6255,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6293,7 +6298,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6307,10 +6312,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45983</v>
+        <v>45789</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6323,7 +6328,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6366,7 +6371,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6380,10 +6385,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45986</v>
+        <v>45111</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6395,13 +6400,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6444,7 +6444,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46078</v>
+        <v>44909</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45999</v>
+        <v>44917</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6546,13 +6546,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6595,7 +6590,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6609,10 +6604,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46010</v>
+        <v>45933</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6625,7 +6620,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6668,7 +6663,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6682,10 +6677,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44526</v>
+        <v>46154</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6698,7 +6693,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6741,7 +6736,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6755,10 +6750,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45111</v>
+        <v>45092</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6771,7 +6766,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6814,7 +6809,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6828,10 +6823,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44760</v>
+        <v>45264</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6844,7 +6839,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6887,7 +6882,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6901,10 +6896,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45679</v>
+        <v>46154</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6917,7 +6912,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6960,7 +6955,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6974,10 +6969,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46078</v>
+        <v>46154</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6990,7 +6985,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>13.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7033,7 +7028,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7047,10 +7042,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46106</v>
+        <v>45817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7062,13 +7057,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7111,7 +7101,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7125,10 +7115,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44754</v>
+        <v>46157</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7140,13 +7130,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7189,7 +7174,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7203,10 +7188,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45368</v>
+        <v>46157</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7219,7 +7204,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7262,7 +7247,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7276,10 +7261,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46122</v>
+        <v>45747</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7292,7 +7277,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7335,7 +7320,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7349,10 +7334,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46128</v>
+        <v>46157</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7365,7 +7350,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7408,7 +7393,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7422,10 +7407,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46132</v>
+        <v>46161</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7438,7 +7423,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7481,7 +7466,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7495,10 +7480,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45092</v>
+        <v>46161</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7511,7 +7496,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7554,7 +7539,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7568,10 +7553,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45560</v>
+        <v>44909</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7584,7 +7569,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7627,7 +7612,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7644,7 +7629,7 @@
         <v>44909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7657,7 +7642,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7700,7 +7685,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7714,10 +7699,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44662</v>
+        <v>45109</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7730,7 +7715,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7773,7 +7758,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7787,10 +7772,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45758</v>
+        <v>44994</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7803,7 +7788,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7846,7 +7831,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7860,10 +7845,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45740</v>
+        <v>46169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7876,7 +7861,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.8</v>
+        <v>1.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7919,7 +7904,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7933,10 +7918,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45456</v>
+        <v>45408</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7949,7 +7934,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7992,7 +7977,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8006,10 +7991,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45741</v>
+        <v>45012</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8022,7 +8007,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8082,7 +8067,7 @@
         <v>45264</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8138,7 +8123,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8152,10 +8137,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45385</v>
+        <v>46177</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8211,7 +8196,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8225,10 +8210,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45012</v>
+        <v>46177</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8241,7 +8226,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8284,7 +8269,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8298,10 +8283,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44668</v>
+        <v>46177</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8314,7 +8299,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8357,7 +8342,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8371,10 +8356,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45789</v>
+        <v>46177</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8387,7 +8372,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8430,7 +8415,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8444,10 +8429,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45230</v>
+        <v>46181</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8460,7 +8445,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8503,7 +8488,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8517,10 +8502,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45429</v>
+        <v>45952</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8533,7 +8518,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8576,7 +8561,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8590,10 +8575,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45714</v>
+        <v>44516</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8649,7 +8634,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8663,10 +8648,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45608</v>
+        <v>45429</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8679,7 +8664,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8722,7 +8707,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8736,10 +8721,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45434</v>
+        <v>45962</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8752,7 +8737,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8795,7 +8780,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8809,10 +8794,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44602</v>
+        <v>46195</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8822,6 +8807,11 @@
       <c r="G108" t="inlineStr">
         <is>
           <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -8868,7 +8858,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8882,10 +8872,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45706</v>
+        <v>44602</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8898,7 +8888,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8941,7 +8931,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8955,10 +8945,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45817</v>
+        <v>45965</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8970,8 +8960,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>11.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9014,7 +9009,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9028,10 +9023,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46154</v>
+        <v>44830</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9044,7 +9039,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9087,7 +9082,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9101,10 +9096,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46154</v>
+        <v>45608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9117,7 +9112,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>13.6</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9160,7 +9155,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9174,10 +9169,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46154</v>
+        <v>45706</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9190,7 +9185,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9233,7 +9228,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9247,10 +9242,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46157</v>
+        <v>46204</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9263,7 +9258,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9306,7 +9301,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9320,10 +9315,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46157</v>
+        <v>45986</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9335,8 +9330,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I115" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9379,7 +9379,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9393,10 +9393,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46157</v>
+        <v>45983</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9452,7 +9452,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46161</v>
+        <v>46206</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9525,7 +9525,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9539,10 +9539,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46161</v>
+        <v>46251</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9554,8 +9554,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>6.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9598,7 +9603,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9612,10 +9617,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44781</v>
+        <v>46206</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9628,7 +9633,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9671,7 +9676,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9685,10 +9690,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44512</v>
+        <v>44668</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9701,7 +9706,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9744,7 +9749,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9758,10 +9763,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46169</v>
+        <v>45983</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9774,7 +9779,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>13.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9817,7 +9822,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9831,10 +9836,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46177</v>
+        <v>45167</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9847,7 +9852,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>7.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9890,7 +9895,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9904,10 +9909,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9920,7 +9925,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9963,7 +9968,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9977,10 +9982,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45006</v>
+        <v>46206</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9993,7 +9998,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10036,7 +10041,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10050,10 +10055,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10066,7 +10071,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10109,7 +10114,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10123,10 +10128,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46177</v>
+        <v>46206</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10139,7 +10144,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10182,7 +10187,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10196,10 +10201,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44978</v>
+        <v>44662</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10212,7 +10217,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10255,7 +10260,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10269,10 +10274,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46181</v>
+        <v>46169</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10285,7 +10290,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.2</v>
+        <v>3.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10328,7 +10333,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10342,10 +10347,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44960</v>
+        <v>44754</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10359,11 +10364,11 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>14.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10406,7 +10411,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10420,10 +10425,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45699</v>
+        <v>45999</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10435,8 +10440,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10479,7 +10489,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10493,10 +10503,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45379</v>
+        <v>45230</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10509,7 +10519,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10552,7 +10562,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10566,10 +10576,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44988</v>
+        <v>44663</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10582,7 +10592,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10625,7 +10635,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10639,10 +10649,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46195</v>
+        <v>46265</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10654,13 +10664,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10703,7 +10708,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10717,10 +10722,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45243</v>
+        <v>45264</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10732,13 +10737,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10781,7 +10781,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10795,10 +10795,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45109</v>
+        <v>45264</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10854,7 +10854,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10868,10 +10868,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45408</v>
+        <v>46169</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10941,10 +10941,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46204</v>
+        <v>46169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11000,7 +11000,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11014,10 +11014,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44622</v>
+        <v>44781</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11073,7 +11073,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11087,10 +11087,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46206</v>
+        <v>45448</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11146,7 +11146,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46206</v>
+        <v>46010</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11219,7 +11219,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11229,14 +11229,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11292,7 +11292,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11306,10 +11306,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11365,7 +11365,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11379,10 +11379,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45159</v>
+        <v>46275</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11452,10 +11452,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11511,7 +11511,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11525,10 +11525,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46251</v>
+        <v>46275</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11540,13 +11540,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11589,7 +11584,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11603,10 +11598,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11619,7 +11614,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11662,7 +11657,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11676,10 +11671,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44790</v>
+        <v>46277</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11692,7 +11687,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11735,7 +11730,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11749,10 +11744,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44887</v>
+        <v>44978</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11765,7 +11760,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11808,7 +11803,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11822,10 +11817,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44886</v>
+        <v>46277</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11837,13 +11832,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11886,7 +11876,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11900,10 +11890,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45230</v>
+        <v>46030</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11916,7 +11906,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11959,7 +11949,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11973,10 +11963,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46169</v>
+        <v>46030</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11989,7 +11979,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12032,7 +12022,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12046,10 +12036,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44634</v>
+        <v>44790</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12062,7 +12052,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12105,7 +12095,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12119,10 +12109,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45194</v>
+        <v>45614</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12134,8 +12124,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12178,7 +12173,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12192,10 +12187,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45145</v>
+        <v>45593</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12208,7 +12203,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12251,7 +12246,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12265,10 +12260,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44909</v>
+        <v>44634</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12281,7 +12276,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12324,7 +12319,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12338,10 +12333,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44909</v>
+        <v>45232</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12354,7 +12349,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12397,7 +12392,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12411,10 +12406,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46169</v>
+        <v>46037</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12427,7 +12422,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12470,7 +12465,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12484,10 +12479,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46265</v>
+        <v>44960</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12499,8 +12494,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>14.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12543,7 +12543,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12553,14 +12553,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45187</v>
+        <v>44494</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12572,13 +12572,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12621,7 +12616,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12635,10 +12630,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46169</v>
+        <v>45145</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12651,7 +12646,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12694,7 +12689,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12708,10 +12703,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45699</v>
+        <v>45679</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12724,7 +12719,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12767,7 +12762,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12781,10 +12776,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44994</v>
+        <v>44622</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12797,7 +12792,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12840,7 +12835,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12854,10 +12849,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45253</v>
+        <v>45456</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12870,7 +12865,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>4.3</v>
+        <v>7.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12913,7 +12908,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12927,10 +12922,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45341</v>
+        <v>45434</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12943,7 +12938,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12986,7 +12981,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13000,10 +12995,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46275</v>
+        <v>45209</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13016,7 +13011,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13059,7 +13054,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 50007-2021</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13073,10 +13068,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44456</v>
+        <v>44988</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13088,13 +13083,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13137,7 +13127,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13151,10 +13141,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44530</v>
+        <v>45194</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13167,7 +13157,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13210,7 +13200,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13224,10 +13214,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46275</v>
+        <v>45368</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13240,7 +13230,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13283,7 +13273,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13297,10 +13287,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45448</v>
+        <v>44530</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13313,7 +13303,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13356,7 +13346,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13370,10 +13360,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46275</v>
+        <v>45714</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13386,7 +13376,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13429,7 +13419,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13443,10 +13433,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46275</v>
+        <v>45159</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13459,7 +13449,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13502,7 +13492,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13516,10 +13506,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46275</v>
+        <v>45699</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13532,7 +13522,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13575,7 +13565,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13585,14 +13575,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46275</v>
+        <v>45694</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13605,7 +13595,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>10.2</v>
+        <v>0.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13648,7 +13638,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13662,10 +13652,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45747</v>
+        <v>45253</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13678,7 +13668,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13721,7 +13711,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13735,10 +13725,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46277</v>
+        <v>45615</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13751,7 +13741,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13794,7 +13784,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13808,10 +13798,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46277</v>
+        <v>45012</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13824,7 +13814,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13867,7 +13857,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13881,10 +13871,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45632</v>
+        <v>45629</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13897,7 +13887,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13940,7 +13930,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13954,10 +13944,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45615</v>
+        <v>45632</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13970,7 +13960,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14013,7 +14003,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14027,10 +14017,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45012</v>
+        <v>45290</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14043,7 +14033,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14086,7 +14076,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14100,10 +14090,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45629</v>
+        <v>44966</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14116,7 +14106,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14159,7 +14149,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14173,10 +14163,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45184</v>
+        <v>45588</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14189,7 +14179,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14232,7 +14222,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14246,10 +14236,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45628</v>
+        <v>45660</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14262,7 +14252,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14305,7 +14295,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14319,10 +14309,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44966</v>
+        <v>45628</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14335,7 +14325,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14378,7 +14368,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14392,10 +14382,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45660</v>
+        <v>45184</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14408,7 +14398,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14448,10 +14438,10 @@
       </c>
       <c r="V184" s="2" t="inlineStr"/>
     </row>
-    <row r="185" ht="15" customHeight="1">
+    <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14465,10 +14455,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45290</v>
+        <v>45547</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14480,8 +14470,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14520,79 +14515,6 @@
         <v>0</v>
       </c>
       <c r="V185" s="2" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>A 47648-2024</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D186" s="1" t="n">
-        <v>45588</v>
-      </c>
-      <c r="E186" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I186" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J186" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" t="n">
-        <v>0</v>
-      </c>
-      <c r="M186" t="n">
-        <v>0</v>
-      </c>
-      <c r="N186" t="n">
-        <v>0</v>
-      </c>
-      <c r="O186" t="n">
-        <v>0</v>
-      </c>
-      <c r="P186" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0</v>
-      </c>
-      <c r="S186" t="n">
-        <v>0</v>
-      </c>
-      <c r="T186" t="n">
-        <v>0</v>
-      </c>
-      <c r="U186" t="n">
-        <v>0</v>
-      </c>
-      <c r="V186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE185"/>
+  <dimension ref="A1:AE186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16116-2022</t>
+          <t>A 69169-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44665</v>
+        <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 69169-2021</t>
+          <t>A 16116-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44530</v>
+        <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44760</v>
+        <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3085,8 +3085,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>0.3</v>
+        <v>14.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3129,7 +3134,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3143,10 +3148,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45341</v>
+        <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3159,7 +3164,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3202,7 +3207,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3216,10 +3221,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45397</v>
+        <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3232,7 +3237,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3275,7 +3280,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3289,10 +3294,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45385</v>
+        <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3305,7 +3310,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3348,7 +3353,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3362,10 +3367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45379</v>
+        <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3378,7 +3383,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3421,7 +3426,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3435,10 +3440,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44886</v>
+        <v>44844</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3450,13 +3455,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44582</v>
+        <v>45358</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44582</v>
+        <v>44917</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.3</v>
+        <v>10.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45230</v>
+        <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44512</v>
+        <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44526</v>
+        <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44974</v>
+        <v>44671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3893,13 +3893,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>14.1</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3942,7 +3937,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3956,10 +3951,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44671</v>
+        <v>44582</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3972,7 +3967,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4015,7 +4010,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4029,10 +4024,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45699</v>
+        <v>44582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4045,7 +4040,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4088,7 +4083,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4102,10 +4097,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45560</v>
+        <v>45694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4118,7 +4113,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4161,7 +4156,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4175,10 +4170,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44886</v>
+        <v>45000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4190,13 +4185,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>19.4</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4239,7 +4229,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4253,10 +4243,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45358</v>
+        <v>44663</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4269,7 +4259,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4312,7 +4302,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4326,10 +4316,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45883</v>
+        <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4342,7 +4332,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4385,7 +4375,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4399,10 +4389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45883</v>
+        <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4415,7 +4405,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>9.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4458,7 +4448,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4472,10 +4462,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44887</v>
+        <v>45593</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4488,7 +4478,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4531,7 +4521,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4541,14 +4531,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46078</v>
+        <v>45512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4561,7 +4551,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4604,7 +4594,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4618,10 +4608,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46078</v>
+        <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4633,8 +4623,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4677,7 +4672,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4691,10 +4686,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46078</v>
+        <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4707,7 +4702,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4750,7 +4745,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4764,10 +4759,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45006</v>
+        <v>45397</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4780,7 +4775,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4823,7 +4818,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4833,14 +4828,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45187</v>
+        <v>44909</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4852,13 +4847,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4901,7 +4891,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4915,10 +4905,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46078</v>
+        <v>45883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4931,7 +4921,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4974,7 +4964,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4991,7 +4981,7 @@
         <v>45264</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5004,7 +4994,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5047,7 +5037,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5064,7 +5054,7 @@
         <v>44909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5120,7 +5110,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5134,10 +5124,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46106</v>
+        <v>45758</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5149,13 +5139,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5198,7 +5183,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5212,10 +5197,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45000</v>
+        <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5228,7 +5213,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5271,7 +5256,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5285,10 +5270,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46122</v>
+        <v>45741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5301,7 +5286,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5344,7 +5329,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5354,14 +5339,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45512</v>
+        <v>45789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5374,7 +5359,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5417,7 +5402,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5431,10 +5416,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46128</v>
+        <v>44526</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5447,7 +5432,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5490,7 +5475,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5504,10 +5489,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46132</v>
+        <v>45111</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5520,7 +5505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5563,7 +5548,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5577,10 +5562,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45740</v>
+        <v>45919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5593,7 +5578,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5636,7 +5621,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5650,10 +5635,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45758</v>
+        <v>44760</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5666,7 +5651,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5709,7 +5694,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5723,10 +5708,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45243</v>
+        <v>45919</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5738,13 +5723,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>0.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5787,7 +5767,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5804,7 +5784,7 @@
         <v>45919</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5817,7 +5797,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5860,7 +5840,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5874,10 +5854,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45741</v>
+        <v>45919</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5890,7 +5870,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5933,7 +5913,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5947,10 +5927,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45919</v>
+        <v>45679</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5963,7 +5943,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>3.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6006,7 +5986,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6020,10 +6000,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6036,7 +6016,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6079,7 +6059,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6093,10 +6073,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45919</v>
+        <v>44754</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6108,8 +6088,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6152,7 +6137,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6166,10 +6151,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45665</v>
+        <v>45368</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6182,7 +6167,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6225,7 +6210,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6239,10 +6224,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44844</v>
+        <v>45952</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6255,7 +6240,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6298,7 +6283,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6312,10 +6297,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45789</v>
+        <v>45965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6327,8 +6312,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>11.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6371,7 +6361,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6385,10 +6375,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45111</v>
+        <v>45817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6401,7 +6391,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6444,7 +6434,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6458,10 +6448,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44909</v>
+        <v>45962</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6474,7 +6464,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6517,7 +6507,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6531,10 +6521,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44917</v>
+        <v>45092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6547,7 +6537,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10.9</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6590,7 +6580,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6604,10 +6594,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45933</v>
+        <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6620,7 +6610,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6663,7 +6653,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6677,10 +6667,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46154</v>
+        <v>45560</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6693,7 +6683,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6736,7 +6726,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6750,10 +6740,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45092</v>
+        <v>44662</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6766,7 +6756,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6809,7 +6799,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6823,10 +6813,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45264</v>
+        <v>46154</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6839,7 +6829,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>13.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6882,7 +6872,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6896,10 +6886,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46154</v>
+        <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6912,7 +6902,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6955,7 +6945,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6969,10 +6959,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46154</v>
+        <v>45264</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6985,7 +6975,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>13.6</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7028,7 +7018,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7042,10 +7032,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45817</v>
+        <v>46154</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7058,7 +7048,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7101,7 +7091,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7115,10 +7105,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46157</v>
+        <v>45385</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7131,7 +7121,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7174,7 +7164,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7188,10 +7178,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46157</v>
+        <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7204,7 +7194,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7247,7 +7237,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7261,10 +7251,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45747</v>
+        <v>45983</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7277,7 +7267,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>13.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7320,7 +7310,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7334,10 +7324,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46157</v>
+        <v>44668</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7350,7 +7340,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7393,7 +7383,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7407,10 +7397,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7423,7 +7413,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7466,7 +7456,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7480,10 +7470,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46161</v>
+        <v>45983</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7496,7 +7486,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7539,7 +7529,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7553,10 +7543,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44909</v>
+        <v>46157</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7569,7 +7559,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.5</v>
+        <v>6.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7612,7 +7602,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7626,10 +7616,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44909</v>
+        <v>46157</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7642,7 +7632,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7685,7 +7675,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7699,10 +7689,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45109</v>
+        <v>46161</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7715,7 +7705,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5.9</v>
+        <v>1.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7758,7 +7748,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7772,10 +7762,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44994</v>
+        <v>46161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7788,7 +7778,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7831,7 +7821,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7845,10 +7835,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46169</v>
+        <v>45986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7860,8 +7850,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7904,7 +7899,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7918,10 +7913,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45408</v>
+        <v>45230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7934,7 +7929,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7977,7 +7972,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7991,10 +7986,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45012</v>
+        <v>45429</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8007,7 +8002,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8050,7 +8045,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8064,10 +8059,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45264</v>
+        <v>45999</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8079,8 +8074,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8123,7 +8123,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46177</v>
+        <v>45714</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8196,7 +8196,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8210,10 +8210,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46177</v>
+        <v>45608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8269,7 +8269,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46177</v>
+        <v>45434</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8342,7 +8342,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8356,10 +8356,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46177</v>
+        <v>44602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8415,7 +8415,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46181</v>
+        <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45952</v>
+        <v>45706</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8575,10 +8575,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44516</v>
+        <v>46169</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45429</v>
+        <v>46030</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8707,7 +8707,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45962</v>
+        <v>44781</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8780,7 +8780,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46195</v>
+        <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8809,13 +8809,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8858,7 +8853,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8872,10 +8867,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44602</v>
+        <v>46037</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8888,7 +8883,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>9.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8931,7 +8926,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8945,10 +8940,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45965</v>
+        <v>44512</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8960,13 +8955,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9009,7 +8999,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9023,10 +9013,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44830</v>
+        <v>46177</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9082,7 +9072,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9096,10 +9086,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45608</v>
+        <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9112,7 +9102,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9155,7 +9145,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9169,10 +9159,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45706</v>
+        <v>46177</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9185,7 +9175,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9228,7 +9218,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9242,10 +9232,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46204</v>
+        <v>46177</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9258,7 +9248,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9301,7 +9291,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9315,10 +9305,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45986</v>
+        <v>46181</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9330,13 +9320,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9379,7 +9364,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9393,10 +9378,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45983</v>
+        <v>45006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9409,7 +9394,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9452,7 +9437,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9466,10 +9451,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46206</v>
+        <v>44978</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9482,7 +9467,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9525,7 +9510,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9539,10 +9524,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46251</v>
+        <v>44960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9556,11 +9541,11 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>6.7</v>
+        <v>14.8</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9603,7 +9588,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9617,10 +9602,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46206</v>
+        <v>46078</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9633,7 +9618,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9676,7 +9661,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9690,10 +9675,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44668</v>
+        <v>46078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9706,7 +9691,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9749,7 +9734,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9763,10 +9748,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45983</v>
+        <v>45699</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9779,7 +9764,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>13.2</v>
+        <v>5.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9822,7 +9807,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9836,10 +9821,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45167</v>
+        <v>46078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9852,7 +9837,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>7.1</v>
+        <v>0.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9895,7 +9880,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9909,10 +9894,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46206</v>
+        <v>45379</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9925,7 +9910,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9968,7 +9953,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9982,10 +9967,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46206</v>
+        <v>44988</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9998,7 +9983,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10041,7 +10026,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10055,10 +10040,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46206</v>
+        <v>46078</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10071,7 +10056,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10114,7 +10099,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10128,10 +10113,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46206</v>
+        <v>46195</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10143,8 +10128,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10187,7 +10177,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10201,10 +10191,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44662</v>
+        <v>46106</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10216,8 +10206,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10260,7 +10255,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10274,10 +10269,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46169</v>
+        <v>45243</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10289,8 +10284,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10333,7 +10333,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10347,10 +10347,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44754</v>
+        <v>45109</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10362,13 +10362,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10411,7 +10406,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10425,10 +10420,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45999</v>
+        <v>45408</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10440,13 +10435,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10489,7 +10479,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10503,10 +10493,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45230</v>
+        <v>46122</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10519,7 +10509,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10562,7 +10552,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10576,10 +10566,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44663</v>
+        <v>44622</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10592,7 +10582,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10635,7 +10625,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10649,10 +10639,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46265</v>
+        <v>45159</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10665,7 +10655,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>7.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10708,7 +10698,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10722,10 +10712,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45264</v>
+        <v>46128</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10738,7 +10728,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10781,7 +10771,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10795,10 +10785,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45264</v>
+        <v>44790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10811,7 +10801,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.3</v>
+        <v>2.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10854,7 +10844,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10868,10 +10858,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46169</v>
+        <v>46132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10884,7 +10874,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10927,7 +10917,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10941,10 +10931,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46169</v>
+        <v>44887</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10957,7 +10947,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11000,7 +10990,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11014,10 +11004,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44781</v>
+        <v>44886</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11029,8 +11019,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11073,7 +11068,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11087,10 +11082,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45448</v>
+        <v>46204</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11103,7 +11098,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11146,7 +11141,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11160,10 +11155,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46010</v>
+        <v>45230</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11176,7 +11171,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11219,7 +11214,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11229,14 +11224,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46275</v>
+        <v>44634</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11249,7 +11244,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11292,7 +11287,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11306,10 +11301,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11322,7 +11317,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11365,7 +11360,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11379,10 +11374,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11395,7 +11390,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11438,7 +11433,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11452,10 +11447,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46275</v>
+        <v>45194</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11468,7 +11463,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11511,7 +11506,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11525,10 +11520,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11541,7 +11536,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11584,7 +11579,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11598,10 +11593,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11614,7 +11609,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11657,7 +11652,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11671,10 +11666,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46277</v>
+        <v>45145</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11730,7 +11725,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11744,10 +11739,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44978</v>
+        <v>46206</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11760,7 +11755,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11803,7 +11798,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11817,10 +11812,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46277</v>
+        <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11832,8 +11827,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>6.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11876,7 +11876,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11890,10 +11890,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46030</v>
+        <v>46206</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11949,7 +11949,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11963,10 +11963,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46030</v>
+        <v>44909</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12036,10 +12036,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44790</v>
+        <v>44909</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12095,7 +12095,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12105,14 +12105,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45614</v>
+        <v>45187</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12173,7 +12173,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12187,10 +12187,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45593</v>
+        <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.5</v>
+        <v>3.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12260,10 +12260,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44634</v>
+        <v>45699</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12276,7 +12276,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12319,7 +12319,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12333,10 +12333,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45232</v>
+        <v>44994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12392,7 +12392,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12406,10 +12406,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46037</v>
+        <v>45253</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12422,7 +12422,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>9.1</v>
+        <v>4.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12465,7 +12465,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12479,10 +12479,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>44960</v>
+        <v>45341</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12494,13 +12494,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>14.8</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12543,7 +12538,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12557,10 +12552,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44494</v>
+        <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12573,7 +12568,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12616,7 +12611,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12630,10 +12625,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45145</v>
+        <v>46265</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12646,7 +12641,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12689,7 +12684,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12703,10 +12698,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45679</v>
+        <v>44530</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12719,7 +12714,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12762,7 +12757,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12776,10 +12771,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44622</v>
+        <v>46169</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12792,7 +12787,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12835,7 +12830,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12849,10 +12844,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45456</v>
+        <v>45448</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12865,7 +12860,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12908,7 +12903,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12922,10 +12917,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45434</v>
+        <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12938,7 +12933,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12981,7 +12976,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12995,10 +12990,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45209</v>
+        <v>46275</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13011,7 +13006,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13054,7 +13049,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13068,10 +13063,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44988</v>
+        <v>45632</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13084,7 +13079,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13127,7 +13122,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13141,10 +13136,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45194</v>
+        <v>46275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13157,7 +13152,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13200,7 +13195,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13214,10 +13209,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45368</v>
+        <v>46275</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13230,7 +13225,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13273,7 +13268,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13287,10 +13282,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44530</v>
+        <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13303,7 +13298,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13346,7 +13341,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13360,10 +13355,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45714</v>
+        <v>46275</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13376,7 +13371,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13419,7 +13414,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13433,10 +13428,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45159</v>
+        <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13449,7 +13444,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13492,7 +13487,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13502,14 +13497,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45699</v>
+        <v>46275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13522,7 +13517,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.3</v>
+        <v>10.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13565,7 +13560,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13579,10 +13574,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45694</v>
+        <v>45012</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13595,7 +13590,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13638,7 +13633,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13652,10 +13647,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45253</v>
+        <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13668,7 +13663,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.3</v>
+        <v>1.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13711,7 +13706,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13725,10 +13720,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45615</v>
+        <v>46277</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13741,7 +13736,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13784,7 +13779,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13798,10 +13793,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45012</v>
+        <v>46277</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13814,7 +13809,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13857,7 +13852,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13871,10 +13866,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45629</v>
+        <v>45184</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13887,7 +13882,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13930,7 +13925,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13944,10 +13939,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13960,7 +13955,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14003,7 +13998,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14017,10 +14012,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45290</v>
+        <v>44966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14033,7 +14028,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14076,7 +14071,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14090,10 +14085,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44966</v>
+        <v>45660</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14106,7 +14101,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14149,7 +14144,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14163,10 +14158,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45588</v>
+        <v>45290</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14179,7 +14174,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14222,7 +14217,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14236,10 +14231,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45660</v>
+        <v>45588</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14252,7 +14247,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14295,7 +14290,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14309,10 +14304,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45628</v>
+        <v>46283</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14324,8 +14319,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14368,7 +14368,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14382,10 +14382,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45184</v>
+        <v>45547</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14397,8 +14397,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14438,10 +14443,10 @@
       </c>
       <c r="V184" s="2" t="inlineStr"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14455,10 +14460,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45547</v>
+        <v>44886</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14476,7 +14481,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>19.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14515,6 +14520,79 @@
         <v>0</v>
       </c>
       <c r="V185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>A 38302-2025</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="n">
+        <v>45883</v>
+      </c>
+      <c r="E186" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0</v>
+      </c>
+      <c r="S186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
+        <v>0</v>
+      </c>
+      <c r="U186" t="n">
+        <v>0</v>
+      </c>
+      <c r="V186" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>44844</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45358</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44917</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>44671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44582</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>45000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>44663</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>45593</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>44830</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>45397</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>44909</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45883</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>45264</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>44909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45758</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>45740</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>45741</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>45789</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44526</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>45111</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>44760</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45919</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45919</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>45919</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>45679</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>45933</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44754</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>45368</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45952</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>45817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45962</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>45092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>46154</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45560</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44662</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>46154</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>45456</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>45264</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>46154</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>45385</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>45012</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>45983</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44668</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45983</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>46157</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>46157</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>46161</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>46161</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>45986</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>45230</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45429</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>45999</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>45714</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>45608</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>45434</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44602</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45706</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>46169</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>46030</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44781</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>46030</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>46037</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>44512</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>46177</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>46177</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>46177</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9235,7 +9235,7 @@
         <v>46177</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>46181</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45006</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44978</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44960</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>46078</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         <v>46078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45699</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>46078</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45379</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44988</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>46078</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>46195</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>46106</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>45243</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>45109</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45408</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>46122</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44622</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>45159</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>46128</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
         <v>44790</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>46132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44887</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>44886</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>46204</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>45230</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44634</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>46206</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>46206</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45194</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46206</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>46206</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>45145</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46206</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>46251</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>46206</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44909</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>44909</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>45187</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12263,7 +12263,7 @@
         <v>45699</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44994</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>45253</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45341</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12555,7 +12555,7 @@
         <v>46169</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12628,7 +12628,7 @@
         <v>46265</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44530</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>46169</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         <v>45448</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45747</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>46275</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13066,7 +13066,7 @@
         <v>45632</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>46275</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46275</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>46275</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45615</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>46275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45012</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>46277</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>46277</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45184</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45628</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>44966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45660</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45290</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45588</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>46283</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>45547</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14463,7 +14463,7 @@
         <v>44886</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>45883</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45804</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45434</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45665</v>
+        <v>44844</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44844</v>
+        <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>45358</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44917</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>44671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44582</v>
+        <v>45694</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4027,7 +4027,7 @@
         <v>44582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45694</v>
+        <v>44582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4173,7 +4173,7 @@
         <v>45000</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>44663</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4448,7 +4448,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4458,14 +4458,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45593</v>
+        <v>45512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4521,7 +4521,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4531,14 +4531,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45512</v>
+        <v>44830</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4594,7 +4594,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45614</v>
+        <v>45883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4623,13 +4623,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4672,7 +4667,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4686,10 +4681,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44830</v>
+        <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4702,7 +4697,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4745,7 +4740,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4759,10 +4754,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45397</v>
+        <v>45593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4775,7 +4770,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4818,7 +4813,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4832,10 +4827,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44909</v>
+        <v>45614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4847,8 +4842,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45883</v>
+        <v>44909</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>9.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4964,7 +4964,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45264</v>
+        <v>45758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.3</v>
+        <v>2.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44909</v>
+        <v>45397</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5110,7 +5110,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5124,10 +5124,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45758</v>
+        <v>45740</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45740</v>
+        <v>45741</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5256,7 +5256,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45741</v>
+        <v>44909</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5329,7 +5329,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5343,10 +5343,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45789</v>
+        <v>45264</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5402,7 +5402,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5416,10 +5416,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44526</v>
+        <v>45789</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5475,7 +5475,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5489,10 +5489,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45111</v>
+        <v>45919</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5565,7 +5565,7 @@
         <v>45919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44760</v>
+        <v>45919</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5711,7 +5711,7 @@
         <v>45919</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5767,7 +5767,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5840,7 +5840,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5854,10 +5854,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45919</v>
+        <v>45817</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5913,7 +5913,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5927,10 +5927,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45679</v>
+        <v>46154</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5986,7 +5986,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6000,10 +6000,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45933</v>
+        <v>46154</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>13.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6073,10 +6073,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44754</v>
+        <v>46154</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6088,13 +6088,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6137,7 +6132,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6151,10 +6146,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45368</v>
+        <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6167,7 +6162,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6210,7 +6205,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6224,10 +6219,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45952</v>
+        <v>45111</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6240,7 +6235,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.1</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6283,7 +6278,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6297,10 +6292,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45965</v>
+        <v>44760</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6312,13 +6307,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>11.6</v>
+        <v>0.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6361,7 +6351,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6375,10 +6365,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45817</v>
+        <v>45679</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6391,7 +6381,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6434,7 +6424,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6448,10 +6438,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45962</v>
+        <v>46157</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6464,7 +6454,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6507,7 +6497,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6521,10 +6511,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45092</v>
+        <v>46157</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6537,7 +6527,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6580,7 +6570,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6594,10 +6584,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46154</v>
+        <v>46157</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6610,7 +6600,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6653,7 +6643,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6667,10 +6657,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45560</v>
+        <v>46161</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6683,7 +6673,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6726,7 +6716,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6740,10 +6730,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44662</v>
+        <v>46161</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6756,7 +6746,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6799,7 +6789,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6813,10 +6803,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46154</v>
+        <v>45952</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6829,7 +6819,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>13.6</v>
+        <v>6.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6872,7 +6862,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6886,10 +6876,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45456</v>
+        <v>45965</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6901,8 +6891,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>7.5</v>
+        <v>11.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6945,7 +6940,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6959,10 +6954,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45264</v>
+        <v>45962</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6975,7 +6970,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7018,7 +7013,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7032,10 +7027,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46154</v>
+        <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7047,8 +7042,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7091,7 +7091,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7105,10 +7105,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45385</v>
+        <v>45368</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7164,7 +7164,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7178,10 +7178,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45012</v>
+        <v>45983</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>13.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7237,7 +7237,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7254,7 +7254,7 @@
         <v>45983</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>13.2</v>
+        <v>1.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7310,7 +7310,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44668</v>
+        <v>46169</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7383,7 +7383,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7397,10 +7397,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46157</v>
+        <v>45986</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7412,8 +7412,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7456,7 +7461,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7470,10 +7475,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45983</v>
+        <v>45999</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7485,8 +7490,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7529,7 +7539,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7543,10 +7553,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7559,7 +7569,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7602,7 +7612,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7616,10 +7626,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46157</v>
+        <v>46177</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7632,7 +7642,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7675,7 +7685,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7689,10 +7699,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7705,7 +7715,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7748,7 +7758,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7762,10 +7772,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7778,7 +7788,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7821,7 +7831,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7835,10 +7845,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45986</v>
+        <v>45092</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7850,13 +7860,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>7.7</v>
+        <v>0.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7899,7 +7904,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7913,10 +7918,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45230</v>
+        <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7929,7 +7934,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7972,7 +7977,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7986,10 +7991,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45429</v>
+        <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8002,7 +8007,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8045,7 +8050,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8059,10 +8064,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45999</v>
+        <v>46181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8074,13 +8079,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>8.6</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8123,7 +8123,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45714</v>
+        <v>44662</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8196,7 +8196,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8210,10 +8210,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45608</v>
+        <v>45456</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8269,7 +8269,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45434</v>
+        <v>45264</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8342,7 +8342,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8356,10 +8356,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44602</v>
+        <v>45385</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8415,7 +8415,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8429,10 +8429,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46010</v>
+        <v>45012</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8502,10 +8502,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45706</v>
+        <v>44668</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8561,7 +8561,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8575,10 +8575,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46169</v>
+        <v>46030</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8651,7 +8651,7 @@
         <v>46030</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8707,7 +8707,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44781</v>
+        <v>46037</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>9.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8780,7 +8780,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46030</v>
+        <v>45230</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8853,7 +8853,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8867,10 +8867,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46037</v>
+        <v>45429</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8926,7 +8926,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44512</v>
+        <v>45714</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8999,7 +8999,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9013,10 +9013,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46177</v>
+        <v>46195</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9028,8 +9028,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I111" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9072,7 +9077,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9086,10 +9091,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46177</v>
+        <v>45608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9102,7 +9107,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9145,7 +9150,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9159,10 +9164,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46177</v>
+        <v>45434</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9175,7 +9180,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9218,7 +9223,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9232,10 +9237,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46177</v>
+        <v>44602</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9248,7 +9253,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9291,7 +9296,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9305,10 +9310,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46181</v>
+        <v>46078</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9321,7 +9326,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9364,7 +9369,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9378,10 +9383,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45006</v>
+        <v>46078</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9394,7 +9399,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9437,7 +9442,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9451,10 +9456,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44978</v>
+        <v>46078</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9467,7 +9472,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9510,7 +9515,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9524,10 +9529,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44960</v>
+        <v>45706</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9539,13 +9544,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>14.8</v>
+        <v>0.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9588,7 +9588,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9602,10 +9602,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46078</v>
+        <v>44781</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9661,7 +9661,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9678,7 +9678,7 @@
         <v>46078</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9734,7 +9734,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45699</v>
+        <v>46204</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9807,7 +9807,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46078</v>
+        <v>44512</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9837,7 +9837,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9880,7 +9880,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9894,10 +9894,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45379</v>
+        <v>46106</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9909,8 +9909,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9953,7 +9958,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9967,10 +9972,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44988</v>
+        <v>46206</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9983,7 +9988,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10026,7 +10031,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10040,10 +10045,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46078</v>
+        <v>46206</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10056,7 +10061,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10099,7 +10104,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10113,10 +10118,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46195</v>
+        <v>46206</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10128,13 +10133,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10177,7 +10177,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10191,10 +10191,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46106</v>
+        <v>46206</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10206,13 +10206,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10255,7 +10250,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10269,10 +10264,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45243</v>
+        <v>46122</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10284,13 +10279,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>3.7</v>
+        <v>6.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10333,7 +10323,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10347,10 +10337,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45109</v>
+        <v>46128</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10363,7 +10353,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10406,7 +10396,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10420,10 +10410,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45408</v>
+        <v>45006</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10436,7 +10426,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10479,7 +10469,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10493,10 +10483,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46122</v>
+        <v>46206</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10509,7 +10499,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10552,7 +10542,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10566,10 +10556,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44622</v>
+        <v>44978</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10582,7 +10572,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10625,7 +10615,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10639,10 +10629,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45159</v>
+        <v>46132</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10655,7 +10645,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.3</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10698,7 +10688,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10712,10 +10702,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46128</v>
+        <v>46251</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10727,8 +10717,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10771,7 +10766,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10785,10 +10780,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44790</v>
+        <v>44960</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10800,8 +10795,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>2.4</v>
+        <v>14.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10844,7 +10844,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10858,10 +10858,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46132</v>
+        <v>46206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10917,7 +10917,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10931,10 +10931,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44887</v>
+        <v>45699</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10990,7 +10990,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11004,10 +11004,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44886</v>
+        <v>45379</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11019,13 +11019,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11068,7 +11063,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11082,10 +11077,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46204</v>
+        <v>44988</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11098,7 +11093,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11141,7 +11136,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11155,10 +11150,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45230</v>
+        <v>46169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11171,7 +11166,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11214,7 +11209,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11228,10 +11223,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44634</v>
+        <v>45243</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11243,8 +11238,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11287,7 +11287,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11301,10 +11301,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46206</v>
+        <v>45109</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11360,7 +11360,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11374,10 +11374,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46206</v>
+        <v>45408</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>4.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11433,7 +11433,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11447,10 +11447,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45194</v>
+        <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11506,7 +11506,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46206</v>
+        <v>46265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11579,7 +11579,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11593,10 +11593,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46206</v>
+        <v>44622</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11652,7 +11652,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11666,10 +11666,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45145</v>
+        <v>46169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11725,7 +11725,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11739,10 +11739,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46206</v>
+        <v>45159</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11812,10 +11812,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46251</v>
+        <v>44790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11827,13 +11827,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>6.7</v>
+        <v>2.4</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11876,7 +11871,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11890,10 +11885,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46206</v>
+        <v>44887</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11906,7 +11901,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11949,7 +11944,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11963,10 +11958,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44909</v>
+        <v>44886</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11978,8 +11973,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12036,10 +12036,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44909</v>
+        <v>45230</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12095,7 +12095,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12105,14 +12105,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45187</v>
+        <v>44634</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12124,13 +12124,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12173,7 +12168,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12187,10 +12182,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46169</v>
+        <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12203,7 +12198,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12246,7 +12241,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12260,10 +12255,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45699</v>
+        <v>46275</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12276,7 +12271,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12319,7 +12314,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12333,10 +12328,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44994</v>
+        <v>45194</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12349,7 +12344,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12392,7 +12387,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12406,10 +12401,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45253</v>
+        <v>46275</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12422,7 +12417,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12465,7 +12460,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12479,10 +12474,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45341</v>
+        <v>46275</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12495,7 +12490,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12538,7 +12533,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12552,10 +12547,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46169</v>
+        <v>46275</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12568,7 +12563,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12611,7 +12606,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12625,10 +12620,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46265</v>
+        <v>45145</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12641,7 +12636,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12684,7 +12679,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12694,14 +12689,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44530</v>
+        <v>46275</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12714,7 +12709,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>4.2</v>
+        <v>10.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12757,7 +12752,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12771,10 +12766,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46169</v>
+        <v>46277</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12787,7 +12782,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12830,7 +12825,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12844,10 +12839,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45448</v>
+        <v>46277</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12860,7 +12855,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12903,7 +12898,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12917,10 +12912,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45747</v>
+        <v>44909</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12933,7 +12928,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12976,7 +12971,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12990,10 +12985,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46275</v>
+        <v>44909</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13006,7 +13001,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13049,7 +13044,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13059,14 +13054,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45632</v>
+        <v>45187</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13078,8 +13073,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13122,7 +13122,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13136,10 +13136,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46275</v>
+        <v>45699</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13195,7 +13195,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13209,10 +13209,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46275</v>
+        <v>46283</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13224,8 +13224,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13268,7 +13273,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13282,10 +13287,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46275</v>
+        <v>44994</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13298,7 +13303,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>3.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13341,7 +13346,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13355,10 +13360,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46275</v>
+        <v>45253</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13371,7 +13376,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13414,7 +13419,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13428,10 +13433,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45615</v>
+        <v>45341</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13444,7 +13449,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13487,7 +13492,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13497,14 +13502,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46275</v>
+        <v>44530</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13517,7 +13522,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>10.2</v>
+        <v>4.2</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13560,7 +13565,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13574,10 +13579,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45012</v>
+        <v>45448</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13590,7 +13595,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13633,7 +13638,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13647,10 +13652,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45629</v>
+        <v>45747</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13663,7 +13668,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13706,7 +13711,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13720,10 +13725,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46277</v>
+        <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13736,7 +13741,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13779,7 +13784,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13793,10 +13798,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46277</v>
+        <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13809,7 +13814,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13852,7 +13857,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13866,10 +13871,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45184</v>
+        <v>45012</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13882,7 +13887,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13925,7 +13930,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13939,10 +13944,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45628</v>
+        <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13955,7 +13960,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>6.2</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -13998,7 +14003,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14012,10 +14017,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44966</v>
+        <v>45184</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14028,7 +14033,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14071,7 +14076,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14085,10 +14090,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45660</v>
+        <v>45628</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14101,7 +14106,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14144,7 +14149,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14158,10 +14163,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45290</v>
+        <v>44966</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14174,7 +14179,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14217,7 +14222,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14231,10 +14236,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45588</v>
+        <v>45660</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14247,7 +14252,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14290,7 +14295,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14304,10 +14309,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46283</v>
+        <v>45290</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14319,13 +14324,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14368,7 +14368,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14382,10 +14382,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45547</v>
+        <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14395,11 +14395,6 @@
       <c r="G184" t="inlineStr">
         <is>
           <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -14446,7 +14441,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14460,10 +14455,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44886</v>
+        <v>45547</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14481,7 +14476,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>19.4</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14524,7 +14519,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14538,10 +14533,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45883</v>
+        <v>44886</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14553,8 +14548,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>0.4</v>
+        <v>19.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 944-2025</t>
+          <t>A 26044-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45666</v>
+        <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams
+Humleblomster</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 944-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45666</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Fällmossa
 Rävticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 26044-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams
-Humleblomster</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46674-2023</t>
+          <t>A 20064-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45198</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46674-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45198</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20064-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 64461-2021</t>
+          <t>A 56463-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44511</v>
+        <v>45625</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1624,14 +1624,19 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>12.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1661,152 +1666,147 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 64461-2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44511</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Vitsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 64461-2021 artfynd.xlsx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 64461-2021 karta.png", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 64461-2021 georefererad karta.tif", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 64461-2021 FSC-klagomål.docx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 64461-2021 FSC-klagomål mail.docx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 64461-2021 tillsynsbegäran.docx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 64461-2021 tillsynsbegäran mail.docx", "A 64461-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 56463-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Scharlakansskål</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16173-2022</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44668</v>
+        <v>45632</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44974</v>
+        <v>45243</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3087,11 +3087,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>14.1</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3134,7 +3134,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 16173-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45209</v>
+        <v>44668</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45264</v>
+        <v>45341</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3280,7 +3280,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45264</v>
+        <v>44760</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44844</v>
+        <v>45665</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45665</v>
+        <v>44844</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45358</v>
+        <v>45111</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44917</v>
+        <v>45230</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.9</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44494</v>
+        <v>45397</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45264</v>
+        <v>45290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45232</v>
+        <v>44966</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44671</v>
+        <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45694</v>
+        <v>45660</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44582</v>
+        <v>45385</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44582</v>
+        <v>45628</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4156,7 +4156,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45000</v>
+        <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44663</v>
+        <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4302,7 +4302,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44516</v>
+        <v>45883</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45167</v>
+        <v>45547</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4404,8 +4404,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4448,7 +4453,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4458,14 +4463,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45512</v>
+        <v>44917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4483,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>10.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4521,7 +4526,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4535,10 +4540,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44830</v>
+        <v>45092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4556,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4594,7 +4599,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4608,10 +4613,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45883</v>
+        <v>45379</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4624,7 +4629,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4667,7 +4672,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4681,10 +4686,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45883</v>
+        <v>45264</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4697,7 +4702,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4740,7 +4745,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4754,10 +4759,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45593</v>
+        <v>45747</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4770,7 +4775,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4813,7 +4818,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4827,10 +4832,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45614</v>
+        <v>44582</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4842,13 +4847,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44909</v>
+        <v>44582</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4964,7 +4964,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45758</v>
+        <v>44886</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4993,8 +4993,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5037,7 +5042,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5051,10 +5056,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45397</v>
+        <v>44909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5067,7 +5072,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5110,7 +5115,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5124,10 +5129,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45740</v>
+        <v>44909</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5140,7 +5145,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5183,7 +5188,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5197,10 +5202,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45741</v>
+        <v>44512</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5213,7 +5218,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5256,7 +5261,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5270,10 +5275,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44909</v>
+        <v>45109</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5286,7 +5291,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.5</v>
+        <v>5.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5329,7 +5334,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5343,10 +5348,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45264</v>
+        <v>44994</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,7 +5364,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6.3</v>
+        <v>3.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5402,7 +5407,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5416,10 +5421,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45789</v>
+        <v>45919</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,7 +5437,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5475,7 +5480,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5489,10 +5494,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45919</v>
+        <v>45408</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5510,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5565,7 +5570,7 @@
         <v>45919</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5638,7 +5643,7 @@
         <v>45919</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5694,7 +5699,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5711,7 +5716,7 @@
         <v>45919</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5729,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5767,7 +5772,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5781,10 +5786,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45933</v>
+        <v>45012</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5802,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5840,7 +5845,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5854,10 +5859,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45817</v>
+        <v>45264</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5875,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5913,7 +5918,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5927,10 +5932,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46154</v>
+        <v>45933</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,7 +5948,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5986,7 +5991,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6000,10 +6005,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46154</v>
+        <v>45699</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6016,7 +6021,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>13.6</v>
+        <v>5.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6059,7 +6064,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6073,10 +6078,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46154</v>
+        <v>44516</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,7 +6094,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6149,7 +6154,7 @@
         <v>44526</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6205,7 +6210,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6219,10 +6224,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45111</v>
+        <v>44671</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6235,7 +6240,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6278,7 +6283,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6292,10 +6297,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44760</v>
+        <v>45429</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6308,7 +6313,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6351,7 +6356,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6365,10 +6370,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45679</v>
+        <v>44974</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6380,8 +6385,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>14.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6424,7 +6434,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6438,10 +6448,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46157</v>
+        <v>45560</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6454,7 +6464,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6497,7 +6507,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6511,10 +6521,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46157</v>
+        <v>45358</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6527,7 +6537,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.6</v>
+        <v>2.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6570,7 +6580,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6584,10 +6594,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46157</v>
+        <v>44887</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6600,7 +6610,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6643,7 +6653,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6657,10 +6667,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46161</v>
+        <v>44602</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6673,7 +6683,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6716,7 +6726,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6730,10 +6740,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46161</v>
+        <v>45952</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6746,7 +6756,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6789,7 +6799,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6803,10 +6813,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45952</v>
+        <v>44886</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6818,8 +6828,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>6.1</v>
+        <v>19.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6862,7 +6877,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6876,10 +6891,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45965</v>
+        <v>45006</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6891,13 +6906,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>11.6</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6957,7 +6967,7 @@
         <v>45962</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7013,7 +7023,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7027,10 +7037,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44754</v>
+        <v>44830</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7042,13 +7052,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>8.800000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7091,7 +7096,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7101,14 +7106,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45368</v>
+        <v>45187</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7120,8 +7125,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7164,7 +7174,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7178,10 +7188,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45983</v>
+        <v>45965</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7193,8 +7203,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7237,7 +7252,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7251,10 +7266,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45983</v>
+        <v>45608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7267,7 +7282,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7310,7 +7325,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7324,10 +7339,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46169</v>
+        <v>45706</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7340,7 +7355,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7383,7 +7398,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7397,10 +7412,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45986</v>
+        <v>45264</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7412,13 +7427,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7461,7 +7471,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7475,10 +7485,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45999</v>
+        <v>44909</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7490,13 +7500,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7539,7 +7544,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7553,10 +7558,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46177</v>
+        <v>44668</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7569,7 +7574,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7612,7 +7617,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7626,10 +7631,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>46177</v>
+        <v>45167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7642,7 +7647,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.3</v>
+        <v>7.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7685,7 +7690,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7699,10 +7704,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46177</v>
+        <v>45986</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7714,8 +7719,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7758,7 +7768,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7772,10 +7782,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46177</v>
+        <v>45983</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7788,7 +7798,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7831,7 +7841,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7845,10 +7855,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45092</v>
+        <v>45000</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7861,7 +7871,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7904,7 +7914,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7918,10 +7928,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45560</v>
+        <v>45983</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7934,7 +7944,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.9</v>
+        <v>13.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7977,7 +7987,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7991,10 +8001,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46010</v>
+        <v>44662</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8007,7 +8017,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8050,7 +8060,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8060,14 +8070,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46181</v>
+        <v>45512</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8080,7 +8090,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8123,7 +8133,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8137,10 +8147,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44662</v>
+        <v>46030</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8153,7 +8163,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8196,7 +8206,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8210,10 +8220,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45456</v>
+        <v>45999</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8225,8 +8235,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8269,7 +8284,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8283,10 +8298,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45264</v>
+        <v>46030</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8299,7 +8314,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.7</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8342,7 +8357,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8356,10 +8371,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45385</v>
+        <v>44754</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8371,8 +8386,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8415,7 +8435,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8429,10 +8449,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45012</v>
+        <v>46037</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8445,7 +8465,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.1</v>
+        <v>9.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8488,7 +8508,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8502,10 +8522,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44668</v>
+        <v>45230</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8518,7 +8538,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8561,7 +8581,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8575,10 +8595,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46030</v>
+        <v>44663</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8591,7 +8611,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8634,7 +8654,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8648,10 +8668,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46030</v>
+        <v>46010</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8664,7 +8684,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8707,7 +8727,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8721,10 +8741,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46037</v>
+        <v>45264</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8737,7 +8757,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8780,7 +8800,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8794,10 +8814,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45230</v>
+        <v>45264</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8810,7 +8830,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8853,7 +8873,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8867,10 +8887,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45429</v>
+        <v>44781</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8926,7 +8946,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8940,10 +8960,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45714</v>
+        <v>46283</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8955,8 +8975,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8999,7 +9024,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9013,10 +9038,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46195</v>
+        <v>45448</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9028,13 +9053,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9077,7 +9097,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9091,10 +9111,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45608</v>
+        <v>46078</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9107,7 +9127,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9150,7 +9170,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9164,10 +9184,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45434</v>
+        <v>46078</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9180,7 +9200,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9223,7 +9243,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9237,10 +9257,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44602</v>
+        <v>46078</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9253,7 +9273,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9296,7 +9316,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9310,10 +9330,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46078</v>
+        <v>44978</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9326,7 +9346,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9369,7 +9389,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9383,10 +9403,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46078</v>
+        <v>44790</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9399,7 +9419,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9442,7 +9462,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9459,7 +9479,7 @@
         <v>46078</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9472,7 +9492,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9515,7 +9535,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9529,10 +9549,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45706</v>
+        <v>45614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9544,8 +9564,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9588,7 +9613,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9602,10 +9627,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44781</v>
+        <v>45593</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9618,7 +9643,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9661,7 +9686,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9675,10 +9700,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46078</v>
+        <v>44634</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9691,7 +9716,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9734,7 +9759,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9748,10 +9773,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46204</v>
+        <v>45232</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9764,7 +9789,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9807,7 +9832,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9821,10 +9846,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44512</v>
+        <v>44960</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9836,8 +9861,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>14.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9897,7 +9927,7 @@
         <v>46106</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9958,7 +9988,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9972,10 +10002,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46206</v>
+        <v>46122</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9988,7 +10018,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10031,7 +10061,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10045,10 +10075,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46206</v>
+        <v>44494</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10061,7 +10091,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10104,7 +10134,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10118,10 +10148,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46206</v>
+        <v>46128</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10134,7 +10164,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10177,7 +10207,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10191,10 +10221,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46206</v>
+        <v>46132</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10207,7 +10237,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10250,7 +10280,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10264,10 +10294,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46122</v>
+        <v>45740</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10280,7 +10310,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10323,7 +10353,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10337,10 +10367,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46128</v>
+        <v>45145</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10353,7 +10383,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10396,7 +10426,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10410,10 +10440,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45006</v>
+        <v>45679</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10426,7 +10456,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10469,7 +10499,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10483,10 +10513,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46206</v>
+        <v>44622</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10499,7 +10529,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10542,7 +10572,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10556,10 +10586,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44978</v>
+        <v>45456</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10572,7 +10602,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10615,7 +10645,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10629,10 +10659,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46132</v>
+        <v>45758</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10645,7 +10675,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10688,7 +10718,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10702,10 +10732,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46251</v>
+        <v>45741</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10717,13 +10747,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>6.7</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10766,7 +10791,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10780,10 +10805,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44960</v>
+        <v>45434</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10795,13 +10820,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>14.8</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10844,7 +10864,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10858,10 +10878,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46206</v>
+        <v>45789</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10874,7 +10894,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10917,7 +10937,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10931,10 +10951,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45699</v>
+        <v>45209</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10947,7 +10967,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.4</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10990,7 +11010,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11004,10 +11024,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45379</v>
+        <v>44988</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11020,7 +11040,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11063,7 +11083,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11077,10 +11097,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44988</v>
+        <v>45194</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11093,7 +11113,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11136,7 +11156,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11150,10 +11170,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46169</v>
+        <v>45368</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11166,7 +11186,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11209,7 +11229,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11223,10 +11243,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45243</v>
+        <v>44530</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11238,13 +11258,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11287,7 +11302,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11301,10 +11316,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45109</v>
+        <v>45714</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11317,7 +11332,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.9</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11360,7 +11375,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11374,10 +11389,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45408</v>
+        <v>44909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11390,7 +11405,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11433,7 +11448,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11447,10 +11462,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46169</v>
+        <v>45159</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11463,7 +11478,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>7.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11506,7 +11521,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11520,10 +11535,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46265</v>
+        <v>45699</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11579,7 +11594,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11593,10 +11608,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44622</v>
+        <v>45694</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11609,7 +11624,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11652,7 +11667,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11666,10 +11681,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46169</v>
+        <v>45253</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11682,7 +11697,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11725,7 +11740,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11739,10 +11754,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45159</v>
+        <v>46154</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11755,7 +11770,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7.3</v>
+        <v>2.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11798,7 +11813,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11812,10 +11827,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44790</v>
+        <v>45615</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11828,7 +11843,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11871,7 +11886,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11885,10 +11900,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44887</v>
+        <v>45012</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11901,7 +11916,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11944,7 +11959,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11958,10 +11973,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44886</v>
+        <v>46154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11973,13 +11988,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12022,7 +12032,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12036,10 +12046,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45230</v>
+        <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12052,7 +12062,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.5</v>
+        <v>13.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12095,7 +12105,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12109,10 +12119,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44634</v>
+        <v>45629</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12125,7 +12135,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12168,7 +12178,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12182,10 +12192,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46275</v>
+        <v>45817</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12198,7 +12208,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12241,7 +12251,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12255,10 +12265,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46275</v>
+        <v>46157</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12271,7 +12281,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12314,7 +12324,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12328,10 +12338,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45194</v>
+        <v>46157</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12344,7 +12354,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12387,7 +12397,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12401,10 +12411,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46275</v>
+        <v>46157</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12417,7 +12427,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12460,7 +12470,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12474,10 +12484,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46275</v>
+        <v>46161</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12490,7 +12500,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12533,7 +12543,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12547,10 +12557,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46275</v>
+        <v>46161</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12563,7 +12573,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.9</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12606,7 +12616,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12620,10 +12630,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45145</v>
+        <v>46169</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12636,7 +12646,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12679,7 +12689,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12689,14 +12699,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46275</v>
+        <v>46177</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12709,7 +12719,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>10.2</v>
+        <v>1.4</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12752,7 +12762,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12766,10 +12776,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46277</v>
+        <v>46177</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12782,7 +12792,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12825,7 +12835,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12839,10 +12849,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46277</v>
+        <v>46177</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12855,7 +12865,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12898,7 +12908,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12912,10 +12922,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44909</v>
+        <v>46177</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12928,7 +12938,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12971,7 +12981,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12985,10 +12995,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44909</v>
+        <v>46181</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13001,7 +13011,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13044,7 +13054,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13054,14 +13064,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45187</v>
+        <v>46195</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13075,11 +13085,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13122,7 +13132,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13136,10 +13146,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45699</v>
+        <v>46204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13152,7 +13162,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13195,7 +13205,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13209,10 +13219,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46283</v>
+        <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13224,13 +13234,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13273,7 +13278,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13287,10 +13292,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44994</v>
+        <v>46251</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13302,8 +13307,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13346,7 +13356,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13360,10 +13370,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45253</v>
+        <v>46206</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13376,7 +13386,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13419,7 +13429,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13433,10 +13443,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45341</v>
+        <v>46206</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13449,7 +13459,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13492,7 +13502,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13506,10 +13516,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>44530</v>
+        <v>46206</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13522,7 +13532,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13565,7 +13575,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13579,10 +13589,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45448</v>
+        <v>46206</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13595,7 +13605,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13638,7 +13648,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13652,10 +13662,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45747</v>
+        <v>46206</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13668,7 +13678,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13711,7 +13721,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13725,10 +13735,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45632</v>
+        <v>46169</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13741,7 +13751,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13784,7 +13794,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13798,10 +13808,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45615</v>
+        <v>46265</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13814,7 +13824,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13857,7 +13867,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13871,10 +13881,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45012</v>
+        <v>46169</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13887,7 +13897,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13930,7 +13940,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13944,10 +13954,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45629</v>
+        <v>46169</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13960,7 +13970,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14003,7 +14013,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14013,14 +14023,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45184</v>
+        <v>46275</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14033,7 +14043,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.2</v>
+        <v>10.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14076,7 +14086,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14090,10 +14100,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45628</v>
+        <v>46275</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14106,7 +14116,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14149,7 +14159,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14163,10 +14173,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44966</v>
+        <v>46275</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14179,7 +14189,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14222,7 +14232,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14236,10 +14246,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45660</v>
+        <v>46275</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14252,7 +14262,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14295,7 +14305,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14309,10 +14319,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45290</v>
+        <v>46275</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14325,7 +14335,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14368,7 +14378,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14382,10 +14392,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45588</v>
+        <v>46275</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14398,7 +14408,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14441,7 +14451,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14455,10 +14465,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45547</v>
+        <v>46277</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14470,13 +14480,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14519,7 +14524,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14533,10 +14538,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44886</v>
+        <v>46277</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,13 +14553,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>19.4</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26044-2025</t>
+          <t>A 944-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45804</v>
+        <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,17 +1088,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>31.3</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Fällmossa
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 26044-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams
 Humleblomster</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 944-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45666</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Fällmossa
-Rävticka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 56463-2024</t>
+          <t>A 64461-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45625</v>
+        <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1624,19 +1624,14 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>12.2</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1666,147 +1661,152 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 64461-2021 artfynd.xlsx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 64461-2021 karta.png", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 64461-2021 georefererad karta.tif", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 64461-2021 FSC-klagomål.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 64461-2021 FSC-klagomål mail.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 64461-2021 tillsynsbegäran.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 64461-2021 tillsynsbegäran mail.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 56463-2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>Scharlakansskål</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 64461-2021</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44511</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Vitsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 64461-2021 artfynd.xlsx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 64461-2021 karta.png", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 64461-2021 georefererad karta.tif", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 64461-2021 FSC-klagomål.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 64461-2021 FSC-klagomål mail.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 64461-2021 tillsynsbegäran.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 64461-2021 tillsynsbegäran mail.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>44642</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>44698</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>44847</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>44745</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>44663</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>44512</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44536</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>44668</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>44699</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>44728</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>44676</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>44530</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 16173-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45632</v>
+        <v>44668</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3056,7 +3056,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45243</v>
+        <v>44974</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3087,11 +3087,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>14.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3134,7 +3134,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16173-2022</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44668</v>
+        <v>45209</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45341</v>
+        <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3280,7 +3280,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44760</v>
+        <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3353,7 +3353,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,10 +3367,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45665</v>
+        <v>44844</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3426,7 +3426,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44844</v>
+        <v>45665</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3499,7 +3499,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45111</v>
+        <v>45358</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45230</v>
+        <v>44917</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.5</v>
+        <v>10.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45397</v>
+        <v>44494</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45290</v>
+        <v>45264</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44966</v>
+        <v>45232</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3864,7 +3864,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,10 +3878,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45588</v>
+        <v>44671</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45660</v>
+        <v>44582</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4010,7 +4010,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45385</v>
+        <v>44582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4083,7 +4083,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45628</v>
+        <v>45000</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4156,7 +4156,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4170,10 +4170,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45883</v>
+        <v>45694</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4229,7 +4229,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45184</v>
+        <v>44663</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4302,7 +4302,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45883</v>
+        <v>44516</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4375,7 +4375,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45547</v>
+        <v>45167</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4404,13 +4404,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4453,7 +4448,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4463,14 +4458,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44917</v>
+        <v>45512</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4483,7 +4478,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>10.9</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4526,7 +4521,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4540,10 +4535,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45092</v>
+        <v>44830</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4556,7 +4551,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4599,7 +4594,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4613,10 +4608,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45379</v>
+        <v>45883</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4629,7 +4624,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4672,7 +4667,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4686,10 +4681,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45264</v>
+        <v>45883</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4702,7 +4697,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4745,7 +4740,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4759,10 +4754,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45747</v>
+        <v>45593</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4775,7 +4770,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4818,7 +4813,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4832,10 +4827,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44582</v>
+        <v>45614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4847,8 +4842,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4891,7 +4891,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44582</v>
+        <v>45397</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4964,7 +4964,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44886</v>
+        <v>44909</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4993,13 +4993,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5042,7 +5037,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5059,7 +5054,7 @@
         <v>44909</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5115,7 +5110,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5129,10 +5124,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44909</v>
+        <v>45264</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5145,7 +5140,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5188,7 +5183,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5202,10 +5197,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44512</v>
+        <v>45758</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5218,7 +5213,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5261,7 +5256,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5275,10 +5270,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45109</v>
+        <v>45919</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5291,7 +5286,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5334,7 +5329,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5348,10 +5343,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44994</v>
+        <v>45919</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5364,7 +5359,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5407,7 +5402,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5424,7 +5419,7 @@
         <v>45919</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5437,7 +5432,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5480,7 +5475,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5494,10 +5489,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45408</v>
+        <v>45919</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5510,7 +5505,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5553,7 +5548,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5567,10 +5562,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45919</v>
+        <v>45740</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5583,7 +5578,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.3</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5626,7 +5621,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5640,10 +5635,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45919</v>
+        <v>45741</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5656,7 +5651,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5699,7 +5694,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5713,10 +5708,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5729,7 +5724,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5772,7 +5767,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5786,10 +5781,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45012</v>
+        <v>44526</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5802,7 +5797,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5845,7 +5840,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5859,10 +5854,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45264</v>
+        <v>45111</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5875,7 +5870,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5918,7 +5913,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5932,10 +5927,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45933</v>
+        <v>44760</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5948,7 +5943,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5991,7 +5986,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6005,10 +6000,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45699</v>
+        <v>45679</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6021,7 +6016,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6064,7 +6059,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6078,10 +6073,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44516</v>
+        <v>45789</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6094,7 +6089,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6137,7 +6132,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6151,10 +6146,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44526</v>
+        <v>45952</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6167,7 +6162,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6210,7 +6205,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6224,10 +6219,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44671</v>
+        <v>44754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6239,8 +6234,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6283,7 +6283,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6297,10 +6297,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45429</v>
+        <v>45965</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6312,8 +6312,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>11.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6356,7 +6361,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6370,10 +6375,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44974</v>
+        <v>45962</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6385,13 +6390,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>14.1</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45560</v>
+        <v>45368</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6507,7 +6507,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45358</v>
+        <v>45983</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.3</v>
+        <v>13.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6594,10 +6594,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44887</v>
+        <v>45983</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6653,7 +6653,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44602</v>
+        <v>45986</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6682,8 +6682,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6726,7 +6731,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6740,10 +6745,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45952</v>
+        <v>45999</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6755,8 +6760,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>6.1</v>
+        <v>8.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6799,7 +6809,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6813,10 +6823,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44886</v>
+        <v>45817</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6828,13 +6838,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6877,7 +6882,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6891,10 +6896,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45006</v>
+        <v>45092</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6907,7 +6912,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6950,7 +6955,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6964,10 +6969,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45962</v>
+        <v>46154</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6980,7 +6985,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7023,7 +7028,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7037,10 +7042,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44830</v>
+        <v>46154</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7053,7 +7058,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>13.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7096,7 +7101,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7106,14 +7111,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45187</v>
+        <v>46154</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7125,13 +7130,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7174,7 +7174,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7188,10 +7188,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45965</v>
+        <v>45560</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7203,13 +7203,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>11.6</v>
+        <v>2.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7252,7 +7247,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7266,10 +7261,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45608</v>
+        <v>46157</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7282,7 +7277,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7325,7 +7320,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7339,10 +7334,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45706</v>
+        <v>46157</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7355,7 +7350,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7398,7 +7393,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7412,10 +7407,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45264</v>
+        <v>46157</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7428,7 +7423,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7471,7 +7466,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7485,10 +7480,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44909</v>
+        <v>46161</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7501,7 +7496,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7544,7 +7539,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7558,10 +7553,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44668</v>
+        <v>46161</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7574,7 +7569,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7617,7 +7612,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7631,10 +7626,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45167</v>
+        <v>44662</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7647,7 +7642,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>7.1</v>
+        <v>3.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7690,7 +7685,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7704,10 +7699,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45986</v>
+        <v>46010</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7719,13 +7714,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7768,7 +7758,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7782,10 +7772,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45983</v>
+        <v>45456</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7798,7 +7788,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7841,7 +7831,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7855,10 +7845,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45000</v>
+        <v>45264</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7871,7 +7861,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.2</v>
+        <v>4.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7914,7 +7904,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7928,10 +7918,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45983</v>
+        <v>45385</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7944,7 +7934,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>13.2</v>
+        <v>1.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7987,7 +7977,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8001,10 +7991,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44662</v>
+        <v>45012</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8017,7 +8007,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8060,7 +8050,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8070,14 +8060,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45512</v>
+        <v>44668</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8150,7 +8140,7 @@
         <v>46030</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8206,7 +8196,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8220,10 +8210,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45999</v>
+        <v>46030</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8235,13 +8225,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8284,7 +8269,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8298,10 +8283,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46030</v>
+        <v>45230</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8314,7 +8299,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8357,7 +8342,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8371,10 +8356,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44754</v>
+        <v>46037</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8386,13 +8371,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8435,7 +8415,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8449,10 +8429,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46037</v>
+        <v>45429</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8465,7 +8445,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>9.1</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8508,7 +8488,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8522,10 +8502,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45230</v>
+        <v>45714</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8538,7 +8518,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8581,7 +8561,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8595,10 +8575,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44663</v>
+        <v>45608</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8611,7 +8591,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8654,7 +8634,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8668,10 +8648,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46010</v>
+        <v>45434</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8684,7 +8664,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8727,7 +8707,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8741,10 +8721,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45264</v>
+        <v>44602</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8757,7 +8737,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8800,7 +8780,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8814,10 +8794,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45264</v>
+        <v>46169</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8830,7 +8810,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8873,7 +8853,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8887,10 +8867,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44781</v>
+        <v>45706</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8903,7 +8883,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8946,7 +8926,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8960,10 +8940,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46283</v>
+        <v>46078</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8975,13 +8955,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9024,7 +8999,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9038,10 +9013,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45448</v>
+        <v>46078</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9054,7 +9029,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9097,7 +9072,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9111,10 +9086,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46078</v>
+        <v>44781</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9127,7 +9102,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9170,7 +9145,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9187,7 +9162,7 @@
         <v>46078</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9200,7 +9175,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9243,7 +9218,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9257,10 +9232,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46078</v>
+        <v>46177</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9273,7 +9248,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9316,7 +9291,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9330,10 +9305,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44978</v>
+        <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9346,7 +9321,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9389,7 +9364,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9403,10 +9378,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44790</v>
+        <v>46177</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9419,7 +9394,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9462,7 +9437,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9476,10 +9451,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46078</v>
+        <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9492,7 +9467,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9535,7 +9510,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9549,10 +9524,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45614</v>
+        <v>44512</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9564,13 +9539,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9613,7 +9583,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9627,10 +9597,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45593</v>
+        <v>46078</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9643,7 +9613,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9686,7 +9656,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9700,10 +9670,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44634</v>
+        <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9759,7 +9729,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9773,10 +9743,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45232</v>
+        <v>46106</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9788,8 +9758,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9832,7 +9807,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9846,10 +9821,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44960</v>
+        <v>45006</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9861,13 +9836,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>14.8</v>
+        <v>1.3</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9910,7 +9880,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9924,10 +9894,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46106</v>
+        <v>44978</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9939,13 +9909,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10005,7 +9970,7 @@
         <v>46122</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10061,7 +10026,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10075,10 +10040,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44494</v>
+        <v>44960</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10090,8 +10055,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>14.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10151,7 +10121,7 @@
         <v>46128</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10207,7 +10177,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10221,10 +10191,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46132</v>
+        <v>45699</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10237,7 +10207,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>5.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10280,7 +10250,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10294,10 +10264,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45740</v>
+        <v>46132</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10310,7 +10280,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10353,7 +10323,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10367,10 +10337,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45145</v>
+        <v>45379</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10383,7 +10353,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10426,7 +10396,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10440,10 +10410,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45679</v>
+        <v>46195</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10455,8 +10425,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10499,7 +10474,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10513,10 +10488,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44622</v>
+        <v>44988</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10529,7 +10504,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10572,7 +10547,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10586,10 +10561,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45456</v>
+        <v>46204</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10602,7 +10577,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10645,7 +10620,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10659,10 +10634,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45758</v>
+        <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10675,7 +10650,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10718,7 +10693,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10732,10 +10707,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45741</v>
+        <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10748,7 +10723,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10791,7 +10766,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10805,10 +10780,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45434</v>
+        <v>46206</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10821,7 +10796,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10864,7 +10839,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10878,10 +10853,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45789</v>
+        <v>46206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10937,7 +10912,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10951,10 +10926,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45209</v>
+        <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10967,7 +10942,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11010,7 +10985,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11024,10 +10999,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44988</v>
+        <v>45243</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11039,8 +11014,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11083,7 +11063,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11097,10 +11077,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45194</v>
+        <v>46251</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11112,8 +11092,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.8</v>
+        <v>6.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11156,7 +11141,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11170,10 +11155,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45368</v>
+        <v>45109</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11186,7 +11171,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11229,7 +11214,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11243,10 +11228,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44530</v>
+        <v>46206</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11259,7 +11244,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11302,7 +11287,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11316,10 +11301,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45714</v>
+        <v>45408</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11332,7 +11317,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11375,7 +11360,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11389,10 +11374,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44909</v>
+        <v>44622</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11405,7 +11390,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11465,7 +11450,7 @@
         <v>45159</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11521,7 +11506,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11535,10 +11520,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45699</v>
+        <v>44790</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11551,7 +11536,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11594,7 +11579,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11608,10 +11593,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45694</v>
+        <v>44887</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11624,7 +11609,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11667,7 +11652,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11681,10 +11666,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45253</v>
+        <v>46169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11697,7 +11682,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11740,7 +11725,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11754,10 +11739,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46154</v>
+        <v>44886</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11769,8 +11754,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11813,7 +11803,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11827,10 +11817,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45615</v>
+        <v>45230</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11843,7 +11833,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11886,7 +11876,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11900,10 +11890,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45012</v>
+        <v>44634</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11916,7 +11906,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11959,7 +11949,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11973,10 +11963,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46154</v>
+        <v>45194</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11989,7 +11979,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12032,7 +12022,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12046,10 +12036,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46154</v>
+        <v>45145</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12062,7 +12052,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>13.6</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12105,7 +12095,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12119,10 +12109,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45629</v>
+        <v>46169</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12135,7 +12125,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12178,7 +12168,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12192,10 +12182,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45817</v>
+        <v>46265</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12208,7 +12198,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12251,7 +12241,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12265,10 +12255,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12281,7 +12271,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12324,7 +12314,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12338,10 +12328,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46157</v>
+        <v>44909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12354,7 +12344,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6.6</v>
+        <v>2.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12397,7 +12387,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12411,10 +12401,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46157</v>
+        <v>44909</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12427,7 +12417,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12470,7 +12460,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12480,14 +12470,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46161</v>
+        <v>45187</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12499,8 +12489,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I158" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12543,7 +12538,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12557,10 +12552,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46161</v>
+        <v>45699</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12573,7 +12568,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12616,7 +12611,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12630,10 +12625,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46169</v>
+        <v>44994</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12646,7 +12641,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12689,7 +12684,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12703,10 +12698,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46177</v>
+        <v>46275</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12719,7 +12714,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12762,7 +12757,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12776,10 +12771,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46177</v>
+        <v>46275</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12792,7 +12787,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12835,7 +12830,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12849,10 +12844,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46177</v>
+        <v>46275</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12865,7 +12860,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12908,7 +12903,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12922,10 +12917,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46177</v>
+        <v>46275</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12938,7 +12933,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12981,7 +12976,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12995,10 +12990,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46181</v>
+        <v>46275</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13011,7 +13006,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13054,7 +13049,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13068,10 +13063,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46195</v>
+        <v>45253</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13083,13 +13078,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13132,7 +13122,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13146,10 +13136,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46204</v>
+        <v>45341</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13162,7 +13152,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13205,7 +13195,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13215,14 +13205,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46206</v>
+        <v>46275</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13235,7 +13225,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>10.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13278,7 +13268,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13292,10 +13282,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46251</v>
+        <v>46277</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13307,13 +13297,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13356,7 +13341,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13370,10 +13355,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46206</v>
+        <v>46277</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13386,7 +13371,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13429,7 +13414,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13443,10 +13428,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46206</v>
+        <v>44530</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13459,7 +13444,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13502,7 +13487,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13516,10 +13501,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46206</v>
+        <v>45448</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13532,7 +13517,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13575,7 +13560,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13589,10 +13574,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46206</v>
+        <v>45747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13605,7 +13590,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13648,7 +13633,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13662,10 +13647,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46206</v>
+        <v>46283</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13677,8 +13662,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13721,7 +13711,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13735,10 +13725,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46169</v>
+        <v>45632</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13751,7 +13741,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13794,7 +13784,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13808,10 +13798,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46265</v>
+        <v>45615</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13824,7 +13814,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13867,7 +13857,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13881,10 +13871,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46169</v>
+        <v>45012</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13897,7 +13887,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13940,7 +13930,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13954,10 +13944,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46169</v>
+        <v>45629</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13970,7 +13960,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14013,7 +14003,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14023,14 +14013,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46275</v>
+        <v>45184</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14043,7 +14033,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>10.2</v>
+        <v>3.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14086,7 +14076,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14100,10 +14090,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46275</v>
+        <v>45628</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14116,7 +14106,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14159,7 +14149,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14173,10 +14163,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46275</v>
+        <v>44966</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14189,7 +14179,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14232,7 +14222,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14246,10 +14236,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46275</v>
+        <v>45660</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14262,7 +14252,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14305,7 +14295,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14319,10 +14309,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46275</v>
+        <v>45290</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14335,7 +14325,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14378,7 +14368,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14392,10 +14382,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46275</v>
+        <v>45588</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14408,7 +14398,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14451,7 +14441,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14465,10 +14455,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46277</v>
+        <v>45547</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14480,8 +14470,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14524,7 +14519,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14538,10 +14533,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46277</v>
+        <v>44886</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14553,8 +14548,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>1.6</v>
+        <v>19.4</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE186"/>
+  <dimension ref="A1:AE195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 944-2025</t>
+          <t>A 26044-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45666</v>
+        <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams
+Humleblomster</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 944-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45666</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Fällmossa
 Rävticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 26044-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams
-Humleblomster</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46674-2023</t>
+          <t>A 20064-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45198</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46674-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45198</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20064-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 56463-2024</t>
+          <t>A 39832-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45625</v>
+        <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>12.2</v>
+        <v>6.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1775,115 +1775,152 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 39832-2026 artfynd.xlsx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 39832-2026 karta.png", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 39832-2026 georefererad karta.tif", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 39832-2026 FSC-klagomål.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 39832-2026 FSC-klagomål mail.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 39832-2026 tillsynsbegäran.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 39832-2026 tillsynsbegäran mail.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 56463-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Scharlakansskål</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 12909-2022</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44642</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr"/>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 68256-2021</t>
+          <t>A 12909-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1897,10 +1934,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44526</v>
+        <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1913,7 +1950,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1956,7 +1993,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 20271-2022</t>
+          <t>A 68256-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1970,10 +2007,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44698</v>
+        <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1986,7 +2023,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2029,7 +2066,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 46192-2022</t>
+          <t>A 20271-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2043,10 +2080,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44847</v>
+        <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2059,7 +2096,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2102,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 63811-2021</t>
+          <t>A 46192-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2116,10 +2153,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44509</v>
+        <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2132,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2175,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 27986-2022</t>
+          <t>A 63811-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2189,10 +2226,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44745</v>
+        <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2205,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2248,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15776-2022</t>
+          <t>A 27986-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2262,10 +2299,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44663</v>
+        <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2278,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2321,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 64839-2021</t>
+          <t>A 15776-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2335,10 +2372,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44512</v>
+        <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2351,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2394,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 70266-2021</t>
+          <t>A 64839-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2408,10 +2445,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44536</v>
+        <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2423,13 +2460,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2472,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 16174-2022</t>
+          <t>A 70266-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2486,10 +2518,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44668</v>
+        <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2501,8 +2533,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2545,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16175-2022</t>
+          <t>A 16174-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2562,7 +2599,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2575,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2618,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 20445-2022</t>
+          <t>A 16175-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2632,10 +2669,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44699</v>
+        <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2648,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2691,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 24870-2022</t>
+          <t>A 20445-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2705,10 +2742,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44728</v>
+        <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2721,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2764,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 17062-2022</t>
+          <t>A 24870-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2778,10 +2815,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44676</v>
+        <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2794,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2837,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 69169-2021</t>
+          <t>A 17062-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2851,10 +2888,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44530</v>
+        <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2867,7 +2904,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10.5</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2910,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16116-2022</t>
+          <t>A 69169-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2924,10 +2961,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44665</v>
+        <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2940,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2983,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16173-2022</t>
+          <t>A 16116-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2997,10 +3034,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44668</v>
+        <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3013,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3056,7 +3093,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 16173-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3070,10 +3107,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44974</v>
+        <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3085,13 +3122,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>14.1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3134,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3148,10 +3180,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45209</v>
+        <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3164,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3207,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3221,10 +3253,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45264</v>
+        <v>45341</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3237,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3280,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3294,10 +3326,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45264</v>
+        <v>45397</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3310,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3353,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3367,10 +3399,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44844</v>
+        <v>45230</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3383,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3426,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3440,10 +3472,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45665</v>
+        <v>45385</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3456,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3499,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3513,10 +3545,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45358</v>
+        <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3529,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3572,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3586,10 +3618,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44917</v>
+        <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3602,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.9</v>
+        <v>2.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3645,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3659,10 +3691,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44494</v>
+        <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3675,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3718,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3732,10 +3764,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45264</v>
+        <v>45290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3748,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3791,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3805,10 +3837,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45232</v>
+        <v>44966</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3821,7 +3853,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3864,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3878,10 +3910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44671</v>
+        <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3894,7 +3926,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3937,7 +3969,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3951,10 +3983,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44582</v>
+        <v>46030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3967,7 +3999,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4010,7 +4042,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4024,10 +4056,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44582</v>
+        <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4039,8 +4071,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4083,7 +4120,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4097,10 +4134,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45000</v>
+        <v>45660</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4113,7 +4150,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4156,7 +4193,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4170,10 +4207,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45694</v>
+        <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4186,7 +4223,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4229,7 +4266,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4243,10 +4280,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44663</v>
+        <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4259,7 +4296,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4302,7 +4339,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4316,10 +4353,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44516</v>
+        <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4331,8 +4368,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4375,7 +4417,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4389,10 +4431,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45167</v>
+        <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4405,7 +4447,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4448,7 +4490,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4458,14 +4500,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45512</v>
+        <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4478,7 +4520,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4521,7 +4563,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4535,10 +4577,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44830</v>
+        <v>45883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4551,7 +4593,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4594,7 +4636,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4608,10 +4650,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45883</v>
+        <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4624,7 +4666,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4667,7 +4709,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4681,10 +4723,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45883</v>
+        <v>46037</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4697,7 +4739,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4740,7 +4782,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4754,10 +4796,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45593</v>
+        <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4770,7 +4812,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4813,7 +4855,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4827,10 +4869,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45614</v>
+        <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4842,13 +4884,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4891,7 +4928,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4905,10 +4942,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45397</v>
+        <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4921,7 +4958,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4964,7 +5001,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4978,10 +5015,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44909</v>
+        <v>45919</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4994,7 +5031,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5037,7 +5074,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5051,10 +5088,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44909</v>
+        <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5067,7 +5104,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5110,7 +5147,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5124,10 +5161,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45264</v>
+        <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5140,7 +5177,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>6.3</v>
+        <v>2.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5183,7 +5220,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5197,10 +5234,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45758</v>
+        <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5213,7 +5250,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5256,7 +5293,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5270,10 +5307,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45919</v>
+        <v>44974</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5285,8 +5322,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>14.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5329,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5343,10 +5385,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45919</v>
+        <v>45560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5359,7 +5401,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5402,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5416,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45919</v>
+        <v>46078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5432,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5475,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5489,10 +5531,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45919</v>
+        <v>46078</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5505,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5548,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5562,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45740</v>
+        <v>45358</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5578,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5621,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5635,10 +5677,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45741</v>
+        <v>46078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5651,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5694,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5708,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45933</v>
+        <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5724,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5767,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5781,10 +5823,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44526</v>
+        <v>45933</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5797,7 +5839,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5840,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5854,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45111</v>
+        <v>46078</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5870,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5913,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5927,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44760</v>
+        <v>45006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5943,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5986,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5996,14 +6038,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45679</v>
+        <v>45187</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6015,8 +6057,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6059,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6073,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45789</v>
+        <v>45952</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6089,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6132,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6146,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45952</v>
+        <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6161,8 +6208,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6205,7 +6257,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6219,10 +6271,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44754</v>
+        <v>45264</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6234,13 +6286,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8.800000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6283,7 +6330,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6297,10 +6344,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45965</v>
+        <v>45962</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6312,13 +6359,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6361,7 +6403,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6375,10 +6417,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45962</v>
+        <v>44909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6391,7 +6433,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6434,7 +6476,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6448,10 +6490,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45368</v>
+        <v>45965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6463,8 +6505,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>11.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6507,7 +6554,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6521,10 +6568,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45983</v>
+        <v>46122</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6537,7 +6584,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6580,7 +6627,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6594,10 +6641,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45983</v>
+        <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6610,7 +6657,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6653,7 +6700,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6667,10 +6714,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45986</v>
+        <v>46128</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6682,13 +6729,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6731,7 +6773,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6745,10 +6787,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45999</v>
+        <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6760,13 +6802,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>8.6</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6809,7 +6846,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6819,14 +6856,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45817</v>
+        <v>45512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6839,7 +6876,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6882,7 +6919,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6896,10 +6933,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45092</v>
+        <v>45986</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6911,8 +6948,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>7.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6955,7 +6997,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6969,10 +7011,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46154</v>
+        <v>45983</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6985,7 +7027,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7028,7 +7070,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7042,10 +7084,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46154</v>
+        <v>45983</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7058,7 +7100,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7101,7 +7143,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7115,10 +7157,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46154</v>
+        <v>45740</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7131,7 +7173,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7174,7 +7216,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7188,10 +7230,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45560</v>
+        <v>45758</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7204,7 +7246,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7247,7 +7289,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7261,10 +7303,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46157</v>
+        <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7277,7 +7319,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7320,7 +7362,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7334,10 +7376,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46157</v>
+        <v>45999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7349,8 +7391,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7393,7 +7440,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7407,10 +7454,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46157</v>
+        <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7422,8 +7469,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>2.4</v>
+        <v>19.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7466,7 +7518,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7480,10 +7532,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46161</v>
+        <v>45243</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7495,8 +7547,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7539,7 +7596,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7553,10 +7610,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46161</v>
+        <v>45789</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7569,7 +7626,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7612,7 +7669,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7626,10 +7683,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44662</v>
+        <v>45665</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7642,7 +7699,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7702,7 +7759,7 @@
         <v>46010</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7758,7 +7815,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7772,10 +7829,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45456</v>
+        <v>44844</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7788,7 +7845,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7831,7 +7888,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7845,10 +7902,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45264</v>
+        <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7861,7 +7918,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7904,7 +7961,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7918,10 +7975,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45385</v>
+        <v>44909</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7934,7 +7991,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7977,7 +8034,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 22290-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7991,10 +8048,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45012</v>
+        <v>46154</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8007,7 +8064,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8050,7 +8107,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8064,10 +8121,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44668</v>
+        <v>46154</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8123,7 +8180,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8137,10 +8194,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46030</v>
+        <v>46154</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8153,7 +8210,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.8</v>
+        <v>13.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8196,7 +8253,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8210,10 +8267,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46030</v>
+        <v>45817</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8226,7 +8283,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8269,7 +8326,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8283,10 +8340,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45230</v>
+        <v>46157</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8299,7 +8356,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8342,7 +8399,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8356,10 +8413,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46037</v>
+        <v>44917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8372,7 +8429,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8415,7 +8472,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8429,10 +8486,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45429</v>
+        <v>46157</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8445,7 +8502,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8488,7 +8545,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8502,10 +8559,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45714</v>
+        <v>46157</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8518,7 +8575,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8561,7 +8618,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8575,10 +8632,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45608</v>
+        <v>46161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8591,7 +8648,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8634,7 +8691,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8648,10 +8705,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45434</v>
+        <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8664,7 +8721,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8707,7 +8764,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8721,10 +8778,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44602</v>
+        <v>45092</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8737,7 +8794,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8780,7 +8837,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8794,10 +8851,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46169</v>
+        <v>45264</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8810,7 +8867,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8853,7 +8910,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8867,10 +8924,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45706</v>
+        <v>45747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8883,7 +8940,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8926,7 +8983,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8940,10 +8997,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46078</v>
+        <v>44909</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8956,7 +9013,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -8999,7 +9056,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9013,10 +9070,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46078</v>
+        <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9029,7 +9086,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9072,7 +9129,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9086,10 +9143,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44781</v>
+        <v>46169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9102,7 +9159,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9145,7 +9202,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9159,10 +9216,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46078</v>
+        <v>45109</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9175,7 +9232,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.3</v>
+        <v>5.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9218,7 +9275,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9232,10 +9289,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46177</v>
+        <v>44994</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9248,7 +9305,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9291,7 +9348,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9308,7 +9365,7 @@
         <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9321,7 +9378,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9364,7 +9421,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9381,7 +9438,7 @@
         <v>46177</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9394,7 +9451,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9437,7 +9494,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9454,7 +9511,7 @@
         <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9467,7 +9524,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9510,7 +9567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9524,10 +9581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44512</v>
+        <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9540,7 +9597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9583,7 +9640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9597,10 +9654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46078</v>
+        <v>45408</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9613,7 +9670,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9673,7 +9730,7 @@
         <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9729,7 +9786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9743,10 +9800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46106</v>
+        <v>45012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9758,13 +9815,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9807,7 +9859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9821,10 +9873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45006</v>
+        <v>45264</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9837,7 +9889,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9880,7 +9932,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9894,10 +9946,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44978</v>
+        <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9910,7 +9962,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -9953,7 +10005,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9967,10 +10019,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46122</v>
+        <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9983,7 +10035,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10026,7 +10078,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10040,10 +10092,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44960</v>
+        <v>46195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10057,11 +10109,11 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>14.8</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10104,7 +10156,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10118,10 +10170,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46128</v>
+        <v>44602</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10177,7 +10229,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10191,10 +10243,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45699</v>
+        <v>46204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10207,7 +10259,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10250,7 +10302,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10264,10 +10316,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46132</v>
+        <v>46206</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10280,7 +10332,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10323,7 +10375,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10337,10 +10389,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45379</v>
+        <v>46251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10352,8 +10404,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>6.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10396,7 +10453,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10410,10 +10467,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46195</v>
+        <v>46206</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10423,11 +10480,6 @@
       <c r="G130" t="inlineStr">
         <is>
           <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -10474,7 +10526,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10488,10 +10540,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44988</v>
+        <v>46206</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10504,7 +10556,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10547,7 +10599,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10561,10 +10613,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10577,7 +10629,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10620,7 +10672,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10634,10 +10686,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46206</v>
+        <v>44830</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10650,7 +10702,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10693,7 +10745,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10710,7 +10762,7 @@
         <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10723,7 +10775,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10766,7 +10818,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10783,7 +10835,7 @@
         <v>46206</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10796,7 +10848,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10839,7 +10891,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10853,10 +10905,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46206</v>
+        <v>45608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10869,7 +10921,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10912,7 +10964,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10926,10 +10978,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46206</v>
+        <v>46169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10942,7 +10994,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -10985,7 +11037,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10999,10 +11051,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45243</v>
+        <v>45706</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11014,13 +11066,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11063,7 +11110,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11077,10 +11124,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46251</v>
+        <v>44668</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11092,13 +11139,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11141,7 +11183,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11155,10 +11197,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45109</v>
+        <v>45167</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11171,7 +11213,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11214,7 +11256,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11228,10 +11270,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46206</v>
+        <v>44662</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11244,7 +11286,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11287,7 +11329,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11301,10 +11343,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45408</v>
+        <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11317,7 +11359,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11360,7 +11402,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11374,10 +11416,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44622</v>
+        <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11390,7 +11432,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11433,7 +11475,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11447,10 +11489,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45159</v>
+        <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11463,7 +11505,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11506,7 +11548,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11520,10 +11562,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44790</v>
+        <v>44754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11535,8 +11577,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11579,7 +11626,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11593,10 +11640,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44887</v>
+        <v>45230</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11609,7 +11656,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11652,7 +11699,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11666,10 +11713,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46169</v>
+        <v>44663</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11682,7 +11729,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11725,7 +11772,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11739,10 +11786,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44886</v>
+        <v>45264</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11754,13 +11801,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11803,7 +11845,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11817,10 +11859,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45230</v>
+        <v>45264</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11833,7 +11875,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11876,7 +11918,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11886,14 +11928,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44634</v>
+        <v>46275</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11906,7 +11948,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>10.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11949,7 +11991,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11963,10 +12005,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45194</v>
+        <v>44781</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11979,7 +12021,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12022,7 +12064,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12036,10 +12078,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45145</v>
+        <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12052,7 +12094,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12095,7 +12137,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12109,10 +12151,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46169</v>
+        <v>46275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12125,7 +12167,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12168,7 +12210,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12182,10 +12224,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12198,7 +12240,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12241,7 +12283,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12255,10 +12297,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46169</v>
+        <v>46275</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12271,7 +12313,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12314,7 +12356,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12328,10 +12370,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44909</v>
+        <v>46275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12344,7 +12386,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12387,7 +12429,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12401,10 +12443,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>44909</v>
+        <v>46277</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12417,7 +12459,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12460,7 +12502,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12470,14 +12512,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45187</v>
+        <v>46277</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12489,13 +12531,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12538,7 +12575,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12552,10 +12589,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45699</v>
+        <v>45448</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12568,7 +12605,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12611,7 +12648,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12625,10 +12662,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44994</v>
+        <v>46283</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12640,8 +12677,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12684,7 +12726,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12698,10 +12740,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46275</v>
+        <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12714,7 +12756,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12757,7 +12799,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 39827-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12771,10 +12813,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12786,8 +12828,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12830,7 +12877,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12844,10 +12891,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46275</v>
+        <v>44790</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12860,7 +12907,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12903,7 +12950,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 39760-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12917,10 +12964,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12932,8 +12979,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -12976,7 +13028,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 39770-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12990,10 +13042,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13005,8 +13057,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13049,7 +13106,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 39733-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13063,10 +13120,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45253</v>
+        <v>46289</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13078,8 +13135,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I166" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13122,7 +13184,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 39828-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13136,10 +13198,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45341</v>
+        <v>46289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13151,8 +13213,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13195,7 +13262,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 39819-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13205,14 +13272,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46275</v>
+        <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13224,8 +13291,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>10.2</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13268,7 +13340,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 39800-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13282,10 +13354,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46277</v>
+        <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13297,8 +13369,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13341,7 +13418,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 39739-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13355,10 +13432,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46277</v>
+        <v>46289</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13370,8 +13447,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13414,7 +13496,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13428,10 +13510,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44530</v>
+        <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13443,8 +13525,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13487,7 +13574,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13501,10 +13588,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45448</v>
+        <v>45593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13517,7 +13604,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13560,7 +13647,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13574,10 +13661,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45747</v>
+        <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13590,7 +13677,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13633,7 +13720,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13647,10 +13734,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46283</v>
+        <v>45232</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13662,13 +13749,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13711,7 +13793,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13725,10 +13807,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45632</v>
+        <v>44960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13740,8 +13822,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>3.8</v>
+        <v>14.8</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13784,7 +13871,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13798,10 +13885,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45615</v>
+        <v>44494</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13814,7 +13901,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13857,7 +13944,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13871,10 +13958,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45012</v>
+        <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13887,7 +13974,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13930,7 +14017,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13944,10 +14031,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45629</v>
+        <v>45679</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13960,7 +14047,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14003,7 +14090,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14017,10 +14104,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45184</v>
+        <v>44622</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14033,7 +14120,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14076,7 +14163,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14090,10 +14177,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45628</v>
+        <v>45456</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14106,7 +14193,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14149,7 +14236,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14163,10 +14250,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44966</v>
+        <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14179,7 +14266,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14222,7 +14309,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14236,10 +14323,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45660</v>
+        <v>45209</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14252,7 +14339,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14295,7 +14382,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14309,10 +14396,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45290</v>
+        <v>44988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14325,7 +14412,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14368,7 +14455,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14382,10 +14469,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45588</v>
+        <v>45194</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14398,7 +14485,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14441,7 +14528,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14455,10 +14542,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45547</v>
+        <v>45368</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14470,13 +14557,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14516,10 +14598,10 @@
       </c>
       <c r="V185" s="2" t="inlineStr"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14533,10 +14615,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44886</v>
+        <v>44530</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14548,13 +14630,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>19.4</v>
+        <v>4.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14593,6 +14670,663 @@
         <v>0</v>
       </c>
       <c r="V186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187" ht="15" customHeight="1">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>A 9238-2025</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="n">
+        <v>45714</v>
+      </c>
+      <c r="E187" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0</v>
+      </c>
+      <c r="S187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
+        <v>0</v>
+      </c>
+      <c r="U187" t="n">
+        <v>0</v>
+      </c>
+      <c r="V187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188" ht="15" customHeight="1">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>A 37601-2023</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="n">
+        <v>45159</v>
+      </c>
+      <c r="E188" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" s="2" t="inlineStr"/>
+    </row>
+    <row r="189" ht="15" customHeight="1">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>A 6493-2025</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="n">
+        <v>45699</v>
+      </c>
+      <c r="E189" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0</v>
+      </c>
+      <c r="S189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
+        <v>0</v>
+      </c>
+      <c r="U189" t="n">
+        <v>0</v>
+      </c>
+      <c r="V189" s="2" t="inlineStr"/>
+    </row>
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>A 5752-2025</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="n">
+        <v>45694</v>
+      </c>
+      <c r="E190" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0</v>
+      </c>
+      <c r="S190" t="n">
+        <v>0</v>
+      </c>
+      <c r="T190" t="n">
+        <v>0</v>
+      </c>
+      <c r="U190" t="n">
+        <v>0</v>
+      </c>
+      <c r="V190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>A 59270-2023</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="n">
+        <v>45253</v>
+      </c>
+      <c r="E191" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0</v>
+      </c>
+      <c r="S191" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" t="n">
+        <v>0</v>
+      </c>
+      <c r="V191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192" ht="15" customHeight="1">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>A 54054-2024</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="n">
+        <v>45615</v>
+      </c>
+      <c r="E192" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I192" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193" ht="15" customHeight="1">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>A 14413-2023</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="n">
+        <v>45012</v>
+      </c>
+      <c r="E193" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194" ht="15" customHeight="1">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>A 57256-2024</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>45629</v>
+      </c>
+      <c r="E194" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>A 58241-2024</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>45632</v>
+      </c>
+      <c r="E195" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I195" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45666</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45625</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45341</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45397</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45230</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45385</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44966</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>46030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45660</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>46037</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45919</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44974</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>45560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>46078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>46078</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45358</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>46078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45933</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>46078</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45187</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45952</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45264</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45962</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>46122</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>46128</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45986</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45983</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45983</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45740</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45758</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45243</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45789</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45665</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>46010</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44844</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44909</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>46154</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>46154</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46154</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45817</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46157</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46157</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>46157</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>46161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45092</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45264</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44909</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>46169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45109</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44994</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46177</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45408</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45264</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44602</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>46204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46206</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>46251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46206</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>46206</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>46206</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44830</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46206</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45706</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44668</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45167</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44662</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45230</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44663</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45264</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45264</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>46275</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44781</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>46275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46275</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>46275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46277</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>46277</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45448</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>46283</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>46289</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44790</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>46289</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>46289</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>46289</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>46289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>46289</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45232</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44494</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45679</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44622</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45456</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45209</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45194</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45368</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44530</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45714</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45159</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45699</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45694</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45253</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45615</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45012</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45629</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45632</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45666</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>45198</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>46289</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>45625</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45341</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45397</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         <v>45230</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>45385</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3548,7 +3548,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>44582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>44582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>44966</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>45588</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         <v>46030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44886</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>45660</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>45184</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>46030</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4507,7 +4507,7 @@
         <v>45883</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
         <v>45883</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>44512</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>46037</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
         <v>45919</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>44671</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>44974</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
         <v>45560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>46078</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>46078</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>45358</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>46078</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45933</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>46078</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45006</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45187</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45952</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>46106</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45264</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
         <v>45962</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>44909</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45965</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6571,7 +6571,7 @@
         <v>46122</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>45000</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>46128</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>46132</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6863,7 +6863,7 @@
         <v>45512</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
         <v>45986</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>45983</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>45983</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>45740</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>45758</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44886</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>45243</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         <v>45789</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         <v>45665</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>46010</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44844</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7905,7 +7905,7 @@
         <v>45111</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         <v>44909</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>46154</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>46154</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>46154</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45817</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>46157</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>44917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46157</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>46157</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>46161</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45092</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45264</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44909</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>44909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>46169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45109</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>44994</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>46177</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>46177</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45408</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45264</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>46195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44602</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>46204</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46206</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>46251</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>46206</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>46206</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>46206</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44830</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46206</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>45608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>46169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>45706</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44668</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>45167</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44662</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44754</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45230</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44663</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45264</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45264</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>46275</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44781</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>46275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>46275</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>46275</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>46277</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>46277</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>45448</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>46283</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>46289</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44790</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>46289</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>46289</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>46289</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>46289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13357,7 +13357,7 @@
         <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>46289</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45614</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>45593</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13664,7 +13664,7 @@
         <v>44634</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45232</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44494</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45145</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>45679</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44622</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45456</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         <v>45434</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45209</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44988</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45194</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>45368</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>44530</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14691,7 +14691,7 @@
         <v>45714</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45159</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>45699</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>45694</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14983,7 +14983,7 @@
         <v>45253</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15056,7 +15056,7 @@
         <v>45615</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15129,7 +15129,7 @@
         <v>45012</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45629</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>45632</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE195"/>
+  <dimension ref="A1:AE194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45666</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39832-2026</t>
+          <t>A 56463-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46289</v>
+        <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>12.2</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1775,148 +1775,148 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 39832-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 39832-2026 artfynd.xlsx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 39832-2026 karta.png", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 39832-2026 georefererad karta.tif", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 39832-2026 FSC-klagomål.docx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 39832-2026 FSC-klagomål mail.docx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 39832-2026 tillsynsbegäran.docx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 39832-2026 tillsynsbegäran mail.docx", "A 39832-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 56463-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Scharlakansskål</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 46192-2022</t>
+          <t>A 63811-2021</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44847</v>
+        <v>44509</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 63811-2021</t>
+          <t>A 46192-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44509</v>
+        <v>44847</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44760</v>
+        <v>45264</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45341</v>
+        <v>45264</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45397</v>
+        <v>44844</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45230</v>
+        <v>44974</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,8 +3414,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.5</v>
+        <v>14.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3463,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3477,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45385</v>
+        <v>45209</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3493,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3536,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45379</v>
+        <v>45665</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3566,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3609,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,10 +3623,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44582</v>
+        <v>45184</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3639,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3682,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44582</v>
+        <v>45628</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3712,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3755,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,10 +3769,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45290</v>
+        <v>44966</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3785,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3828,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3837,10 +3842,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44966</v>
+        <v>45660</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3858,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45588</v>
+        <v>45290</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3926,7 +3931,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3969,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3983,10 +3988,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46030</v>
+        <v>45588</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3999,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4042,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4056,10 +4061,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44886</v>
+        <v>45358</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4071,13 +4076,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45660</v>
+        <v>45547</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,8 +4149,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4193,7 +4198,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4207,10 +4212,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45628</v>
+        <v>46010</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4223,7 +4228,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4266,7 +4271,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4280,10 +4285,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45184</v>
+        <v>44917</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4296,7 +4301,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.2</v>
+        <v>10.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4339,7 +4344,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4353,10 +4358,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45547</v>
+        <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,13 +4373,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46030</v>
+        <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,8 +4446,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>19.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4490,7 +4495,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45883</v>
+        <v>45919</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4520,7 +4525,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4563,7 +4568,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4577,10 +4582,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45883</v>
+        <v>45919</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4593,7 +4598,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9.199999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4636,7 +4641,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4650,10 +4655,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44512</v>
+        <v>45919</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4666,7 +4671,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4709,7 +4714,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4723,10 +4728,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46037</v>
+        <v>45264</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4739,7 +4744,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9.1</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4782,7 +4787,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4796,10 +4801,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45699</v>
+        <v>45919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4812,7 +4817,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4855,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4869,10 +4874,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45919</v>
+        <v>45232</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4885,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4928,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4942,10 +4947,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45919</v>
+        <v>45933</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4958,7 +4963,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5001,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45919</v>
+        <v>45952</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5031,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5074,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5088,10 +5093,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45919</v>
+        <v>46030</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5104,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5147,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5161,10 +5166,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44526</v>
+        <v>46030</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5177,7 +5182,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5220,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5234,10 +5239,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44671</v>
+        <v>45965</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5249,8 +5254,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>11.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5293,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5307,10 +5317,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44974</v>
+        <v>45962</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5322,13 +5332,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>14.1</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5371,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5385,10 +5390,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45560</v>
+        <v>44671</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5401,7 +5406,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5444,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46078</v>
+        <v>45694</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5474,7 +5479,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5517,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5531,10 +5536,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46078</v>
+        <v>44582</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5604,10 +5609,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45358</v>
+        <v>44582</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5620,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5663,7 +5668,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5677,10 +5682,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46078</v>
+        <v>45883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5693,7 +5698,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5736,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44887</v>
+        <v>45000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5771,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5823,10 +5828,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45933</v>
+        <v>45883</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5839,7 +5844,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5887,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5901,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46078</v>
+        <v>46037</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5917,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>9.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5960,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5969,10 +5974,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45006</v>
+        <v>44663</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5990,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6033,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6038,14 +6043,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45187</v>
+        <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6057,13 +6062,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45952</v>
+        <v>45983</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>6.1</v>
+        <v>13.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46106</v>
+        <v>45167</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6208,13 +6208,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6257,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6267,14 +6262,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45264</v>
+        <v>45512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6287,7 +6282,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6330,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45962</v>
+        <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6360,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6403,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6417,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44909</v>
+        <v>45983</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6433,7 +6428,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6476,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6490,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45965</v>
+        <v>45986</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6507,11 +6502,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>11.6</v>
+        <v>7.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6554,7 +6549,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6568,10 +6563,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46122</v>
+        <v>45593</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6584,7 +6579,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.4</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6627,7 +6622,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6641,10 +6636,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45000</v>
+        <v>45999</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6656,8 +6651,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>8.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6700,7 +6700,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46128</v>
+        <v>45614</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6729,8 +6729,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6773,7 +6778,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6787,10 +6792,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46132</v>
+        <v>45397</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6803,7 +6808,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6846,7 +6851,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6856,14 +6861,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45512</v>
+        <v>44909</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6876,7 +6881,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6919,7 +6924,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6933,10 +6938,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45986</v>
+        <v>45264</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6948,13 +6953,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>7.7</v>
+        <v>6.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6997,7 +6997,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7011,10 +7011,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45983</v>
+        <v>46078</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7070,7 +7070,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45983</v>
+        <v>46078</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>13.2</v>
+        <v>0.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7143,7 +7143,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7157,10 +7157,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45740</v>
+        <v>46078</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.8</v>
+        <v>0.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7216,7 +7216,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7230,10 +7230,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45758</v>
+        <v>44526</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7289,7 +7289,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7303,10 +7303,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45741</v>
+        <v>45111</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7362,7 +7362,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45999</v>
+        <v>44760</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7391,13 +7391,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>8.6</v>
+        <v>0.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7440,7 +7435,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7454,10 +7449,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44886</v>
+        <v>46078</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7469,13 +7464,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>19.4</v>
+        <v>1.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7518,7 +7508,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7532,10 +7522,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45243</v>
+        <v>45679</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7547,13 +7537,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7596,7 +7581,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7610,10 +7595,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45789</v>
+        <v>46106</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7625,8 +7610,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7669,7 +7659,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7683,10 +7673,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45665</v>
+        <v>44754</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7698,8 +7688,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7742,7 +7737,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7756,10 +7751,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46010</v>
+        <v>45368</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7772,7 +7767,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7815,7 +7810,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7829,10 +7824,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44844</v>
+        <v>46122</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7845,7 +7840,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7888,7 +7883,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7902,10 +7897,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45111</v>
+        <v>46128</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7918,7 +7913,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7961,7 +7956,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7975,10 +7970,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44909</v>
+        <v>45092</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7991,7 +7986,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8034,7 +8029,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 22290-2026</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8048,10 +8043,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46154</v>
+        <v>44909</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8064,7 +8059,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8107,7 +8102,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8121,10 +8116,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46154</v>
+        <v>45758</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8137,7 +8132,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8180,7 +8175,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8194,10 +8189,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46154</v>
+        <v>45560</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8210,7 +8205,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>13.6</v>
+        <v>2.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8253,7 +8248,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8267,10 +8262,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45817</v>
+        <v>44662</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8283,7 +8278,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8326,7 +8321,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8340,10 +8335,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46157</v>
+        <v>45740</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8356,7 +8351,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8399,7 +8394,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8413,10 +8408,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44917</v>
+        <v>45741</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8429,7 +8424,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>10.9</v>
+        <v>1.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8472,7 +8467,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8486,10 +8481,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46157</v>
+        <v>45456</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8502,7 +8497,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8545,7 +8540,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8559,10 +8554,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46157</v>
+        <v>45264</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8575,7 +8570,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8618,7 +8613,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8632,10 +8627,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46161</v>
+        <v>45385</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8648,7 +8643,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8691,7 +8686,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8705,10 +8700,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>46161</v>
+        <v>45012</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8721,7 +8716,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8764,7 +8759,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8778,10 +8773,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45092</v>
+        <v>44668</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8794,7 +8789,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8837,7 +8832,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45264</v>
+        <v>45789</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8867,7 +8862,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8910,7 +8905,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45747</v>
+        <v>45230</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8940,7 +8935,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8983,7 +8978,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8997,10 +8992,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44909</v>
+        <v>45429</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9013,7 +9008,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9056,7 +9051,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9070,10 +9065,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44909</v>
+        <v>45714</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9086,7 +9081,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9129,7 +9124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46169</v>
+        <v>45608</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9159,7 +9154,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9202,7 +9197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9216,10 +9211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45109</v>
+        <v>45434</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9232,7 +9227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.9</v>
+        <v>3.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9275,7 +9270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44994</v>
+        <v>44602</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9305,7 +9300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9348,7 +9343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46177</v>
+        <v>45817</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9378,7 +9373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9421,7 +9416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9435,10 +9430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46177</v>
+        <v>45706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9451,7 +9446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9494,7 +9489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46177</v>
+        <v>46154</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9524,7 +9519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.3</v>
+        <v>13.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9567,7 +9562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9581,10 +9576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46177</v>
+        <v>46154</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9597,7 +9592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9640,7 +9635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9654,10 +9649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45408</v>
+        <v>46157</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9670,7 +9665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9713,7 +9708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9727,10 +9722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46181</v>
+        <v>46157</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9743,7 +9738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9786,7 +9781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9800,10 +9795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45012</v>
+        <v>46157</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9816,7 +9811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9859,7 +9854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9873,10 +9868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45264</v>
+        <v>46161</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9889,7 +9884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4.7</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9932,7 +9927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9946,10 +9941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44516</v>
+        <v>46161</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9962,7 +9957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10005,7 +10000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45429</v>
+        <v>44781</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10078,7 +10073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10092,10 +10087,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46195</v>
+        <v>44512</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10107,13 +10102,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10156,7 +10146,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10170,10 +10160,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44602</v>
+        <v>46169</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10186,7 +10176,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10229,7 +10219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10243,10 +10233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46204</v>
+        <v>46177</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10259,7 +10249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10302,7 +10292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10316,10 +10306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46206</v>
+        <v>46177</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10332,7 +10322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10375,7 +10365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10389,10 +10379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46251</v>
+        <v>46177</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10404,13 +10394,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>6.7</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10453,7 +10438,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10467,10 +10452,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46206</v>
+        <v>46177</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10483,7 +10468,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10526,7 +10511,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10540,10 +10525,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46206</v>
+        <v>45006</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10556,7 +10541,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10599,7 +10584,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10613,10 +10598,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46206</v>
+        <v>44978</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10629,7 +10614,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>3.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10672,7 +10657,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10686,10 +10671,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44830</v>
+        <v>46181</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10702,7 +10687,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10745,7 +10730,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10759,10 +10744,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46206</v>
+        <v>44960</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10774,8 +10759,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>14.8</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10818,7 +10808,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10832,10 +10822,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46206</v>
+        <v>45699</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10848,7 +10838,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10891,7 +10881,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10905,10 +10895,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45608</v>
+        <v>45379</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10921,7 +10911,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10964,7 +10954,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10978,10 +10968,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46169</v>
+        <v>44988</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10984,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11037,7 +11027,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11051,10 +11041,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45706</v>
+        <v>46195</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11066,8 +11056,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11110,7 +11105,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11124,10 +11119,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44668</v>
+        <v>45243</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11139,8 +11134,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11183,7 +11183,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11197,10 +11197,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45167</v>
+        <v>45109</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11256,7 +11256,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44662</v>
+        <v>46204</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46265</v>
+        <v>45408</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11402,7 +11402,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11416,10 +11416,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46169</v>
+        <v>46206</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11475,7 +11475,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11489,10 +11489,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46169</v>
+        <v>46206</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11548,7 +11548,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11562,10 +11562,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44754</v>
+        <v>44622</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11577,13 +11577,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11626,7 +11621,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11640,10 +11635,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45230</v>
+        <v>46206</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11656,7 +11651,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11699,7 +11694,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11713,10 +11708,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44663</v>
+        <v>46206</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11729,7 +11724,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11772,7 +11767,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11786,10 +11781,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45264</v>
+        <v>46206</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11802,7 +11797,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11845,7 +11840,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11859,10 +11854,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45264</v>
+        <v>46206</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11875,7 +11870,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11918,7 +11913,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11928,14 +11923,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46275</v>
+        <v>45159</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11948,7 +11943,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>10.2</v>
+        <v>7.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11991,7 +11986,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12005,10 +12000,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44781</v>
+        <v>44790</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12021,7 +12016,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12064,7 +12059,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12078,10 +12073,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46275</v>
+        <v>44887</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12094,7 +12089,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12137,7 +12132,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12151,10 +12146,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46275</v>
+        <v>44886</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12166,8 +12161,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12210,7 +12210,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12224,10 +12224,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46275</v>
+        <v>45230</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12283,7 +12283,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46275</v>
+        <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12356,7 +12356,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12370,10 +12370,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46275</v>
+        <v>44634</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12429,7 +12429,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12443,10 +12443,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46277</v>
+        <v>45194</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12502,7 +12502,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12516,10 +12516,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46277</v>
+        <v>45145</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12575,7 +12575,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12589,10 +12589,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45448</v>
+        <v>44909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12648,7 +12648,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46283</v>
+        <v>44909</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12677,13 +12677,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12726,7 +12721,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12740,10 +12735,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44978</v>
+        <v>46169</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12756,7 +12751,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12799,7 +12794,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 39827-2026</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12813,10 +12808,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46289</v>
+        <v>46265</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12828,13 +12823,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12877,7 +12867,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12887,14 +12877,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44790</v>
+        <v>45187</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12906,8 +12896,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12950,7 +12945,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 39760-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12964,10 +12959,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46289</v>
+        <v>46169</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12979,13 +12974,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>9.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13028,7 +13018,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 39770-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13042,10 +13032,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46289</v>
+        <v>45699</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13057,13 +13047,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13106,7 +13091,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 39733-2026</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13120,10 +13105,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46289</v>
+        <v>44994</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13135,13 +13120,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13184,7 +13164,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 39828-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13198,10 +13178,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46289</v>
+        <v>45253</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13213,13 +13193,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I167" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13262,7 +13237,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 39819-2026</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13276,10 +13251,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46289</v>
+        <v>45341</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13291,13 +13266,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13340,7 +13310,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 39800-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13354,10 +13324,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13369,13 +13339,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13418,7 +13383,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 39739-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13432,10 +13397,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13447,13 +13412,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13496,7 +13456,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13510,10 +13470,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45614</v>
+        <v>46275</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13525,13 +13485,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13574,7 +13529,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13588,10 +13543,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45593</v>
+        <v>46275</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13604,7 +13559,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13647,7 +13602,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13661,10 +13616,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44634</v>
+        <v>46275</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13677,7 +13632,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13720,7 +13675,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13734,10 +13689,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45232</v>
+        <v>44530</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13750,7 +13705,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13793,7 +13748,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13807,10 +13762,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44960</v>
+        <v>45448</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13822,13 +13777,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>14.8</v>
+        <v>2.6</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13871,7 +13821,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13881,14 +13831,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44494</v>
+        <v>46275</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13901,7 +13851,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13944,7 +13894,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13958,10 +13908,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45145</v>
+        <v>46277</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14017,7 +13967,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14031,10 +13981,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45679</v>
+        <v>46277</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14047,7 +13997,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14090,7 +14040,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14104,10 +14054,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44622</v>
+        <v>45747</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14120,7 +14070,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14163,7 +14113,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14177,10 +14127,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45456</v>
+        <v>45632</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14193,7 +14143,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14236,7 +14186,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14250,10 +14200,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45434</v>
+        <v>45615</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14266,7 +14216,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14309,7 +14259,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14323,10 +14273,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45209</v>
+        <v>46283</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14338,8 +14288,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14382,7 +14337,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14396,10 +14351,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44988</v>
+        <v>45012</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14412,7 +14367,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14455,7 +14410,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14469,10 +14424,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45194</v>
+        <v>45629</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14485,7 +14440,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14528,7 +14483,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 39733-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14542,10 +14497,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45368</v>
+        <v>46289</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14557,8 +14512,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14601,7 +14561,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 39760-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14615,10 +14575,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44530</v>
+        <v>46289</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14630,8 +14590,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14674,7 +14639,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14688,10 +14653,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45714</v>
+        <v>46132</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14704,7 +14669,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14747,7 +14712,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 39828-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14761,10 +14726,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45159</v>
+        <v>46289</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14776,8 +14741,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14820,7 +14790,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 39827-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14834,10 +14804,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45699</v>
+        <v>46289</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14849,8 +14819,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.3</v>
+        <v>3.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14893,7 +14868,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 39819-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14907,10 +14882,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45694</v>
+        <v>46289</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14922,8 +14897,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14966,7 +14946,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 39800-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14980,10 +14960,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45253</v>
+        <v>46289</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14995,8 +14975,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>4.3</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15039,7 +15024,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15053,10 +15038,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45615</v>
+        <v>46251</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15068,8 +15053,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>3.2</v>
+        <v>6.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15112,7 +15102,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 39739-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15126,10 +15116,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45012</v>
+        <v>46289</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15141,8 +15131,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15182,10 +15177,10 @@
       </c>
       <c r="V193" s="2" t="inlineStr"/>
     </row>
-    <row r="194" ht="15" customHeight="1">
+    <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 39770-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15199,10 +15194,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45629</v>
+        <v>46289</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15214,8 +15209,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -15254,79 +15254,6 @@
         <v>0</v>
       </c>
       <c r="V194" s="2" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>A 58241-2024</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D195" s="1" t="n">
-        <v>45632</v>
-      </c>
-      <c r="E195" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I195" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J195" t="n">
-        <v>0</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" t="n">
-        <v>0</v>
-      </c>
-      <c r="N195" t="n">
-        <v>0</v>
-      </c>
-      <c r="O195" t="n">
-        <v>0</v>
-      </c>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0</v>
-      </c>
-      <c r="S195" t="n">
-        <v>0</v>
-      </c>
-      <c r="T195" t="n">
-        <v>0</v>
-      </c>
-      <c r="U195" t="n">
-        <v>0</v>
-      </c>
-      <c r="V195" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45666</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46674-2023</t>
+          <t>A 20064-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45198</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46674-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45198</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20064-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 63811-2021</t>
+          <t>A 46192-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44509</v>
+        <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 46192-2022</t>
+          <t>A 63811-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44847</v>
+        <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
         <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 69169-2021</t>
+          <t>A 16116-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44530</v>
+        <v>44665</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16116-2022</t>
+          <t>A 69169-2021</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44665</v>
+        <v>44530</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45264</v>
+        <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45264</v>
+        <v>45341</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44844</v>
+        <v>45230</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44974</v>
+        <v>45397</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3414,13 +3414,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>14.1</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3463,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3477,10 +3472,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45209</v>
+        <v>45385</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3493,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3536,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45665</v>
+        <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3566,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3609,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3623,10 +3618,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45184</v>
+        <v>45290</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3639,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3682,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45628</v>
+        <v>44966</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3712,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3755,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3769,10 +3764,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44966</v>
+        <v>45588</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3785,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3845,7 +3840,7 @@
         <v>45660</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3901,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3915,10 +3910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45290</v>
+        <v>44582</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3931,7 +3926,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3974,7 +3969,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3988,10 +3983,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45588</v>
+        <v>44582</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4004,7 +3999,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4047,7 +4042,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4061,10 +4056,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45358</v>
+        <v>45628</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4077,7 +4072,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4120,7 +4115,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4134,10 +4129,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45547</v>
+        <v>45184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4149,13 +4144,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4198,7 +4188,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4212,10 +4202,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46010</v>
+        <v>44886</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4227,8 +4217,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4271,7 +4266,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4285,10 +4280,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44917</v>
+        <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4301,7 +4296,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10.9</v>
+        <v>0.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4344,7 +4339,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4358,10 +4353,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44494</v>
+        <v>45547</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4373,8 +4368,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44886</v>
+        <v>45883</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,13 +4446,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>19.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4495,7 +4490,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4509,10 +4504,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45919</v>
+        <v>46030</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4525,7 +4520,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4568,7 +4563,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4582,10 +4577,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45919</v>
+        <v>44512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4598,7 +4593,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4641,7 +4636,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4655,10 +4650,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45919</v>
+        <v>46030</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4671,7 +4666,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4714,7 +4709,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4728,10 +4723,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45264</v>
+        <v>44886</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4743,8 +4738,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>2.2</v>
+        <v>19.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4787,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45919</v>
+        <v>46037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>9.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4874,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45232</v>
+        <v>45699</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4933,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45933</v>
+        <v>44526</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5006,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45952</v>
+        <v>44671</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5079,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,10 +5093,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46030</v>
+        <v>45919</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46030</v>
+        <v>44974</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5181,8 +5181,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>14.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5230,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5239,10 +5244,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45965</v>
+        <v>45919</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5254,13 +5259,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>11.6</v>
+        <v>0.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5303,7 +5303,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45962</v>
+        <v>45919</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5390,10 +5390,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44671</v>
+        <v>45919</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5449,7 +5449,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45694</v>
+        <v>45560</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5536,10 +5536,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44582</v>
+        <v>45358</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5595,7 +5595,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5609,10 +5609,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44582</v>
+        <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>2.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5668,7 +5668,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45883</v>
+        <v>45933</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5755,10 +5755,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45000</v>
+        <v>45006</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5824,14 +5824,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45883</v>
+        <v>45187</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5843,8 +5843,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.199999999999999</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5887,7 +5892,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5901,10 +5906,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46037</v>
+        <v>45952</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5917,7 +5922,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5960,7 +5965,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5974,10 +5979,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44663</v>
+        <v>45264</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5990,7 +5995,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6033,7 +6038,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6047,10 +6052,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44516</v>
+        <v>45962</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6063,7 +6068,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6111,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6125,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45983</v>
+        <v>44909</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6141,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>13.2</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6184,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6198,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45167</v>
+        <v>45965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6208,8 +6213,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>11.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6262,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6262,14 +6272,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45512</v>
+        <v>45000</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6282,7 +6292,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6335,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6335,14 +6345,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44830</v>
+        <v>45512</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6355,7 +6365,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6408,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6412,10 +6422,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45983</v>
+        <v>45986</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6427,8 +6437,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.6</v>
+        <v>7.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6486,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6500,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45986</v>
+        <v>45983</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6500,13 +6515,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6549,7 +6559,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6563,10 +6573,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45593</v>
+        <v>45983</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6579,7 +6589,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>13.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6622,7 +6632,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6636,10 +6646,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45999</v>
+        <v>46078</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6651,13 +6661,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>8.6</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6700,7 +6705,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6714,10 +6719,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45614</v>
+        <v>46078</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6729,13 +6734,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6792,10 +6792,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45397</v>
+        <v>46078</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6851,7 +6851,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44909</v>
+        <v>45999</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6880,8 +6880,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6924,7 +6929,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6938,10 +6943,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45264</v>
+        <v>45243</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6953,8 +6958,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6997,7 +7007,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7014,7 +7024,7 @@
         <v>46078</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7027,7 +7037,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7070,7 +7080,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7084,10 +7094,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46078</v>
+        <v>46010</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7100,7 +7110,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7143,7 +7153,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7157,10 +7167,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46078</v>
+        <v>45665</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7173,7 +7183,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7216,7 +7226,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7230,10 +7240,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44526</v>
+        <v>44844</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7246,7 +7256,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7306,7 +7316,7 @@
         <v>45111</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7362,7 +7372,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7376,10 +7386,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44760</v>
+        <v>46106</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7391,8 +7401,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7435,7 +7450,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7449,10 +7464,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46078</v>
+        <v>46122</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7465,7 +7480,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7508,7 +7523,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7522,10 +7537,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45679</v>
+        <v>46128</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7538,7 +7553,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7581,7 +7596,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7595,10 +7610,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46106</v>
+        <v>44917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7610,13 +7625,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>10.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7659,7 +7669,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7673,10 +7683,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44754</v>
+        <v>45092</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7688,13 +7698,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7737,7 +7742,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7751,10 +7756,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45368</v>
+        <v>45264</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7767,7 +7772,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7810,7 +7815,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7824,10 +7829,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>46122</v>
+        <v>45740</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7840,7 +7845,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7883,7 +7888,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7897,10 +7902,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>46128</v>
+        <v>45747</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7913,7 +7918,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7956,7 +7961,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7970,10 +7975,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45092</v>
+        <v>45758</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7986,7 +7991,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8029,7 +8034,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8046,7 +8051,7 @@
         <v>44909</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8102,7 +8107,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8116,10 +8121,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45758</v>
+        <v>44909</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8132,7 +8137,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8175,7 +8180,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8189,10 +8194,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45560</v>
+        <v>45741</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8205,7 +8210,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8248,7 +8253,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8262,10 +8267,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44662</v>
+        <v>45789</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8278,7 +8283,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8321,7 +8326,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8335,10 +8340,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45740</v>
+        <v>45109</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8351,7 +8356,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8394,7 +8399,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8408,10 +8413,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45741</v>
+        <v>44994</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8424,7 +8429,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8467,7 +8472,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8481,10 +8486,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45456</v>
+        <v>45408</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8497,7 +8502,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8540,7 +8545,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8554,10 +8559,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45264</v>
+        <v>45012</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8570,7 +8575,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8613,7 +8618,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8627,10 +8632,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45385</v>
+        <v>45264</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8643,7 +8648,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8686,7 +8691,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8700,10 +8705,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45012</v>
+        <v>44909</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8716,7 +8721,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8759,7 +8764,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8773,10 +8778,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44668</v>
+        <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8789,7 +8794,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8832,7 +8837,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45789</v>
+        <v>45429</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8862,7 +8867,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8905,7 +8910,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8919,10 +8924,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45230</v>
+        <v>44602</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8935,7 +8940,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8978,7 +8983,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8992,10 +8997,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45429</v>
+        <v>46154</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9008,7 +9013,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9051,7 +9056,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9065,10 +9070,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45714</v>
+        <v>46154</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9081,7 +9086,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.8</v>
+        <v>13.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9124,7 +9129,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45608</v>
+        <v>45817</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9154,7 +9159,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9197,7 +9202,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9211,10 +9216,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45434</v>
+        <v>46157</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9227,7 +9232,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9270,7 +9275,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44602</v>
+        <v>44830</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9300,7 +9305,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9343,7 +9348,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45817</v>
+        <v>46157</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9373,7 +9378,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9416,7 +9421,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9430,10 +9435,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45706</v>
+        <v>46157</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9446,7 +9451,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9489,7 +9494,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9519,7 +9524,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>13.6</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9562,7 +9567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9576,10 +9581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9592,7 +9597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9635,7 +9640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9649,10 +9654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46157</v>
+        <v>45608</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9665,7 +9670,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9708,7 +9713,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9722,10 +9727,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46157</v>
+        <v>45706</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9738,7 +9743,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9781,7 +9786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9795,10 +9800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9811,7 +9816,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9854,7 +9859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9868,10 +9873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46161</v>
+        <v>44668</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9884,7 +9889,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9927,7 +9932,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9941,10 +9946,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46161</v>
+        <v>45167</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9957,7 +9962,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10000,7 +10005,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10014,10 +10019,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44781</v>
+        <v>44662</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10030,7 +10035,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10073,7 +10078,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10087,10 +10092,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44512</v>
+        <v>46177</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10103,7 +10108,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10146,7 +10151,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10160,10 +10165,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46169</v>
+        <v>46177</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10176,7 +10181,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10219,7 +10224,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10236,7 +10241,7 @@
         <v>46177</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10249,7 +10254,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10292,7 +10297,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10309,7 +10314,7 @@
         <v>46177</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10322,7 +10327,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10365,7 +10370,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10379,10 +10384,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10395,7 +10400,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10438,7 +10443,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10452,10 +10457,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46177</v>
+        <v>44754</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10467,8 +10472,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10511,7 +10521,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10525,10 +10535,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45006</v>
+        <v>45230</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10541,7 +10551,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10584,7 +10594,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10598,10 +10608,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44978</v>
+        <v>44663</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10614,7 +10624,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10657,7 +10667,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10671,10 +10681,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46181</v>
+        <v>45264</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10687,7 +10697,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10730,7 +10740,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10744,10 +10754,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>44960</v>
+        <v>45264</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10759,13 +10769,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>14.8</v>
+        <v>6.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10808,7 +10813,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10822,10 +10827,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45699</v>
+        <v>44781</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10838,7 +10843,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10881,7 +10886,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10895,10 +10900,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45379</v>
+        <v>46195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10910,8 +10915,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10954,7 +10964,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10968,10 +10978,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44988</v>
+        <v>45448</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10984,7 +10994,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11027,7 +11037,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11041,10 +11051,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46195</v>
+        <v>46204</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11056,13 +11066,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11105,7 +11110,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11119,10 +11124,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45243</v>
+        <v>46206</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11134,13 +11139,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11183,7 +11183,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11197,10 +11197,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45109</v>
+        <v>46206</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11256,7 +11256,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46204</v>
+        <v>44978</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45408</v>
+        <v>46206</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11359,7 +11359,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11402,7 +11402,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11419,7 +11419,7 @@
         <v>46206</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11475,7 +11475,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11492,7 +11492,7 @@
         <v>46206</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11548,7 +11548,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11562,10 +11562,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44622</v>
+        <v>46206</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11635,10 +11635,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46206</v>
+        <v>44790</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11694,7 +11694,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11708,10 +11708,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46206</v>
+        <v>46169</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11767,7 +11767,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46206</v>
+        <v>45614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11796,8 +11796,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11840,7 +11845,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11854,10 +11859,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46206</v>
+        <v>45593</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11870,7 +11875,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11913,7 +11918,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11927,10 +11932,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45159</v>
+        <v>44634</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11943,7 +11948,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>7.3</v>
+        <v>1.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11986,7 +11991,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12000,10 +12005,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44790</v>
+        <v>45232</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12016,7 +12021,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12059,7 +12064,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12073,10 +12078,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44887</v>
+        <v>44960</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12088,8 +12093,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12132,7 +12142,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12146,10 +12156,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44886</v>
+        <v>44494</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12161,13 +12171,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12210,7 +12215,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12224,10 +12229,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45230</v>
+        <v>46265</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12240,7 +12245,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12283,7 +12288,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12300,7 +12305,7 @@
         <v>46169</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12313,7 +12318,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12356,7 +12361,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12370,10 +12375,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>44634</v>
+        <v>46169</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12429,7 +12434,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12443,10 +12448,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45194</v>
+        <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12459,7 +12464,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12502,7 +12507,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12516,10 +12521,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45145</v>
+        <v>45679</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12532,7 +12537,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12575,7 +12580,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12589,10 +12594,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44909</v>
+        <v>44622</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12605,7 +12610,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12648,7 +12653,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12658,14 +12663,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>44909</v>
+        <v>46275</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12678,7 +12683,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.1</v>
+        <v>10.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12721,7 +12726,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12735,10 +12740,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46169</v>
+        <v>46275</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12751,7 +12756,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12794,7 +12799,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12808,10 +12813,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46265</v>
+        <v>46275</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12824,7 +12829,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12867,7 +12872,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12877,14 +12882,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45187</v>
+        <v>46275</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12896,13 +12901,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12945,7 +12945,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12959,10 +12959,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46169</v>
+        <v>46275</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13032,10 +13032,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45699</v>
+        <v>45456</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>7.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13091,7 +13091,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>44994</v>
+        <v>46275</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45253</v>
+        <v>45434</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13251,10 +13251,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45341</v>
+        <v>46277</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13324,10 +13324,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46275</v>
+        <v>45209</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13383,7 +13383,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13456,7 +13456,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46275</v>
+        <v>44988</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13529,7 +13529,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46275</v>
+        <v>45194</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13602,7 +13602,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13616,10 +13616,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46275</v>
+        <v>45368</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13692,7 +13692,7 @@
         <v>44530</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13762,10 +13762,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45448</v>
+        <v>46283</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13777,8 +13777,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13821,7 +13826,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13831,14 +13836,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46275</v>
+        <v>45714</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13851,7 +13856,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>10.2</v>
+        <v>0.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13894,7 +13899,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13908,10 +13913,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46277</v>
+        <v>45159</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13924,7 +13929,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>7.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13967,7 +13972,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13981,10 +13986,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46277</v>
+        <v>45699</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13997,7 +14002,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14040,7 +14045,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14054,10 +14059,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45747</v>
+        <v>45694</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14070,7 +14075,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14113,7 +14118,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14127,10 +14132,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45632</v>
+        <v>45253</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14143,7 +14148,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14186,7 +14191,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 39827-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14200,10 +14205,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45615</v>
+        <v>46289</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14215,8 +14220,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14259,7 +14269,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 39760-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14273,10 +14283,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14294,7 +14304,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14337,7 +14347,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 39770-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14351,10 +14361,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45012</v>
+        <v>46289</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14366,8 +14376,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14410,7 +14425,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14424,10 +14439,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45629</v>
+        <v>45615</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14440,7 +14455,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14483,7 +14498,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 39733-2026</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14497,10 +14512,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46289</v>
+        <v>45012</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14512,13 +14527,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14561,7 +14571,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 39760-2026</t>
+          <t>A 39733-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14578,7 +14588,7 @@
         <v>46289</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14596,7 +14606,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>9.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14639,7 +14649,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 39828-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14653,10 +14663,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46132</v>
+        <v>46289</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14668,8 +14678,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14712,7 +14727,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 39828-2026</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14726,10 +14741,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46289</v>
+        <v>45629</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14741,13 +14756,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14790,7 +14800,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39827-2026</t>
+          <t>A 39819-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14807,7 +14817,7 @@
         <v>46289</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14825,7 +14835,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14868,7 +14878,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 39819-2026</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14882,10 +14892,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46289</v>
+        <v>45632</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14897,13 +14907,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14963,7 +14968,7 @@
         <v>46289</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15024,7 +15029,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 39739-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15038,10 +15043,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46251</v>
+        <v>46289</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15059,7 +15064,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>6.7</v>
+        <v>2.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15102,7 +15107,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 39739-2026</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15116,10 +15121,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46289</v>
+        <v>46132</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15131,13 +15136,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 39770-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15194,10 +15194,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46289</v>
+        <v>46251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26044-2025</t>
+          <t>A 944-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45804</v>
+        <v>45666</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,17 +1088,17 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>31.3</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp
+Fällmossa
+Rävticka</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 26044-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45804</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams
 Humleblomster</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 944-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45666</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Koralltaggsvamp
-Fällmossa
-Rävticka</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 64461-2021</t>
+          <t>A 56463-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44511</v>
+        <v>45625</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1624,14 +1624,19 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>12.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1661,152 +1666,147 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 64461-2021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>44511</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Vitsippa</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 64461-2021 artfynd.xlsx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 64461-2021 karta.png", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 64461-2021 georefererad karta.tif", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 64461-2021 FSC-klagomål.docx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 64461-2021 FSC-klagomål mail.docx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 64461-2021 tillsynsbegäran.docx", "A 64461-2021")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 64461-2021 tillsynsbegäran mail.docx", "A 64461-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 56463-2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Scharlakansskål</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>46289</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 27986-2022</t>
+          <t>A 20445-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44745</v>
+        <v>44699</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15776-2022</t>
+          <t>A 27986-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44663</v>
+        <v>44745</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 64839-2021</t>
+          <t>A 24870-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44512</v>
+        <v>44728</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 70266-2021</t>
+          <t>A 15776-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44536</v>
+        <v>44663</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2533,13 +2533,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2582,7 +2577,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16174-2022</t>
+          <t>A 17062-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2596,10 +2591,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44668</v>
+        <v>44676</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2612,7 +2607,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2655,7 +2650,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16175-2022</t>
+          <t>A 64839-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2669,10 +2664,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44668</v>
+        <v>44512</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2685,7 +2680,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2728,7 +2723,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 20445-2022</t>
+          <t>A 16174-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2742,10 +2737,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44699</v>
+        <v>44668</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2758,7 +2753,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2801,7 +2796,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 24870-2022</t>
+          <t>A 16175-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2815,10 +2810,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44728</v>
+        <v>44668</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2831,7 +2826,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2874,7 +2869,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 17062-2022</t>
+          <t>A 70266-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2888,10 +2883,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44676</v>
+        <v>44536</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2903,8 +2898,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16116-2022</t>
+          <t>A 69169-2021</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44665</v>
+        <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3020,7 +3020,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 69169-2021</t>
+          <t>A 16116-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44530</v>
+        <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10.5</v>
+        <v>2.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44760</v>
+        <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45341</v>
+        <v>44671</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45230</v>
+        <v>45145</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45397</v>
+        <v>45694</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45385</v>
+        <v>44582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45379</v>
+        <v>44582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45290</v>
+        <v>45000</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44966</v>
+        <v>45714</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45588</v>
+        <v>45608</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45660</v>
+        <v>44663</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44582</v>
+        <v>45434</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3969,7 +3969,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44582</v>
+        <v>44909</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45628</v>
+        <v>44909</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4115,7 +4115,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45184</v>
+        <v>44516</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,14 +4198,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44886</v>
+        <v>45187</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4219,11 +4219,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4280,10 +4280,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45883</v>
+        <v>44602</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4339,7 +4339,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4353,10 +4353,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45547</v>
+        <v>45167</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4368,13 +4368,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>7.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4417,7 +4412,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4431,10 +4426,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45883</v>
+        <v>44974</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4446,8 +4441,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>9.199999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46030</v>
+        <v>45209</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4573,14 +4573,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44512</v>
+        <v>45512</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4636,7 +4636,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46030</v>
+        <v>44830</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44886</v>
+        <v>45706</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4738,13 +4738,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>19.4</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4787,7 +4782,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4801,10 +4796,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46037</v>
+        <v>45699</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4817,7 +4812,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9.1</v>
+        <v>1.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4860,7 +4855,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4874,10 +4869,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45699</v>
+        <v>44994</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4890,7 +4885,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4933,7 +4928,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4947,10 +4942,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44526</v>
+        <v>45593</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4963,7 +4958,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5006,7 +5001,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5020,10 +5015,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44671</v>
+        <v>44781</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5036,7 +5031,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5079,7 +5074,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5093,10 +5088,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45919</v>
+        <v>45614</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5108,8 +5103,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44974</v>
+        <v>45253</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5181,13 +5181,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>14.1</v>
+        <v>4.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5230,7 +5225,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5244,10 +5239,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45919</v>
+        <v>45397</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5260,7 +5255,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5303,7 +5298,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5317,10 +5312,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45919</v>
+        <v>44512</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5333,7 +5328,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5376,7 +5371,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5390,10 +5385,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45919</v>
+        <v>45341</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5406,7 +5401,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5449,7 +5444,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5463,10 +5458,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45560</v>
+        <v>44909</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5479,7 +5474,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5522,7 +5517,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5536,10 +5531,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45358</v>
+        <v>45264</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5552,7 +5547,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5595,7 +5590,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5609,10 +5604,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44887</v>
+        <v>45264</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5625,7 +5620,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5668,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5682,10 +5677,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45933</v>
+        <v>45264</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5698,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5741,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5755,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45006</v>
+        <v>44530</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5771,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5814,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5824,14 +5819,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45187</v>
+        <v>45448</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5843,13 +5838,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5892,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5906,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45952</v>
+        <v>44844</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5922,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5965,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5979,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45264</v>
+        <v>45665</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5995,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6038,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6052,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45962</v>
+        <v>45747</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6068,7 +6058,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6111,7 +6101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6125,10 +6115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44909</v>
+        <v>45006</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6141,7 +6131,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6184,7 +6174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6198,10 +6188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45965</v>
+        <v>44978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6213,13 +6203,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>11.6</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6262,7 +6247,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6276,10 +6261,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45000</v>
+        <v>44960</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6291,8 +6276,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6335,7 +6325,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6345,14 +6335,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45512</v>
+        <v>45632</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6365,7 +6355,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6408,7 +6398,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6422,10 +6412,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45986</v>
+        <v>45699</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6437,13 +6427,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>7.7</v>
+        <v>5.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6486,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6500,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45983</v>
+        <v>45615</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6516,7 +6501,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6559,7 +6544,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6573,10 +6558,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45983</v>
+        <v>44526</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6589,7 +6574,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.2</v>
+        <v>2.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6632,7 +6617,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6646,10 +6631,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46078</v>
+        <v>45012</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6662,7 +6647,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6705,7 +6690,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6719,10 +6704,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46078</v>
+        <v>45629</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6735,7 +6720,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6778,7 +6763,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6792,10 +6777,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46078</v>
+        <v>45111</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6808,7 +6793,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6851,7 +6836,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6865,10 +6850,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45999</v>
+        <v>44760</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6880,13 +6865,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>8.6</v>
+        <v>0.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6929,7 +6909,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6943,10 +6923,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45243</v>
+        <v>45379</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6958,13 +6938,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7007,7 +6982,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7021,10 +6996,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46078</v>
+        <v>45679</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7037,7 +7012,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7080,7 +7055,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7094,10 +7069,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46010</v>
+        <v>44988</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7110,7 +7085,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7153,7 +7128,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7167,10 +7142,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45665</v>
+        <v>45184</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7183,7 +7158,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7226,7 +7201,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7240,10 +7215,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44844</v>
+        <v>45628</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7256,7 +7231,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>6.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7299,7 +7274,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7313,10 +7288,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45111</v>
+        <v>44966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7329,7 +7304,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7372,7 +7347,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7386,10 +7361,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46106</v>
+        <v>45358</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7401,13 +7376,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7450,7 +7420,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7464,10 +7434,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46122</v>
+        <v>45660</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7480,7 +7450,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7523,7 +7493,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7537,10 +7507,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46128</v>
+        <v>45290</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7553,7 +7523,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7596,7 +7566,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7610,10 +7580,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44917</v>
+        <v>45588</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7626,7 +7596,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>10.9</v>
+        <v>1.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7669,7 +7639,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7683,10 +7653,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45092</v>
+        <v>44917</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7699,7 +7669,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.8</v>
+        <v>10.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7742,7 +7712,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7756,10 +7726,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45264</v>
+        <v>44494</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7772,7 +7742,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7815,7 +7785,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7829,10 +7799,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45740</v>
+        <v>44754</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7844,8 +7814,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7888,7 +7863,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7902,10 +7877,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45747</v>
+        <v>45547</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7917,8 +7892,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7961,7 +7941,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7975,10 +7955,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45758</v>
+        <v>45368</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7991,7 +7971,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8034,7 +8014,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8048,10 +8028,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44909</v>
+        <v>45243</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8063,8 +8043,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8107,7 +8092,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8121,10 +8106,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44909</v>
+        <v>45109</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8137,7 +8122,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8180,7 +8165,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8194,10 +8179,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45741</v>
+        <v>45408</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8210,7 +8195,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8253,7 +8238,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8267,10 +8252,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45789</v>
+        <v>44622</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8283,7 +8268,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8326,7 +8311,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8340,10 +8325,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45109</v>
+        <v>45264</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8356,7 +8341,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>5.9</v>
+        <v>2.2</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8399,7 +8384,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8413,10 +8398,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44994</v>
+        <v>45159</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8429,7 +8414,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.4</v>
+        <v>7.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8472,7 +8457,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8486,10 +8471,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45408</v>
+        <v>44886</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8501,8 +8486,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>4.2</v>
+        <v>19.4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8545,7 +8535,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8559,10 +8549,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45012</v>
+        <v>44790</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8575,7 +8565,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8618,7 +8608,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8632,10 +8622,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45264</v>
+        <v>44887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8648,7 +8638,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4.7</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8691,7 +8681,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8705,10 +8695,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44909</v>
+        <v>44886</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8720,8 +8710,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8764,7 +8759,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8778,10 +8773,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44516</v>
+        <v>45232</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8794,7 +8789,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8837,7 +8832,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45429</v>
+        <v>45092</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8867,7 +8862,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8910,7 +8905,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44602</v>
+        <v>45230</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8940,7 +8935,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8983,7 +8978,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8997,10 +8992,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46154</v>
+        <v>45560</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9013,7 +9008,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9056,7 +9051,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9070,10 +9065,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46154</v>
+        <v>44662</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9086,7 +9081,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>13.6</v>
+        <v>3.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9129,7 +9124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45817</v>
+        <v>44634</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9159,7 +9154,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9202,7 +9197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9216,10 +9211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46157</v>
+        <v>45456</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9232,7 +9227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9275,7 +9270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44830</v>
+        <v>45264</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9305,7 +9300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9348,7 +9343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46157</v>
+        <v>45194</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9378,7 +9373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9421,7 +9416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9435,10 +9430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46157</v>
+        <v>45385</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9451,7 +9446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9494,7 +9489,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9508,10 +9503,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46161</v>
+        <v>45012</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9524,7 +9519,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9567,7 +9562,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9581,10 +9576,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46161</v>
+        <v>44668</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9597,7 +9592,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9640,7 +9635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9654,10 +9649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45608</v>
+        <v>45230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9670,7 +9665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9713,7 +9708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9727,10 +9722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45706</v>
+        <v>45883</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9743,7 +9738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9786,7 +9781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9800,10 +9795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46169</v>
+        <v>45883</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9816,7 +9811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9859,7 +9854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9873,10 +9868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44668</v>
+        <v>45952</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9889,7 +9884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>6.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9932,7 +9927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9946,10 +9941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45167</v>
+        <v>45965</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9961,8 +9956,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>7.1</v>
+        <v>11.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10005,7 +10005,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10019,10 +10019,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44662</v>
+        <v>45962</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10078,7 +10078,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46177</v>
+        <v>45919</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10151,7 +10151,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10165,10 +10165,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46177</v>
+        <v>45919</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10224,7 +10224,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10238,10 +10238,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46177</v>
+        <v>45919</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10297,7 +10297,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46177</v>
+        <v>45919</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10370,7 +10370,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10384,10 +10384,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46181</v>
+        <v>45933</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10443,7 +10443,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44754</v>
+        <v>45983</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10472,13 +10472,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>8.800000000000001</v>
+        <v>13.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10521,7 +10516,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10535,10 +10530,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45230</v>
+        <v>45983</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10551,7 +10546,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10594,7 +10589,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10608,10 +10603,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>44663</v>
+        <v>45986</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10623,8 +10618,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>7.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10667,7 +10667,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45264</v>
+        <v>45999</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10696,8 +10696,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10740,7 +10745,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10754,10 +10759,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45264</v>
+        <v>46010</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10770,7 +10775,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10813,7 +10818,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10827,10 +10832,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44781</v>
+        <v>46030</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10843,7 +10848,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10886,7 +10891,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10900,10 +10905,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46195</v>
+        <v>46030</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10915,13 +10920,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10964,7 +10964,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10978,10 +10978,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45448</v>
+        <v>46037</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>9.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11037,7 +11037,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11051,10 +11051,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46204</v>
+        <v>46078</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11110,7 +11110,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46206</v>
+        <v>46078</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11183,7 +11183,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11197,10 +11197,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46206</v>
+        <v>46078</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11256,7 +11256,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44978</v>
+        <v>46078</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46206</v>
+        <v>46106</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11358,8 +11358,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11402,7 +11407,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11416,10 +11421,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46206</v>
+        <v>46122</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11432,7 +11437,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>6.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11475,7 +11480,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11489,10 +11494,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46206</v>
+        <v>46128</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11505,7 +11510,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11548,7 +11553,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11562,10 +11567,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46206</v>
+        <v>44909</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11578,7 +11583,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11621,7 +11626,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11635,10 +11640,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44790</v>
+        <v>45758</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11651,7 +11656,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11694,7 +11699,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11708,10 +11713,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46169</v>
+        <v>45740</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11724,7 +11729,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11767,7 +11772,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11781,10 +11786,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45614</v>
+        <v>45741</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11796,13 +11801,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I148" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11845,7 +11845,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11859,10 +11859,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45593</v>
+        <v>45789</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11918,7 +11918,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11932,10 +11932,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44634</v>
+        <v>45817</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12005,10 +12005,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45232</v>
+        <v>46154</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.8</v>
+        <v>13.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12078,10 +12078,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44960</v>
+        <v>46154</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12093,13 +12093,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>14.8</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12142,7 +12137,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12156,10 +12151,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44494</v>
+        <v>46157</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12172,7 +12167,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12215,7 +12210,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12229,10 +12224,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46265</v>
+        <v>46157</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12245,7 +12240,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12288,7 +12283,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12302,10 +12297,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46169</v>
+        <v>46157</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12318,7 +12313,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12361,7 +12356,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12375,10 +12370,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46169</v>
+        <v>46161</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12391,7 +12386,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12434,7 +12429,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12448,10 +12443,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45145</v>
+        <v>46161</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12464,7 +12459,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12507,7 +12502,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12521,10 +12516,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45679</v>
+        <v>46169</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12537,7 +12532,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12580,7 +12575,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12594,10 +12589,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44622</v>
+        <v>46177</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12610,7 +12605,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12653,7 +12648,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12663,14 +12658,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46275</v>
+        <v>46177</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12683,7 +12678,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>10.2</v>
+        <v>2.3</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12726,7 +12721,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12740,10 +12735,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46275</v>
+        <v>46177</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12756,7 +12751,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12799,7 +12794,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12813,10 +12808,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46275</v>
+        <v>46177</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12872,7 +12867,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12886,10 +12881,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46275</v>
+        <v>46181</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12902,7 +12897,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12945,7 +12940,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12959,10 +12954,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46275</v>
+        <v>46195</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12974,8 +12969,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I164" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13018,7 +13018,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13032,10 +13032,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45456</v>
+        <v>46204</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>7.5</v>
+        <v>3.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13091,7 +13091,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13105,10 +13105,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46275</v>
+        <v>46206</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13178,10 +13178,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45434</v>
+        <v>46206</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13251,10 +13251,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46277</v>
+        <v>46206</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13324,10 +13324,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45209</v>
+        <v>46206</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13383,7 +13383,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13397,10 +13397,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46277</v>
+        <v>46206</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13456,7 +13456,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>44988</v>
+        <v>46206</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13486,7 +13486,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13529,7 +13529,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13543,10 +13543,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45194</v>
+        <v>46169</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13559,7 +13559,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13602,7 +13602,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13616,10 +13616,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45368</v>
+        <v>46169</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13689,10 +13689,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44530</v>
+        <v>46265</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13748,7 +13748,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13762,10 +13762,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46283</v>
+        <v>46169</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13775,11 +13775,6 @@
       <c r="G175" t="inlineStr">
         <is>
           <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -13826,7 +13821,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13840,10 +13835,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45714</v>
+        <v>46275</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13856,7 +13851,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13899,7 +13894,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13913,10 +13908,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45159</v>
+        <v>46275</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13929,7 +13924,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>7.3</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13972,7 +13967,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13986,10 +13981,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45699</v>
+        <v>46275</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14002,7 +13997,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14045,7 +14040,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14059,10 +14054,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45694</v>
+        <v>46275</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14075,7 +14070,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14118,7 +14113,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14132,10 +14127,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45253</v>
+        <v>46275</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14148,7 +14143,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14191,7 +14186,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 39827-2026</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14201,14 +14196,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46289</v>
+        <v>46275</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14220,13 +14215,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14269,7 +14259,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 39760-2026</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14283,10 +14273,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46289</v>
+        <v>46277</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14298,13 +14288,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>9.800000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14347,7 +14332,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 39770-2026</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14361,10 +14346,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46289</v>
+        <v>46277</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14376,13 +14361,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14425,7 +14405,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14439,10 +14419,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45615</v>
+        <v>46283</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14454,8 +14434,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I184" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14498,7 +14483,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 39733-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14512,10 +14497,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45012</v>
+        <v>46289</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14527,8 +14512,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14571,7 +14561,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 39733-2026</t>
+          <t>A 39760-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14588,7 +14578,7 @@
         <v>46289</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14606,7 +14596,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14649,7 +14639,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 39828-2026</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14663,10 +14653,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46289</v>
+        <v>46132</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14678,13 +14668,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14727,7 +14712,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 39828-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14741,10 +14726,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45629</v>
+        <v>46289</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14756,8 +14741,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14800,7 +14790,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39819-2026</t>
+          <t>A 39827-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14817,7 +14807,7 @@
         <v>46289</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14835,7 +14825,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14878,7 +14868,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 39819-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14892,10 +14882,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45632</v>
+        <v>46289</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14907,8 +14897,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14968,7 +14963,7 @@
         <v>46289</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15046,7 +15041,7 @@
         <v>46289</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15107,7 +15102,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 39770-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15121,10 +15116,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46132</v>
+        <v>46289</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15136,8 +15131,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15197,7 +15197,7 @@
         <v>46251</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 944-2025</t>
+          <t>A 26044-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45666</v>
+        <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1124,155 +1124,155 @@
         <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams
+Humleblomster</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 944-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45666</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Koralltaggsvamp
 Fällmossa
 Rävticka</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 944-2025 artfynd.xlsx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 944-2025 karta.png", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 944-2025 georefererad karta.tif", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 944-2025 FSC-klagomål.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 944-2025 FSC-klagomål mail.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 944-2025 tillsynsbegäran.docx", "A 944-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 944-2025 tillsynsbegäran mail.docx", "A 944-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 26044-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45804</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams
-Humleblomster</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 26044-2025 artfynd.xlsx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 26044-2025 karta.png", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 26044-2025 georefererad karta.tif", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 26044-2025 FSC-klagomål.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 26044-2025 FSC-klagomål mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 26044-2025 tillsynsbegäran.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 26044-2025 tillsynsbegäran mail.docx", "A 26044-2025")</f>
-        <v/>
-      </c>
-    </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 46674-2023</t>
+          <t>A 20064-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45198</v>
+        <v>45434</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Ask
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 46674-2023</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45198</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Blåsippa
 Getrams</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 20064-2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45434</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Ask
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 56463-2024</t>
+          <t>A 64461-2021</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45625</v>
+        <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1624,19 +1624,14 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>12.2</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1666,257 +1661,262 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 64461-2021 artfynd.xlsx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 64461-2021 karta.png", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 64461-2021 georefererad karta.tif", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 64461-2021 FSC-klagomål.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 64461-2021 FSC-klagomål mail.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 64461-2021 tillsynsbegäran.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 64461-2021 tillsynsbegäran mail.docx", "A 64461-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 39832-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 39832-2026 artfynd.xlsx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 39832-2026 karta.png", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 39832-2026 georefererad karta.tif", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 39832-2026 FSC-klagomål.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 39832-2026 FSC-klagomål mail.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 39832-2026 tillsynsbegäran.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 39832-2026 tillsynsbegäran mail.docx", "A 39832-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 56463-2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45625</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Scharlakansskål</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 64461-2021</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44511</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Vitsippa</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 64461-2021 artfynd.xlsx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 64461-2021 karta.png", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 64461-2021 georefererad karta.tif", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 64461-2021 FSC-klagomål.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 64461-2021 FSC-klagomål mail.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 64461-2021 tillsynsbegäran.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 64461-2021 tillsynsbegäran mail.docx", "A 64461-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 39832-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 39832-2026 artfynd.xlsx", "A 39832-2026")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 39832-2026 karta.png", "A 39832-2026")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 39832-2026 georefererad karta.tif", "A 39832-2026")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 39832-2026 FSC-klagomål.docx", "A 39832-2026")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 39832-2026 FSC-klagomål mail.docx", "A 39832-2026")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 39832-2026 tillsynsbegäran.docx", "A 39832-2026")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 39832-2026 tillsynsbegäran mail.docx", "A 39832-2026")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 20445-2022</t>
+          <t>A 27986-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44699</v>
+        <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 27986-2022</t>
+          <t>A 15776-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44745</v>
+        <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 24870-2022</t>
+          <t>A 64839-2021</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44728</v>
+        <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15776-2022</t>
+          <t>A 70266-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44663</v>
+        <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2533,8 +2533,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2577,7 +2582,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 17062-2022</t>
+          <t>A 16174-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2591,10 +2596,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44676</v>
+        <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2607,7 +2612,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2650,7 +2655,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 64839-2021</t>
+          <t>A 16175-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2664,10 +2669,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44512</v>
+        <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2680,7 +2685,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2723,7 +2728,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16174-2022</t>
+          <t>A 20445-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2737,10 +2742,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44668</v>
+        <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2753,7 +2758,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2796,7 +2801,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16175-2022</t>
+          <t>A 24870-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2810,10 +2815,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44668</v>
+        <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2826,7 +2831,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2869,7 +2874,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 70266-2021</t>
+          <t>A 17062-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2883,10 +2888,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44536</v>
+        <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2898,13 +2903,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45429</v>
+        <v>44760</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3239,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 6666-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44671</v>
+        <v>45341</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35312-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45145</v>
+        <v>45397</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5752-2025</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3399,10 +3399,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45694</v>
+        <v>45385</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 53653-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3472,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44582</v>
+        <v>45230</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44582</v>
+        <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,10 +3618,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45000</v>
+        <v>46030</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3677,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9238-2025</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45714</v>
+        <v>46030</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3750,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 52433-2024</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45608</v>
+        <v>45290</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44663</v>
+        <v>45883</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 20067-2024</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45434</v>
+        <v>44582</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3969,7 +3969,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44909</v>
+        <v>44582</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4042,7 +4042,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44909</v>
+        <v>44966</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4115,7 +4115,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4129,10 +4129,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44516</v>
+        <v>45588</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4198,14 +4198,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45187</v>
+        <v>45660</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4217,13 +4217,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4266,7 +4261,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4280,10 +4275,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44602</v>
+        <v>45628</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4296,7 +4291,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4339,7 +4334,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4353,10 +4348,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45167</v>
+        <v>45883</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4369,7 +4364,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4412,7 +4407,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 55188-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4426,10 +4421,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44974</v>
+        <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4447,7 +4442,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>14.1</v>
+        <v>2.4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4490,7 +4485,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49005-2023</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45209</v>
+        <v>46037</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4520,7 +4515,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>9.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4563,7 +4558,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4573,14 +4568,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45512</v>
+        <v>45184</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4593,7 +4588,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4636,7 +4631,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 38788-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4650,10 +4645,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44830</v>
+        <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4665,8 +4660,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4709,7 +4709,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45706</v>
+        <v>44512</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 6493-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45699</v>
+        <v>45919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44994</v>
+        <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 48659-2024</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45593</v>
+        <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5001,7 +5001,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44781</v>
+        <v>45919</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 53284-2024</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45614</v>
+        <v>46078</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5103,13 +5103,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5152,7 +5147,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 59270-2023</t>
+          <t>A 10702-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5166,10 +5161,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45253</v>
+        <v>46078</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5182,7 +5177,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5225,7 +5220,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5239,10 +5234,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45397</v>
+        <v>45699</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5255,7 +5250,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5298,7 +5293,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 10665-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5312,10 +5307,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44512</v>
+        <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5328,7 +5323,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5371,7 +5366,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5385,10 +5380,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45341</v>
+        <v>44526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5401,7 +5396,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5444,7 +5439,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5458,10 +5453,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44909</v>
+        <v>45933</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5517,7 +5512,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5531,10 +5526,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45264</v>
+        <v>44671</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5547,7 +5542,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5590,7 +5585,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5604,10 +5599,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45264</v>
+        <v>44974</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5619,8 +5614,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>1.7</v>
+        <v>14.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5663,7 +5663,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45264</v>
+        <v>45560</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 69168-2021</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5750,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44530</v>
+        <v>45358</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5809,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 55457-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45448</v>
+        <v>44887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44844</v>
+        <v>46078</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45665</v>
+        <v>45952</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45747</v>
+        <v>46106</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6057,8 +6057,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6101,7 +6106,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6115,10 +6120,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45006</v>
+        <v>45962</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6131,7 +6136,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6174,7 +6179,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6188,10 +6193,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44978</v>
+        <v>45006</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6204,7 +6209,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6247,7 +6252,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 5459-2023</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6261,10 +6266,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44960</v>
+        <v>45965</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6278,11 +6283,11 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>14.8</v>
+        <v>11.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6325,7 +6330,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 58241-2024</t>
+          <t>A 43812-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6335,14 +6340,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45632</v>
+        <v>45187</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6354,8 +6359,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6398,7 +6408,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6412,10 +6422,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45699</v>
+        <v>46122</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6428,7 +6438,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6471,7 +6481,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54054-2024</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6485,10 +6495,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45615</v>
+        <v>45264</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6501,7 +6511,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.2</v>
+        <v>1.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6544,7 +6554,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6558,10 +6568,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44526</v>
+        <v>44909</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6574,7 +6584,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6617,7 +6627,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 14413-2023</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6631,10 +6641,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45012</v>
+        <v>46128</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6647,7 +6657,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6690,7 +6700,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 57256-2024</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6704,10 +6714,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45629</v>
+        <v>44886</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6719,8 +6729,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>19.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6763,7 +6778,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 58781-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6777,10 +6792,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45111</v>
+        <v>45986</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6792,8 +6807,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>7.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6836,7 +6856,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6850,10 +6870,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44760</v>
+        <v>45983</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6866,7 +6886,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6909,7 +6929,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6923,10 +6943,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45379</v>
+        <v>45983</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6939,7 +6959,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.3</v>
+        <v>13.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -6982,7 +7002,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3229-2025</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6996,10 +7016,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45679</v>
+        <v>45000</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7012,7 +7032,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7055,7 +7075,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 10617-2023</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7069,10 +7089,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44988</v>
+        <v>45740</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7085,7 +7105,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7128,7 +7148,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7138,14 +7158,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45184</v>
+        <v>45512</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7158,7 +7178,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7201,7 +7221,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7215,10 +7235,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45628</v>
+        <v>45758</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7231,7 +7251,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7274,7 +7294,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7288,10 +7308,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44966</v>
+        <v>45741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7304,7 +7324,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7347,7 +7367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7361,10 +7381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45358</v>
+        <v>45999</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7376,8 +7396,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7420,7 +7445,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7434,10 +7459,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45660</v>
+        <v>45789</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7450,7 +7475,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7493,7 +7518,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 56345-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7507,10 +7532,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45290</v>
+        <v>45243</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7522,8 +7547,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7566,7 +7596,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7580,10 +7610,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45588</v>
+        <v>46010</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7596,7 +7626,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7639,7 +7669,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7653,10 +7683,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44917</v>
+        <v>45665</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7669,7 +7699,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>10.9</v>
+        <v>1.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7712,7 +7742,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 59715-2021</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7726,10 +7756,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44494</v>
+        <v>44844</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7742,7 +7772,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7785,7 +7815,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7799,10 +7829,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44754</v>
+        <v>45111</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7814,13 +7844,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>8.800000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7863,7 +7888,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 38788-2024</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7877,10 +7902,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45547</v>
+        <v>44909</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7892,13 +7917,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7941,7 +7961,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 10679-2024</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7955,10 +7975,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45368</v>
+        <v>44917</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7971,7 +7991,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4.8</v>
+        <v>10.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8014,7 +8034,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8028,10 +8048,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45243</v>
+        <v>45092</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8043,13 +8063,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8092,7 +8107,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8106,10 +8121,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45109</v>
+        <v>46154</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8122,7 +8137,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8165,7 +8180,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8179,10 +8194,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45408</v>
+        <v>46154</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8195,7 +8210,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8238,7 +8253,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10286-2022</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8252,10 +8267,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44622</v>
+        <v>45264</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8268,7 +8283,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8311,7 +8326,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8325,10 +8340,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45264</v>
+        <v>45817</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8341,7 +8356,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8384,7 +8399,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37601-2023</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8398,10 +8413,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45159</v>
+        <v>46157</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8414,7 +8429,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>7.3</v>
+        <v>2.4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8457,7 +8472,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 15569-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8471,10 +8486,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44886</v>
+        <v>45747</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8486,13 +8501,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>19.4</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8535,7 +8545,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 33809-2022</t>
+          <t>A 22784-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8549,10 +8559,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44790</v>
+        <v>46157</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8565,7 +8575,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>2.4</v>
+        <v>6.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -8608,7 +8618,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8622,10 +8632,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44887</v>
+        <v>46157</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8638,7 +8648,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8681,7 +8691,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 23046-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8695,10 +8705,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44886</v>
+        <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8710,13 +8720,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -8759,7 +8764,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 54094-2023</t>
+          <t>A 23048-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8773,10 +8778,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45232</v>
+        <v>46161</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8789,7 +8794,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -8832,7 +8837,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 59969-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45092</v>
+        <v>44909</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8862,7 +8867,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8905,7 +8910,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 59980-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8919,10 +8924,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45230</v>
+        <v>44909</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8935,7 +8940,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8978,7 +8983,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 29999-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8992,10 +8997,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45560</v>
+        <v>45109</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9008,7 +9013,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9051,7 +9056,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 11696-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9065,10 +9070,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44662</v>
+        <v>44994</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9081,7 +9086,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9124,7 +9129,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 11744-2022</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9138,10 +9143,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44634</v>
+        <v>46169</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9154,7 +9159,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9197,7 +9202,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 24083-2024</t>
+          <t>A 16576-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9211,10 +9216,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45456</v>
+        <v>45408</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9227,7 +9232,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.5</v>
+        <v>4.2</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9270,7 +9275,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9284,10 +9289,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45264</v>
+        <v>45012</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9300,7 +9305,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9343,7 +9348,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 45492-2023</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9357,10 +9362,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45194</v>
+        <v>45264</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9373,7 +9378,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9416,7 +9421,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9430,10 +9435,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45385</v>
+        <v>46177</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9489,7 +9494,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 26103-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9503,10 +9508,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45012</v>
+        <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9519,7 +9524,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -9562,7 +9567,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 26136-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9576,10 +9581,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44668</v>
+        <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9592,7 +9597,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -9635,7 +9640,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9649,10 +9654,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45230</v>
+        <v>46177</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9665,7 +9670,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9708,7 +9713,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9722,10 +9727,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45883</v>
+        <v>46181</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9738,7 +9743,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9781,7 +9786,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9795,10 +9800,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45883</v>
+        <v>44516</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9811,7 +9816,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>9.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9854,7 +9859,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9868,10 +9873,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45952</v>
+        <v>45429</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9884,7 +9889,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9927,7 +9932,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9941,10 +9946,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45965</v>
+        <v>44602</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9956,13 +9961,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>11.6</v>
+        <v>1.1</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10005,7 +10005,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10019,10 +10019,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45962</v>
+        <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10035,7 +10035,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10078,7 +10078,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45919</v>
+        <v>46195</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10107,8 +10107,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10151,7 +10156,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 52433-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10165,10 +10170,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45919</v>
+        <v>45608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10181,7 +10186,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -10224,7 +10229,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10238,10 +10243,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45919</v>
+        <v>45706</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10254,7 +10259,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10297,7 +10302,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10311,10 +10316,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45919</v>
+        <v>46204</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10327,7 +10332,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10370,7 +10375,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10384,10 +10389,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45933</v>
+        <v>46206</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10400,7 +10405,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10443,7 +10448,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10457,10 +10462,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45983</v>
+        <v>46206</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10473,7 +10478,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>13.2</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10516,7 +10521,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10530,10 +10535,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45983</v>
+        <v>44668</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10546,7 +10551,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10589,7 +10594,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58781-2025</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10603,10 +10608,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45986</v>
+        <v>45167</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10618,13 +10623,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10667,7 +10667,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 30066-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10681,10 +10681,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45999</v>
+        <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10696,13 +10696,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -10745,7 +10740,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 30067-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10759,10 +10754,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46010</v>
+        <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10775,7 +10770,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -10818,7 +10813,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 30092-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10832,10 +10827,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46030</v>
+        <v>46206</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10848,7 +10843,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -10891,7 +10886,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10905,10 +10900,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46030</v>
+        <v>46206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10964,7 +10959,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10978,10 +10973,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46037</v>
+        <v>46169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10994,7 +10989,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>9.1</v>
+        <v>3.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11037,7 +11032,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 10702-2026</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11051,10 +11046,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46078</v>
+        <v>44662</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11067,7 +11062,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11110,7 +11105,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11124,10 +11119,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46078</v>
+        <v>44754</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11139,8 +11134,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11183,7 +11183,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 10665-2026</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11197,10 +11197,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46078</v>
+        <v>45230</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.3</v>
+        <v>3.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11256,7 +11256,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11270,10 +11270,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46078</v>
+        <v>44663</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11329,7 +11329,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 35810-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46106</v>
+        <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11358,13 +11358,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I142" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -11407,7 +11402,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11421,10 +11416,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46122</v>
+        <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11437,7 +11432,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11480,7 +11475,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11494,10 +11489,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46128</v>
+        <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11510,7 +11505,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11553,7 +11548,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11567,10 +11562,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44909</v>
+        <v>45264</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11583,7 +11578,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11626,7 +11621,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11640,10 +11635,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45758</v>
+        <v>45264</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11656,7 +11651,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11699,7 +11694,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11713,10 +11708,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45740</v>
+        <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11729,7 +11724,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11772,7 +11767,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 22697-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11786,10 +11781,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45741</v>
+        <v>45448</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11802,7 +11797,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11845,7 +11840,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11855,14 +11850,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45789</v>
+        <v>46275</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11875,7 +11870,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>10.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11918,7 +11913,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11932,10 +11927,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45817</v>
+        <v>46275</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11948,7 +11943,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11991,7 +11986,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12005,10 +12000,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46154</v>
+        <v>46275</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12021,7 +12016,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>13.6</v>
+        <v>1.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12064,7 +12059,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12078,10 +12073,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46154</v>
+        <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12094,7 +12089,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12137,7 +12132,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12151,10 +12146,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46157</v>
+        <v>46275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12167,7 +12162,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12210,7 +12205,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 22784-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12224,10 +12219,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46157</v>
+        <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12240,7 +12235,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.6</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12283,7 +12278,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12297,10 +12292,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46157</v>
+        <v>44978</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12313,7 +12308,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12356,7 +12351,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23046-2026</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12370,10 +12365,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46161</v>
+        <v>46277</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12386,7 +12381,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12429,7 +12424,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23048-2026</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12443,10 +12438,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46161</v>
+        <v>46277</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12459,7 +12454,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -12502,7 +12497,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 33809-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12516,10 +12511,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46169</v>
+        <v>44790</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -12532,7 +12527,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -12575,7 +12570,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26103-2026</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12589,10 +12584,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46177</v>
+        <v>45614</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -12604,8 +12599,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I159" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -12648,7 +12648,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26136-2026</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12662,10 +12662,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46177</v>
+        <v>45593</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12721,7 +12721,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 38647-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12735,10 +12735,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46177</v>
+        <v>46283</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -12750,8 +12750,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -12794,7 +12799,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 11744-2022</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12808,10 +12813,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46177</v>
+        <v>44634</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -12824,7 +12829,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -12867,7 +12872,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12881,10 +12886,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46181</v>
+        <v>45232</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -12897,7 +12902,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -12940,7 +12945,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12954,10 +12959,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46195</v>
+        <v>44960</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12971,11 +12976,11 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>14.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13018,7 +13023,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 39827-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13032,10 +13037,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46204</v>
+        <v>46289</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13047,8 +13052,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13091,7 +13101,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 30066-2026</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13105,10 +13115,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46206</v>
+        <v>44494</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13121,7 +13131,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13164,7 +13174,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 30067-2026</t>
+          <t>A 39760-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13178,10 +13188,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46206</v>
+        <v>46289</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13193,8 +13203,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -13237,7 +13252,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 30092-2026</t>
+          <t>A 39770-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13251,10 +13266,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46206</v>
+        <v>46289</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13266,8 +13281,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -13310,7 +13330,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 39733-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13324,10 +13344,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46206</v>
+        <v>46289</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -13339,8 +13359,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -13383,7 +13408,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 39828-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -13397,10 +13422,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46206</v>
+        <v>46289</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -13412,8 +13437,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13456,7 +13486,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 39819-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -13470,10 +13500,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46206</v>
+        <v>46289</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -13485,8 +13515,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13529,7 +13564,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 39800-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -13543,10 +13578,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46169</v>
+        <v>46289</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -13558,8 +13593,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13602,7 +13642,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 39739-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -13616,10 +13656,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46169</v>
+        <v>46289</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -13631,8 +13671,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13675,7 +13720,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 35810-2026</t>
+          <t>A 19092-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -13689,10 +13734,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46265</v>
+        <v>46132</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -13705,7 +13750,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13748,7 +13793,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 35312-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -13762,10 +13807,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46169</v>
+        <v>45145</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -13778,7 +13823,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13821,7 +13866,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -13835,10 +13880,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46275</v>
+        <v>45679</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -13851,7 +13896,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13894,7 +13939,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 10286-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -13908,10 +13953,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46275</v>
+        <v>44622</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -13924,7 +13969,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -13967,7 +14012,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 33897-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13981,10 +14026,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46275</v>
+        <v>46251</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -13996,8 +14041,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>2.8</v>
+        <v>6.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14040,7 +14090,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14054,10 +14104,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46275</v>
+        <v>45456</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14070,7 +14120,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14113,7 +14163,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14127,10 +14177,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46275</v>
+        <v>45434</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14143,7 +14193,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14186,7 +14236,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14196,14 +14246,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46275</v>
+        <v>45209</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14216,7 +14266,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>10.2</v>
+        <v>0.6</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14259,7 +14309,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 10617-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -14273,10 +14323,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46277</v>
+        <v>44988</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14289,7 +14339,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -14332,7 +14382,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37761-2026</t>
+          <t>A 45492-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -14346,10 +14396,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46277</v>
+        <v>45194</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -14362,7 +14412,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -14405,7 +14455,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 38647-2026</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -14419,10 +14469,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46283</v>
+        <v>45368</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -14434,13 +14484,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -14483,7 +14528,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 39733-2026</t>
+          <t>A 69168-2021</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -14497,10 +14542,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46289</v>
+        <v>44530</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -14512,13 +14557,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -14561,7 +14601,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 39760-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -14575,10 +14615,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46289</v>
+        <v>45714</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -14590,13 +14630,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>9.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -14639,7 +14674,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 19092-2026</t>
+          <t>A 37601-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -14653,10 +14688,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46132</v>
+        <v>45159</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -14669,7 +14704,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -14712,7 +14747,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 39828-2026</t>
+          <t>A 6493-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -14726,10 +14761,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46289</v>
+        <v>45699</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -14741,13 +14776,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -14790,7 +14820,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 39827-2026</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -14804,10 +14834,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46289</v>
+        <v>45694</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -14819,13 +14849,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>3.9</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14868,7 +14893,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 39819-2026</t>
+          <t>A 59270-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -14882,10 +14907,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46289</v>
+        <v>45253</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -14897,13 +14922,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>1.2</v>
+        <v>4.3</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -14946,7 +14966,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 39800-2026</t>
+          <t>A 54054-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -14960,10 +14980,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46289</v>
+        <v>45615</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -14975,13 +14995,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>3.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15024,7 +15039,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 39739-2026</t>
+          <t>A 14413-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15038,10 +15053,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46289</v>
+        <v>45012</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15053,13 +15068,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15102,7 +15112,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 39770-2026</t>
+          <t>A 57256-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15116,10 +15126,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46289</v>
+        <v>45629</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15131,13 +15141,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15180,7 +15185,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 33897-2026</t>
+          <t>A 58241-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15194,10 +15199,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46251</v>
+        <v>45632</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15209,13 +15214,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>6.7</v>
+        <v>3.8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>

--- a/Översikt ARBOGA.xlsx
+++ b/Översikt ARBOGA.xlsx
@@ -601,7 +601,7 @@
         <v>44728</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         <v>44530</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         <v>45666</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>44858</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45804</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>45666</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20064-2024</t>
+          <t>A 46674-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45434</v>
+        <v>45198</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1317,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1338,149 +1338,149 @@
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Blåsippa
+Getrams</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 20064-2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45434</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Ask
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 20064-2024 artfynd.xlsx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 20064-2024 karta.png", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 20064-2024 georefererad karta.tif", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 20064-2024 FSC-klagomål.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 20064-2024 FSC-klagomål mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 20064-2024 tillsynsbegäran.docx", "A 20064-2024")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 20064-2024 tillsynsbegäran mail.docx", "A 20064-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 46674-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>45198</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Blåsippa
-Getrams</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 46674-2023 artfynd.xlsx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 46674-2023 karta.png", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 46674-2023 georefererad karta.tif", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 46674-2023 FSC-klagomål.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 46674-2023 FSC-klagomål mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 46674-2023 tillsynsbegäran.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 46674-2023 tillsynsbegäran mail.docx", "A 46674-2023")</f>
-        <v/>
-      </c>
-    </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>45653</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>44511</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 39832-2026</t>
+          <t>A 56463-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46289</v>
+        <v>45625</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>6.2</v>
+        <v>12.2</v>
       </c>
       <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1775,148 +1775,148 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
+          <t>Scharlakansskål</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A 39832-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 39832-2026 artfynd.xlsx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 39832-2026 karta.png", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 39832-2026 georefererad karta.tif", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 39832-2026 FSC-klagomål.docx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 39832-2026 FSC-klagomål mail.docx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 39832-2026 tillsynsbegäran.docx", "A 39832-2026")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 39832-2026 tillsynsbegäran mail.docx", "A 39832-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 56463-2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45625</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ARBOGA</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Scharlakansskål</t>
-        </is>
-      </c>
-      <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/artfynd/A 56463-2024 artfynd.xlsx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor/A 56463-2024 karta.png", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/kartor_geotiff/A 56463-2024 georefererad karta.tif", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomål/A 56463-2024 FSC-klagomål.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/klagomålsmail/A 56463-2024 FSC-klagomål mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsyn/A 56463-2024 tillsynsbegäran.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-      <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1984/tillsynsmail/A 56463-2024 tillsynsbegäran mail.docx", "A 56463-2024")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44642</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44526</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>44698</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>44847</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>44509</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>44745</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>44663</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44512</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>44536</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44668</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>44668</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44699</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         <v>44728</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44676</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         <v>44530</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>44665</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>44668</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30305-2022</t>
+          <t>A 8125-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44760</v>
+        <v>44974</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3195,8 +3195,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>14.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3239,7 +3244,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6666-2024</t>
+          <t>A 49005-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3253,10 +3258,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45341</v>
+        <v>45209</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3269,7 +3274,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3312,7 +3317,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 14770-2024</t>
+          <t>A 61388-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3326,10 +3331,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45397</v>
+        <v>45264</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3342,7 +3347,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3385,7 +3390,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13121-2024</t>
+          <t>A 61394-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3399,10 +3404,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45385</v>
+        <v>45264</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3415,7 +3420,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3458,7 +3463,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53653-2023</t>
+          <t>A 45797-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3472,10 +3477,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45230</v>
+        <v>44844</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3488,7 +3493,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3531,7 +3536,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12405-2024</t>
+          <t>A 744-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3545,10 +3550,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45379</v>
+        <v>45665</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3561,7 +3566,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3604,7 +3609,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 993-2026</t>
+          <t>A 9247-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3618,10 +3623,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46030</v>
+        <v>45358</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3634,7 +3639,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3677,7 +3682,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1012-2026</t>
+          <t>A 63357-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3691,10 +3696,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46030</v>
+        <v>46010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3707,7 +3712,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3750,7 +3755,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 65255-2023</t>
+          <t>A 61892-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3764,10 +3769,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45290</v>
+        <v>44917</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3780,7 +3785,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>10.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3823,7 +3828,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 38302-2025</t>
+          <t>A 59715-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3837,10 +3842,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45883</v>
+        <v>44494</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3853,7 +3858,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3896,7 +3901,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 3113-2022</t>
+          <t>A 993-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3910,10 +3915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44582</v>
+        <v>46030</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3926,7 +3931,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3969,7 +3974,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 3128-2022</t>
+          <t>A 1012-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3983,10 +3988,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44582</v>
+        <v>46030</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3999,7 +4004,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4042,7 +4047,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6680-2023</t>
+          <t>A 2656-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4056,10 +4061,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44966</v>
+        <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4072,7 +4077,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.3</v>
+        <v>9.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4115,7 +4120,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47648-2024</t>
+          <t>A 43602-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4129,10 +4134,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45588</v>
+        <v>45184</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4145,7 +4150,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4188,7 +4193,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 494-2025</t>
+          <t>A 56977-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4202,10 +4207,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45660</v>
+        <v>45628</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4218,7 +4223,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4261,7 +4266,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 56977-2024</t>
+          <t>A 6680-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4275,10 +4280,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45628</v>
+        <v>44966</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4291,7 +4296,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.2</v>
+        <v>2.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4334,7 +4339,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 38299-2025</t>
+          <t>A 494-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4348,10 +4353,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45883</v>
+        <v>45660</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4364,7 +4369,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4407,7 +4412,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55188-2022</t>
+          <t>A 61300-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4421,10 +4426,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44886</v>
+        <v>45264</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4436,13 +4441,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2656-2026</t>
+          <t>A 65255-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4499,10 +4499,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46037</v>
+        <v>45290</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9.1</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4558,7 +4558,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 43602-2023</t>
+          <t>A 47648-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45184</v>
+        <v>45588</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4648,7 +4648,7 @@
         <v>45547</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 64833-2021</t>
+          <t>A 45154-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4723,10 +4723,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44512</v>
+        <v>45919</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 45116-2025</t>
+          <t>A 45128-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4799,7 +4799,7 @@
         <v>45919</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4855,7 +4855,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 45128-2025</t>
+          <t>A 45143-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4872,7 +4872,7 @@
         <v>45919</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 45143-2025</t>
+          <t>A 45116-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4945,7 +4945,7 @@
         <v>45919</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5001,7 +5001,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 45154-2025</t>
+          <t>A 54094-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45919</v>
+        <v>45232</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10698-2026</t>
+          <t>A 48121-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46078</v>
+        <v>45933</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5164,7 +5164,7 @@
         <v>46078</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6528-2025</t>
+          <t>A 10698-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45699</v>
+        <v>46078</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>46078</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 68237-2021</t>
+          <t>A 51989-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44526</v>
+        <v>45952</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48121-2025</t>
+          <t>A 16447-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45933</v>
+        <v>44671</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 16447-2022</t>
+          <t>A 5752-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5526,10 +5526,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44671</v>
+        <v>45694</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5585,7 +5585,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 8125-2023</t>
+          <t>A 3113-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44974</v>
+        <v>44582</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5614,13 +5614,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>14.1</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5663,7 +5658,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 41490-2024</t>
+          <t>A 3128-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5677,10 +5672,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45560</v>
+        <v>44582</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5693,7 +5688,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -5736,7 +5731,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 9247-2024</t>
+          <t>A 12650-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5750,10 +5745,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45358</v>
+        <v>45000</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5766,7 +5761,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -5809,7 +5804,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55457-2022</t>
+          <t>A 54470-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5823,10 +5818,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44887</v>
+        <v>45965</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5838,8 +5833,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>11.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10699-2026</t>
+          <t>A 54032-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46078</v>
+        <v>45962</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -5955,7 +5955,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 51989-2025</t>
+          <t>A 15711-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5969,10 +5969,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45952</v>
+        <v>44663</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6028,7 +6028,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15406-2026</t>
+          <t>A 65748-2021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46106</v>
+        <v>44516</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6057,13 +6057,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6106,7 +6101,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54032-2025</t>
+          <t>A 10699-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6120,10 +6115,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45962</v>
+        <v>46078</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6136,7 +6131,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6179,7 +6174,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13595-2023</t>
+          <t>A 39780-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6193,10 +6188,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45006</v>
+        <v>45167</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6209,7 +6204,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6252,7 +6247,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 54470-2025</t>
+          <t>A 32275-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6262,14 +6257,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45965</v>
+        <v>45512</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6281,13 +6276,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>11.6</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6330,7 +6320,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 43812-2023</t>
+          <t>A 42045-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6340,14 +6330,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45187</v>
+        <v>44830</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6359,13 +6349,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6408,7 +6393,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 17783-2026</t>
+          <t>A 55187-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6422,10 +6407,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46122</v>
+        <v>44886</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6437,8 +6422,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>6.4</v>
+        <v>19.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6481,7 +6471,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 61388-2023</t>
+          <t>A 15406-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6495,10 +6485,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45264</v>
+        <v>46106</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6510,8 +6500,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6554,7 +6549,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 59970-2022</t>
+          <t>A 58196-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6568,10 +6563,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44909</v>
+        <v>45983</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6584,7 +6579,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>13.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6627,7 +6622,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18827-2026</t>
+          <t>A 58194-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6641,10 +6636,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46128</v>
+        <v>45983</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6657,7 +6652,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6700,7 +6695,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55187-2022</t>
+          <t>A 48659-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6714,10 +6709,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44886</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6729,13 +6724,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>19.4</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6795,7 +6785,7 @@
         <v>45986</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6856,7 +6846,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 58194-2025</t>
+          <t>A 53284-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6870,10 +6860,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45983</v>
+        <v>45614</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6883,6 +6873,11 @@
       <c r="G81" t="inlineStr">
         <is>
           <t>ARBOGA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -6929,7 +6924,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 58196-2025</t>
+          <t>A 17783-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6943,10 +6938,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45983</v>
+        <v>46122</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6959,7 +6954,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>13.2</v>
+        <v>6.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7002,7 +6997,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 12650-2023</t>
+          <t>A 14770-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7016,10 +7011,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45000</v>
+        <v>45397</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7032,7 +7027,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7075,7 +7070,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 14057-2025</t>
+          <t>A 59970-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7089,10 +7084,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45740</v>
+        <v>44909</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7105,7 +7100,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7148,7 +7143,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32275-2024</t>
+          <t>A 61328-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7158,14 +7153,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45512</v>
+        <v>45264</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7178,7 +7173,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>6.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7221,7 +7216,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 17708-2025</t>
+          <t>A 60880-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7235,10 +7230,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45758</v>
+        <v>45999</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7250,8 +7245,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7294,7 +7294,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 14406-2025</t>
+          <t>A 18827-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7308,10 +7308,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45741</v>
+        <v>46128</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 60880-2025</t>
+          <t>A 60046-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45999</v>
+        <v>44909</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -7396,13 +7396,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7445,7 +7440,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 22735-2025</t>
+          <t>A 17708-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -7459,10 +7454,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45789</v>
+        <v>45758</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -7475,7 +7470,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -7518,7 +7513,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 56345-2023</t>
+          <t>A 68237-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7532,10 +7527,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45243</v>
+        <v>44526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -7547,13 +7542,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -7596,7 +7586,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 63357-2025</t>
+          <t>A 30323-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7610,10 +7600,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46010</v>
+        <v>45111</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7626,7 +7616,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -7669,7 +7659,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 744-2025</t>
+          <t>A 14057-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7683,10 +7673,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45665</v>
+        <v>45740</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7699,7 +7689,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.6</v>
+        <v>4.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7742,7 +7732,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 45797-2022</t>
+          <t>A 30305-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7756,10 +7746,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44844</v>
+        <v>44760</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7772,7 +7762,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7815,7 +7805,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 30323-2023</t>
+          <t>A 14406-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7829,10 +7819,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45111</v>
+        <v>45741</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7845,7 +7835,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -7888,7 +7878,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 60046-2022</t>
+          <t>A 3229-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7902,10 +7892,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44909</v>
+        <v>45679</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7918,7 +7908,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7961,7 +7951,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 61892-2022</t>
+          <t>A 22735-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7975,10 +7965,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44917</v>
+        <v>45789</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7991,7 +7981,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>10.9</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8034,7 +8024,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 26633-2023</t>
+          <t>A 29573-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8048,10 +8038,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45092</v>
+        <v>44754</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8063,8 +8053,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8107,7 +8102,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 22392-2026</t>
+          <t>A 10679-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8121,10 +8116,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>46154</v>
+        <v>45368</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8137,7 +8132,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8180,7 +8175,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 22355-2026</t>
+          <t>A 28069-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8194,10 +8189,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46154</v>
+        <v>45817</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8210,7 +8205,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>13.6</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -8253,7 +8248,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 61394-2023</t>
+          <t>A 22355-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8267,10 +8262,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45264</v>
+        <v>46154</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8283,7 +8278,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.7</v>
+        <v>13.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -8326,7 +8321,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 28069-2025</t>
+          <t>A 26633-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -8340,10 +8335,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45817</v>
+        <v>45092</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8356,7 +8351,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -8399,7 +8394,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 22785-2026</t>
+          <t>A 22392-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -8413,10 +8408,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -8429,7 +8424,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8472,7 +8467,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 15569-2025</t>
+          <t>A 22787-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -8486,10 +8481,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45747</v>
+        <v>46157</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -8502,7 +8497,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -8562,7 +8557,7 @@
         <v>46157</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -8618,7 +8613,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 22787-2026</t>
+          <t>A 22785-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8635,7 +8630,7 @@
         <v>46157</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -8648,7 +8643,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -8708,7 +8703,7 @@
         <v>46161</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -8781,7 +8776,7 @@
         <v>46161</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8837,7 +8832,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 59969-2022</t>
+          <t>A 41490-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44909</v>
+        <v>45560</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8867,7 +8862,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -8910,7 +8905,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 59980-2022</t>
+          <t>A 15487-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8924,10 +8919,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>44909</v>
+        <v>44662</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8940,7 +8935,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -8983,7 +8978,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 29999-2023</t>
+          <t>A 24083-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8997,10 +8992,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45109</v>
+        <v>45456</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9013,7 +9008,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>5.9</v>
+        <v>7.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9056,7 +9051,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11696-2023</t>
+          <t>A 61320-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9070,10 +9065,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44994</v>
+        <v>45264</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9086,7 +9081,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -9129,7 +9124,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 24349-2026</t>
+          <t>A 13121-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9143,10 +9138,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46169</v>
+        <v>45385</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9159,7 +9154,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9202,7 +9197,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 16576-2024</t>
+          <t>A 14420-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9216,10 +9211,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45408</v>
+        <v>45012</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9232,7 +9227,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -9275,7 +9270,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 14420-2023</t>
+          <t>A 16178-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9289,10 +9284,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45012</v>
+        <v>44668</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9305,7 +9300,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -9348,7 +9343,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 61320-2023</t>
+          <t>A 24349-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9362,10 +9357,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45264</v>
+        <v>46169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9378,7 +9373,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.7</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -9421,7 +9416,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 26134-2026</t>
+          <t>A 38302-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9435,10 +9430,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46177</v>
+        <v>45883</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -9451,7 +9446,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -9511,7 +9506,7 @@
         <v>46177</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -9584,7 +9579,7 @@
         <v>46177</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -9640,7 +9635,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 26130-2026</t>
+          <t>A 53629-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9654,10 +9649,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46177</v>
+        <v>45230</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -9670,7 +9665,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -9713,7 +9708,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 26302-2026</t>
+          <t>A 26130-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9727,10 +9722,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46181</v>
+        <v>46177</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -9743,7 +9738,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9786,7 +9781,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 65748-2021</t>
+          <t>A 26134-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9800,10 +9795,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44516</v>
+        <v>46177</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9816,7 +9811,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -9859,7 +9854,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19387-2024</t>
+          <t>A 38299-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9873,10 +9868,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45429</v>
+        <v>45883</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9889,7 +9884,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -9932,7 +9927,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 6698-2022</t>
+          <t>A 26302-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9946,10 +9941,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44602</v>
+        <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9962,7 +9957,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10005,7 +10000,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42045-2022</t>
+          <t>A 19387-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10019,10 +10014,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44830</v>
+        <v>45429</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10035,7 +10030,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10078,7 +10073,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 28033-2026</t>
+          <t>A 9238-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10092,10 +10087,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46195</v>
+        <v>45714</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10107,13 +10102,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10173,7 +10163,7 @@
         <v>45608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10229,7 +10219,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 7786-2025</t>
+          <t>A 20067-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10243,10 +10233,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45706</v>
+        <v>45434</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10259,7 +10249,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -10302,7 +10292,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 29571-2026</t>
+          <t>A 6698-2022</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10316,10 +10306,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46204</v>
+        <v>44602</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10332,7 +10322,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -10375,7 +10365,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 30063-2026</t>
+          <t>A 28033-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10389,10 +10379,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46206</v>
+        <v>46195</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10404,8 +10394,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -10448,7 +10443,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 30086-2026</t>
+          <t>A 7786-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10462,10 +10457,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46206</v>
+        <v>45706</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10478,7 +10473,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -10521,7 +10516,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 16178-2022</t>
+          <t>A 29571-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10535,10 +10530,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44668</v>
+        <v>46204</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -10551,7 +10546,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -10594,7 +10589,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 39780-2023</t>
+          <t>A 32224-2022</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10608,10 +10603,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45167</v>
+        <v>44781</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -10624,7 +10619,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -10684,7 +10679,7 @@
         <v>46206</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -10757,7 +10752,7 @@
         <v>46206</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -10830,7 +10825,7 @@
         <v>46206</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10886,7 +10881,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 30073-2026</t>
+          <t>A 30086-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10903,7 +10898,7 @@
         <v>46206</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10916,7 +10911,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10959,7 +10954,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24353-2026</t>
+          <t>A 30063-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10973,10 +10968,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46169</v>
+        <v>46206</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10989,7 +10984,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11032,7 +11027,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 15487-2022</t>
+          <t>A 30073-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11046,10 +11041,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44662</v>
+        <v>46206</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11062,7 +11057,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11105,7 +11100,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 29573-2022</t>
+          <t>A 64833-2021</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11119,10 +11114,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44754</v>
+        <v>44512</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11134,13 +11129,8 @@
           <t>ARBOGA</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11183,7 +11173,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 53629-2023</t>
+          <t>A 24353-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11197,10 +11187,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45230</v>
+        <v>46169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11213,7 +11203,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -11256,7 +11246,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 15711-2022</t>
+          <t>A 24344-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11270,10 +11260,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44663</v>
+        <v>46169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11286,7 +11276,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -11346,7 +11336,7 @@
         <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11402,7 +11392,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 24344-2026</t>
+          <t>A 24334-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11419,7 +11409,7 @@
         <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11432,7 +11422,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -11475,7 +11465,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 24334-2026</t>
+          <t>A 13595-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11489,10 +11479,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46169</v>
+        <v>45006</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11505,7 +11495,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11548,7 +11538,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 61300-2023</t>
+          <t>A 8818-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11562,10 +11552,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45264</v>
+        <v>44978</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11578,7 +11568,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -11621,7 +11611,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 61328-2023</t>
+          <t>A 5459-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11635,10 +11625,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45264</v>
+        <v>44960</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11650,8 +11640,13 @@
           <t>ARBOGA</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>6.3</v>
+        <v>14.8</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -11694,7 +11689,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32224-2022</t>
+          <t>A 6528-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11708,10 +11703,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44781</v>
+        <v>45699</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11724,7 +11719,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>5.4</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -11767,7 +11762,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 22697-2024</t>
+          <t>A 12405-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11781,10 +11776,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45448</v>
+        <v>45379</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -11797,7 +11792,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -11840,7 +11835,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 37404-2026</t>
+          <t>A 37385-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11850,14 +11845,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
         <v>46275</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11870,7 +11865,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>10.2</v>
+        <v>2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -11913,7 +11908,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37392-2026</t>
+          <t>A 37386-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11930,7 +11925,7 @@
         <v>46275</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11943,7 +11938,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -11986,7 +11981,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 37396-2026</t>
+          <t>A 37392-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12003,7 +11998,7 @@
         <v>46275</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12016,7 +12011,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12059,7 +12054,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37397-2026</t>
+          <t>A 37396-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12076,7 +12071,7 @@
         <v>46275</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12089,7 +12084,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12132,7 +12127,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37386-2026</t>
+          <t>A 37397-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12149,7 +12144,7 @@
         <v>46275</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12162,7 +12157,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12205,7 +12200,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 37385-2026</t>
+          <t>A 37404-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -12215,14 +12210,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
         <v>46275</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12235,7 +12230,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2</v>
+        <v>10.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -12278,7 +12273,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 8818-2023</t>
+          <t>A 37785-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12292,10 +12287,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>44978</v>
+        <v>46277</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12308,7 +12303,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -12351,7 +12346,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 37785-2026</t>
+          <t>A 37761-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -12368,7 +12363,7 @@
         <v>46277</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -12381,7 +12376,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -12424,7 +12419,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-        